--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -24,815 +24,857 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="302">
   <si>
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 08:42:47  |  Source: output/exports/score_*.json</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 10:09:07  |  Source: output/exports/score_*.json</t>
   </si>
   <si>
     <t>49.7</t>
   </si>
   <si>
-    <t>Regime / Label</t>
+    <t>Raw Regime / Label</t>
+  </si>
+  <si>
+    <t>🟡 HOLD (raw composite)</t>
+  </si>
+  <si>
+    <t>CALIBRATED ACTION</t>
+  </si>
+  <si>
+    <t>🟠 REDUCE — 35.3</t>
+  </si>
+  <si>
+    <t>Recommended Equity</t>
+  </si>
+  <si>
+    <t>20–40% Equities (calibrated)</t>
+  </si>
+  <si>
+    <t>Percentile Signal</t>
+  </si>
+  <si>
+    <t>REDUCE/SELL</t>
+  </si>
+  <si>
+    <t>Pillar Dispersion</t>
+  </si>
+  <si>
+    <t>HIGH (σ=14.36)</t>
+  </si>
+  <si>
+    <t>Data As-Of</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>Point-in-Time</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>PILLAR CONTRIBUTION DECOMPOSITION</t>
+  </si>
+  <si>
+    <t>Pillar</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Raw Score (0-100)</t>
+  </si>
+  <si>
+    <t>Weighted Contribution</t>
+  </si>
+  <si>
+    <t>% of Total Score</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Macro &amp; Monetary</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Global &amp; Intermarket</t>
+  </si>
+  <si>
+    <t>Bearish</t>
+  </si>
+  <si>
+    <t>Valuation &amp; Leverage</t>
+  </si>
+  <si>
+    <t>Quant Model (MLR/VAR)</t>
+  </si>
+  <si>
+    <t>ML Forecast</t>
+  </si>
+  <si>
+    <t>Market Structure</t>
+  </si>
+  <si>
+    <t>TOTAL COMPOSITE</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>COMPOSITE SCORE HISTORY vs VN-INDEX</t>
+  </si>
+  <si>
+    <t>Two-tier scores: Total Score = raw composite (reference) | Calibrated Score = action signal (z-score vs prior quarters, point-in-time). Pillar columns are weighted contributions (raw × weight). Fwd Return = VN-Index return of the NEXT quarter (signal evaluation).</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Total Score</t>
+  </si>
+  <si>
+    <t>Label (Raw)</t>
+  </si>
+  <si>
+    <t>Calibrated Score</t>
+  </si>
+  <si>
+    <t>Calibrated Label</t>
+  </si>
+  <si>
+    <t>Dispersion</t>
+  </si>
+  <si>
+    <t>VN-Index Close</t>
+  </si>
+  <si>
+    <t>QoQ Return</t>
+  </si>
+  <si>
+    <t>Fwd Return (t+1)</t>
+  </si>
+  <si>
+    <t>2021-Q1</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>2021-Q2</t>
+  </si>
+  <si>
+    <t>2021-Q3</t>
+  </si>
+  <si>
+    <t>2021-Q4</t>
+  </si>
+  <si>
+    <t>2022-Q1</t>
+  </si>
+  <si>
+    <t>BUY/ACCUMULATE</t>
+  </si>
+  <si>
+    <t>2022-Q2</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>2022-Q3</t>
+  </si>
+  <si>
+    <t>REDUCE</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>2022-Q4</t>
+  </si>
+  <si>
+    <t>2023-Q1</t>
+  </si>
+  <si>
+    <t>2023-Q2</t>
+  </si>
+  <si>
+    <t>2023-Q3</t>
+  </si>
+  <si>
+    <t>ACCUMULATE</t>
+  </si>
+  <si>
+    <t>2023-Q4</t>
+  </si>
+  <si>
+    <t>2024-Q1</t>
+  </si>
+  <si>
+    <t>2024-Q2</t>
+  </si>
+  <si>
+    <t>2024-Q3</t>
+  </si>
+  <si>
+    <t>2024-Q4</t>
+  </si>
+  <si>
+    <t>2025-Q1</t>
+  </si>
+  <si>
+    <t>2025-Q2</t>
+  </si>
+  <si>
+    <t>2025-Q3</t>
+  </si>
+  <si>
+    <t>2025-Q4</t>
+  </si>
+  <si>
+    <t>2026-Q1</t>
+  </si>
+  <si>
+    <t>2026-Q2</t>
+  </si>
+  <si>
+    <t>2026-Q3</t>
+  </si>
+  <si>
+    <t>2026-Q4</t>
+  </si>
+  <si>
+    <t>FACTOR IMPACT — MULTIPLE LINEAR REGRESSION (Newey-West HAC)</t>
+  </si>
+  <si>
+    <t>Dependent variable: forward VN-Index log-return. Quarter: 2026-Q4. Significance: *** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10.</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Beta (β)</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>Significance</t>
+  </si>
+  <si>
+    <t>Sign Expected</t>
+  </si>
+  <si>
+    <t>Sign Actual</t>
+  </si>
+  <si>
+    <t>Sign OK</t>
+  </si>
+  <si>
+    <t>|β| Rank</t>
+  </si>
+  <si>
+    <t>Economic Reading</t>
+  </si>
+  <si>
+    <t>delta_dxy</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>A rise in delta_dxy is a headwind for next-quarter VN-Index returns (statistically significant, p=0.028).</t>
+  </si>
+  <si>
+    <t>delta_us10y</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>A rise in delta_us10y is supportive of next-quarter VN-Index returns (not significant, p=0.944).</t>
+  </si>
+  <si>
+    <t>delta_usdjpy</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>A rise in delta_usdjpy is a headwind for next-quarter VN-Index returns (weakly significant, p=0.059).</t>
+  </si>
+  <si>
+    <t>usd_vnd_pct_change</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>A rise in usd_vnd_pct_change is a headwind for next-quarter VN-Index returns (not significant, p=0.749).</t>
+  </si>
+  <si>
+    <t>rsi_14</t>
+  </si>
+  <si>
+    <t>A rise in rsi_14 is supportive of next-quarter VN-Index returns (statistically significant, p=0.022).</t>
+  </si>
+  <si>
+    <t>macd_hist</t>
+  </si>
+  <si>
+    <t>A rise in macd_hist is a headwind for next-quarter VN-Index returns (not significant, p=0.236).</t>
+  </si>
+  <si>
+    <t>bb_pct</t>
+  </si>
+  <si>
+    <t>A rise in bb_pct is a headwind for next-quarter VN-Index returns (not significant, p=0.880).</t>
+  </si>
+  <si>
+    <t>rvol_20d</t>
+  </si>
+  <si>
+    <t>A rise in rvol_20d is a headwind for next-quarter VN-Index returns (not significant, p=0.378).</t>
+  </si>
+  <si>
+    <t>drawdown_from_peak</t>
+  </si>
+  <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>A rise in drawdown_from_peak is a headwind for next-quarter VN-Index returns (statistically significant, p=0.001).</t>
+  </si>
+  <si>
+    <t>price_vs_ma200</t>
+  </si>
+  <si>
+    <t>A rise in price_vs_ma200 is supportive of next-quarter VN-Index returns (weakly significant, p=0.089).</t>
+  </si>
+  <si>
+    <t>log_return_lag1</t>
+  </si>
+  <si>
+    <t>A rise in log_return_lag1 is a headwind for next-quarter VN-Index returns (not significant, p=0.228).</t>
+  </si>
+  <si>
+    <t>log_return_lag5</t>
+  </si>
+  <si>
+    <t>A rise in log_return_lag5 is a headwind for next-quarter VN-Index returns (not significant, p=0.863).</t>
+  </si>
+  <si>
+    <t>Sign-check pass rate:</t>
+  </si>
+  <si>
+    <t>1/12 (8%)</t>
+  </si>
+  <si>
+    <t>BETA STABILITY ACROSS QUARTERS (sign consistency = % quarters with same sign as latest)</t>
+  </si>
+  <si>
+    <t>Sign Consistency</t>
+  </si>
+  <si>
+    <t>VAR GRANGER CAUSALITY — WHICH FACTORS LEAD THE VN-INDEX?</t>
+  </si>
+  <si>
+    <t>H0: factor does NOT Granger-cause VNI returns. p &lt; 0.05 → reject H0 → factor has leading power.</t>
+  </si>
+  <si>
+    <t>F-Statistic</t>
+  </si>
+  <si>
+    <t>Granger-causes VNI?</t>
+  </si>
+  <si>
+    <t>Verdict</t>
+  </si>
+  <si>
+    <t>YES — LEADING</t>
+  </si>
+  <si>
+    <t>delta_dxy contains predictive information for future VN-Index returns.</t>
+  </si>
+  <si>
+    <t>delta_vn1y_yield</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>No statistical evidence that delta_vn1y_yield leads VN-Index returns.</t>
+  </si>
+  <si>
+    <t>pe_zscore</t>
+  </si>
+  <si>
+    <t>No statistical evidence that pe_zscore leads VN-Index returns.</t>
+  </si>
+  <si>
+    <t>No statistical evidence that delta_us10y leads VN-Index returns.</t>
+  </si>
+  <si>
+    <t>No statistical evidence that delta_usdjpy leads VN-Index returns.</t>
+  </si>
+  <si>
+    <t>MACHINE LEARNING — WALK-FORWARD VALIDATION (no look-ahead bias)</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>xgboost</t>
+  </si>
+  <si>
+    <t>Folds</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>Mean Accuracy</t>
+  </si>
+  <si>
+    <t>Std Accuracy</t>
+  </si>
+  <si>
+    <t>Mean F1 (weighted)</t>
+  </si>
+  <si>
+    <t>Latest Prediction</t>
+  </si>
+  <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>Prediction Confidence</t>
+  </si>
+  <si>
+    <t>WALK-FORWARD FOLD METRICS (expanding window)</t>
+  </si>
+  <si>
+    <t>Fold</t>
+  </si>
+  <si>
+    <t>Train Size</t>
+  </si>
+  <si>
+    <t>Test Size</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>F1 (weighted)</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>TOP FEATURE IMPORTANCE (model-implied factor relevance)</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>Importance</t>
+  </si>
+  <si>
+    <t>ema_20</t>
+  </si>
+  <si>
+    <t>macd_line</t>
+  </si>
+  <si>
+    <t>etf_flow_q_zscore</t>
+  </si>
+  <si>
+    <t>bb_mid</t>
+  </si>
+  <si>
+    <t>us10y_30d_change</t>
+  </si>
+  <si>
+    <t>usd_vnd_zscore_lag1</t>
+  </si>
+  <si>
+    <t>us10y_zscore_1y</t>
+  </si>
+  <si>
+    <t>oil_n_shock_days_ytd</t>
+  </si>
+  <si>
+    <t>etf_flow_q_zscore_live</t>
+  </si>
+  <si>
+    <t>dxy_zscore_60d</t>
+  </si>
+  <si>
+    <t>bb_lower</t>
+  </si>
+  <si>
+    <t>ex_vingroup_pe</t>
+  </si>
+  <si>
+    <t>nff_ex_etf_q_ytd</t>
+  </si>
+  <si>
+    <t>nff_ex_etf_rolling60d</t>
+  </si>
+  <si>
+    <t>rvol_10d</t>
+  </si>
+  <si>
+    <t>FACTOR-LEVEL SCORE DECOMPOSITION — 2026-Q4</t>
+  </si>
+  <si>
+    <t>Every indicator inside each pillar with its parsed 0-100 score. &lt;MISSING&gt; indicators fall back to neutral 50.</t>
+  </si>
+  <si>
+    <t>Pillar Weight</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>Observed Value / Analysis</t>
+  </si>
+  <si>
+    <t>Score (0-100)</t>
+  </si>
+  <si>
+    <t>Data Status</t>
+  </si>
+  <si>
+    <t>vn1y_yield</t>
+  </si>
+  <si>
+    <t>3.86%</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>ir_trend</t>
+  </si>
+  <si>
+    <t>Δ VN1Y = 0.0044 (→ Hold)</t>
+  </si>
+  <si>
+    <t>usd_vnd</t>
+  </si>
+  <si>
+    <t>Z-score = -1.27</t>
+  </si>
+  <si>
+    <t>m2_yoy_growth</t>
+  </si>
+  <si>
+    <t>MISSING</t>
+  </si>
+  <si>
+    <t>vn_bonds</t>
+  </si>
+  <si>
+    <t>VN10Y 4.48% | Spread 0.53%</t>
+  </si>
+  <si>
+    <t>dxy</t>
+  </si>
+  <si>
+    <t>Z = 1.05</t>
+  </si>
+  <si>
+    <t>us10y</t>
+  </si>
+  <si>
+    <t>5.18%</t>
+  </si>
+  <si>
+    <t>nff_ex_etf</t>
+  </si>
+  <si>
+    <t>Z = 0.21 (Neutral)</t>
+  </si>
+  <si>
+    <t>-0.16% of Market Cap (YTD in Q)</t>
+  </si>
+  <si>
+    <t>jpy_carry</t>
+  </si>
+  <si>
+    <t>Z = -0.16 (Neutral)</t>
+  </si>
+  <si>
+    <t>oil_shock</t>
+  </si>
+  <si>
+    <t>Oil Shock Score = 43.8 (Max Δ5d = 19.5%)</t>
+  </si>
+  <si>
+    <t>P/E Headline: 12.46 | Median: 10.25 | Ex-VG: 10.03 | Z = 0.81 (FAIR VALUE)</t>
+  </si>
+  <si>
+    <t>pb_zscore</t>
+  </si>
+  <si>
+    <t>Z = 0.68 (FAIR VALUE)</t>
+  </si>
+  <si>
+    <t>margin_risk</t>
+  </si>
+  <si>
+    <t>Risk = 20/100 (SAFE)</t>
+  </si>
+  <si>
+    <t>mlr_forecast</t>
+  </si>
+  <si>
+    <t>Forward log-return/day (next ~1M) = -0.0006</t>
+  </si>
+  <si>
+    <t>var_forecast</t>
+  </si>
+  <si>
+    <t>VAR T+5 return = 0.0011</t>
+  </si>
+  <si>
+    <t>mlr_adj_r2</t>
+  </si>
+  <si>
+    <t>Adj-R² = 0.1092 → confidence bonus 1.1</t>
+  </si>
+  <si>
+    <t>granger_leaders</t>
+  </si>
+  <si>
+    <t>1 vars Granger-cause VNI (p&lt;5%)</t>
+  </si>
+  <si>
+    <t>model_quality</t>
+  </si>
+  <si>
+    <t>Accuracy=42.5% F1=0.369 → quality 40</t>
+  </si>
+  <si>
+    <t>ml_signal</t>
+  </si>
+  <si>
+    <t>Forecast: DOWN (conf=50%)</t>
+  </si>
+  <si>
+    <t>ftse_upgrade</t>
+  </si>
+  <si>
+    <t>Status: confirmed</t>
+  </si>
+  <si>
+    <t>rebalancing</t>
+  </si>
+  <si>
+    <t>0 months to rebalancing → bonus +20</t>
+  </si>
+  <si>
+    <t>adtv</t>
+  </si>
+  <si>
+    <t>ADTV data unavailable → neutral score 50</t>
+  </si>
+  <si>
+    <t>etf_flow</t>
+  </si>
+  <si>
+    <t>Z = -0.21 (Neutral)</t>
+  </si>
+  <si>
+    <t>etf_flow_q_ytd</t>
+  </si>
+  <si>
+    <t>0.00% of Market Cap (YTD in Q)</t>
+  </si>
+  <si>
+    <t>SIGNAL EFFICACY — DOES THE CALIBRATED ACTION SIGNAL PREDICT NEXT-QUARTER RETURNS?</t>
+  </si>
+  <si>
+    <t>Primary test = CALIBRATED action signal (z-score vs prior quarters, point-in-time). Signal at quarter t is evaluated against the VN-Index return over quarter t+1. Raw composite shown as comparison. No look-ahead.</t>
+  </si>
+  <si>
+    <t>Quarters evaluated (N)</t>
+  </si>
+  <si>
+    <t>IC Calibrated (Pearson)</t>
+  </si>
+  <si>
+    <t>IC Calibrated (Spearman)</t>
+  </si>
+  <si>
+    <t>IC Raw composite (Pearson) — comparison</t>
+  </si>
+  <si>
+    <t>IC Raw composite (Spearman) — comparison</t>
+  </si>
+  <si>
+    <t>Directional Hit Rate — calibrated (≥50 → up)</t>
+  </si>
+  <si>
+    <t>Directional Hit Rate — raw (comparison)</t>
+  </si>
+  <si>
+    <t>Strategy total return — calibrated signal</t>
+  </si>
+  <si>
+    <t>Strategy total return — raw signal (comparison)</t>
+  </si>
+  <si>
+    <t>Buy &amp; Hold total return</t>
+  </si>
+  <si>
+    <t>Strategy Sharpe (annualised, rf=0)</t>
+  </si>
+  <si>
+    <t>Buy &amp; Hold Sharpe (annualised, rf=0)</t>
+  </si>
+  <si>
+    <t>FORWARD RETURN BY CALIBRATED REGIME BUCKET</t>
+  </si>
+  <si>
+    <t>Calibrated Regime</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Avg Fwd Return</t>
+  </si>
+  <si>
+    <t>Median Fwd Return</t>
+  </si>
+  <si>
+    <t>Win Rate (fwd&gt;0)</t>
+  </si>
+  <si>
+    <t>QUARTER-BY-QUARTER SIGNAL LEDGER (calibrated)</t>
+  </si>
+  <si>
+    <t>Calibrated (t)</t>
+  </si>
+  <si>
+    <t>Equity Allocation</t>
+  </si>
+  <si>
+    <t>Raw Score (t)</t>
+  </si>
+  <si>
+    <t>Raw Label</t>
+  </si>
+  <si>
+    <t>Strategy Return</t>
+  </si>
+  <si>
+    <t>Hit?</t>
+  </si>
+  <si>
+    <t>Strategy Index</t>
+  </si>
+  <si>
+    <t>Buy&amp;Hold Index</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>✗</t>
+  </si>
+  <si>
+    <t>Note: strategy holds the mid-point of the CALIBRATED recommended equity band (e.g. HOLD = 50%) for the following quarter; residual cash earns 0%. Gross of fees/slippage. Quarterly Sharpe annualised with √4. ICs are reported as-is (no curve-fitting) — low IC means weak directional edge; the calibrated layer primarily restores regime dispersion for allocation sizing, not alpha prediction.</t>
+  </si>
+  <si>
+    <t>METHODOLOGY — WEIGHTS, REGIME BANDS &amp; DATA SOURCES</t>
+  </si>
+  <si>
+    <t>REGIME BANDS (config.py SCORE_LABELS — single source of truth)</t>
+  </si>
+  <si>
+    <t>Score Range</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>80–100</t>
+  </si>
+  <si>
+    <t>🟢 BUY</t>
+  </si>
+  <si>
+    <t>Highly favorable environment — Increase exposure aggressively</t>
+  </si>
+  <si>
+    <t>85–100% Equities</t>
+  </si>
+  <si>
+    <t>65–79</t>
+  </si>
+  <si>
+    <t>🔵 ACCUMULATE</t>
+  </si>
+  <si>
+    <t>Gradually accumulate — Controllable risks</t>
+  </si>
+  <si>
+    <t>70–85% Equities</t>
+  </si>
+  <si>
+    <t>50–64</t>
   </si>
   <si>
     <t>🟡 HOLD</t>
   </si>
   <si>
-    <t>Recommended Equity</t>
+    <t>Neutral — Await confirming signals</t>
   </si>
   <si>
     <t>40–60% Equities</t>
   </si>
   <si>
-    <t>Percentile Signal</t>
-  </si>
-  <si>
-    <t>REDUCE/SELL</t>
-  </si>
-  <si>
-    <t>Pillar Dispersion</t>
-  </si>
-  <si>
-    <t>HIGH (σ=14.36)</t>
-  </si>
-  <si>
-    <t>Data As-Of</t>
-  </si>
-  <si>
-    <t>2026-09-25</t>
-  </si>
-  <si>
-    <t>Point-in-Time</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>PILLAR CONTRIBUTION DECOMPOSITION</t>
-  </si>
-  <si>
-    <t>Pillar</t>
-  </si>
-  <si>
-    <t>Weight</t>
-  </si>
-  <si>
-    <t>Raw Score (0-100)</t>
-  </si>
-  <si>
-    <t>Weighted Contribution</t>
-  </si>
-  <si>
-    <t>% of Total Score</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Macro &amp; Monetary</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Global &amp; Intermarket</t>
-  </si>
-  <si>
-    <t>Bearish</t>
-  </si>
-  <si>
-    <t>Valuation &amp; Leverage</t>
-  </si>
-  <si>
-    <t>Quant Model (MLR/VAR)</t>
-  </si>
-  <si>
-    <t>ML Forecast</t>
-  </si>
-  <si>
-    <t>Market Structure</t>
-  </si>
-  <si>
-    <t>TOTAL COMPOSITE</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>COMPOSITE SCORE HISTORY vs VN-INDEX</t>
-  </si>
-  <si>
-    <t>Pillar columns are weighted contributions (raw × weight). Fwd Return = VN-Index return of the NEXT quarter (signal evaluation).</t>
-  </si>
-  <si>
-    <t>Quarter</t>
-  </si>
-  <si>
-    <t>Total Score</t>
-  </si>
-  <si>
-    <t>Label</t>
-  </si>
-  <si>
-    <t>Dispersion</t>
-  </si>
-  <si>
-    <t>VN-Index Close</t>
-  </si>
-  <si>
-    <t>QoQ Return</t>
-  </si>
-  <si>
-    <t>Fwd Return (t+1)</t>
-  </si>
-  <si>
-    <t>2021-Q1</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>2021-Q2</t>
-  </si>
-  <si>
-    <t>2021-Q3</t>
-  </si>
-  <si>
-    <t>2021-Q4</t>
-  </si>
-  <si>
-    <t>2022-Q1</t>
-  </si>
-  <si>
-    <t>BUY/ACCUMULATE</t>
-  </si>
-  <si>
-    <t>2022-Q2</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>2022-Q3</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>2022-Q4</t>
-  </si>
-  <si>
-    <t>REDUCE</t>
-  </si>
-  <si>
-    <t>2023-Q1</t>
-  </si>
-  <si>
-    <t>2023-Q2</t>
-  </si>
-  <si>
-    <t>2023-Q3</t>
-  </si>
-  <si>
-    <t>2023-Q4</t>
-  </si>
-  <si>
-    <t>2024-Q1</t>
-  </si>
-  <si>
-    <t>2024-Q2</t>
-  </si>
-  <si>
-    <t>2024-Q3</t>
-  </si>
-  <si>
-    <t>2024-Q4</t>
-  </si>
-  <si>
-    <t>2025-Q1</t>
-  </si>
-  <si>
-    <t>2025-Q2</t>
-  </si>
-  <si>
-    <t>2025-Q3</t>
-  </si>
-  <si>
-    <t>2025-Q4</t>
-  </si>
-  <si>
-    <t>2026-Q1</t>
-  </si>
-  <si>
-    <t>2026-Q2</t>
-  </si>
-  <si>
-    <t>2026-Q3</t>
-  </si>
-  <si>
-    <t>2026-Q4</t>
-  </si>
-  <si>
-    <t>FACTOR IMPACT — MULTIPLE LINEAR REGRESSION (Newey-West HAC)</t>
-  </si>
-  <si>
-    <t>Dependent variable: forward VN-Index log-return. Quarter: 2026-Q4. Significance: *** p&lt;0.01, ** p&lt;0.05, * p&lt;0.10.</t>
-  </si>
-  <si>
-    <t>Factor</t>
-  </si>
-  <si>
-    <t>Beta (β)</t>
-  </si>
-  <si>
-    <t>P-value</t>
-  </si>
-  <si>
-    <t>Significance</t>
-  </si>
-  <si>
-    <t>Sign Expected</t>
-  </si>
-  <si>
-    <t>Sign Actual</t>
-  </si>
-  <si>
-    <t>Sign OK</t>
-  </si>
-  <si>
-    <t>|β| Rank</t>
-  </si>
-  <si>
-    <t>Economic Reading</t>
-  </si>
-  <si>
-    <t>delta_dxy</t>
-  </si>
-  <si>
-    <t>**</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>A rise in delta_dxy is a headwind for next-quarter VN-Index returns (statistically significant, p=0.028).</t>
-  </si>
-  <si>
-    <t>delta_us10y</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>+</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>A rise in delta_us10y is supportive of next-quarter VN-Index returns (not significant, p=0.944).</t>
-  </si>
-  <si>
-    <t>delta_usdjpy</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>A rise in delta_usdjpy is a headwind for next-quarter VN-Index returns (weakly significant, p=0.059).</t>
-  </si>
-  <si>
-    <t>usd_vnd_pct_change</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>A rise in usd_vnd_pct_change is a headwind for next-quarter VN-Index returns (not significant, p=0.749).</t>
-  </si>
-  <si>
-    <t>rsi_14</t>
-  </si>
-  <si>
-    <t>A rise in rsi_14 is supportive of next-quarter VN-Index returns (statistically significant, p=0.022).</t>
-  </si>
-  <si>
-    <t>macd_hist</t>
-  </si>
-  <si>
-    <t>A rise in macd_hist is a headwind for next-quarter VN-Index returns (not significant, p=0.236).</t>
-  </si>
-  <si>
-    <t>bb_pct</t>
-  </si>
-  <si>
-    <t>A rise in bb_pct is a headwind for next-quarter VN-Index returns (not significant, p=0.880).</t>
-  </si>
-  <si>
-    <t>rvol_20d</t>
-  </si>
-  <si>
-    <t>A rise in rvol_20d is a headwind for next-quarter VN-Index returns (not significant, p=0.378).</t>
-  </si>
-  <si>
-    <t>drawdown_from_peak</t>
-  </si>
-  <si>
-    <t>***</t>
-  </si>
-  <si>
-    <t>A rise in drawdown_from_peak is a headwind for next-quarter VN-Index returns (statistically significant, p=0.001).</t>
-  </si>
-  <si>
-    <t>price_vs_ma200</t>
-  </si>
-  <si>
-    <t>A rise in price_vs_ma200 is supportive of next-quarter VN-Index returns (weakly significant, p=0.089).</t>
-  </si>
-  <si>
-    <t>log_return_lag1</t>
-  </si>
-  <si>
-    <t>A rise in log_return_lag1 is a headwind for next-quarter VN-Index returns (not significant, p=0.228).</t>
-  </si>
-  <si>
-    <t>log_return_lag5</t>
-  </si>
-  <si>
-    <t>A rise in log_return_lag5 is a headwind for next-quarter VN-Index returns (not significant, p=0.863).</t>
-  </si>
-  <si>
-    <t>Sign-check pass rate:</t>
-  </si>
-  <si>
-    <t>1/12 (8%)</t>
-  </si>
-  <si>
-    <t>BETA STABILITY ACROSS QUARTERS (sign consistency = % quarters with same sign as latest)</t>
-  </si>
-  <si>
-    <t>Sign Consistency</t>
-  </si>
-  <si>
-    <t>VAR GRANGER CAUSALITY — WHICH FACTORS LEAD THE VN-INDEX?</t>
-  </si>
-  <si>
-    <t>H0: factor does NOT Granger-cause VNI returns. p &lt; 0.05 → reject H0 → factor has leading power.</t>
-  </si>
-  <si>
-    <t>F-Statistic</t>
-  </si>
-  <si>
-    <t>Granger-causes VNI?</t>
-  </si>
-  <si>
-    <t>Verdict</t>
-  </si>
-  <si>
-    <t>YES — LEADING</t>
-  </si>
-  <si>
-    <t>delta_dxy contains predictive information for future VN-Index returns.</t>
-  </si>
-  <si>
-    <t>delta_vn1y_yield</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>No statistical evidence that delta_vn1y_yield leads VN-Index returns.</t>
-  </si>
-  <si>
-    <t>pe_zscore</t>
-  </si>
-  <si>
-    <t>No statistical evidence that pe_zscore leads VN-Index returns.</t>
-  </si>
-  <si>
-    <t>No statistical evidence that delta_us10y leads VN-Index returns.</t>
-  </si>
-  <si>
-    <t>No statistical evidence that delta_usdjpy leads VN-Index returns.</t>
-  </si>
-  <si>
-    <t>MACHINE LEARNING — WALK-FORWARD VALIDATION (no look-ahead bias)</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>xgboost</t>
-  </si>
-  <si>
-    <t>Folds</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Features</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>Mean Accuracy</t>
-  </si>
-  <si>
-    <t>Std Accuracy</t>
-  </si>
-  <si>
-    <t>Mean F1 (weighted)</t>
-  </si>
-  <si>
-    <t>Latest Prediction</t>
-  </si>
-  <si>
-    <t>DOWN</t>
-  </si>
-  <si>
-    <t>Prediction Confidence</t>
-  </si>
-  <si>
-    <t>WALK-FORWARD FOLD METRICS (expanding window)</t>
-  </si>
-  <si>
-    <t>Fold</t>
-  </si>
-  <si>
-    <t>Train Size</t>
-  </si>
-  <si>
-    <t>Test Size</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>F1 (weighted)</t>
-  </si>
-  <si>
-    <t>Precision</t>
-  </si>
-  <si>
-    <t>TOP FEATURE IMPORTANCE (model-implied factor relevance)</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Feature</t>
-  </si>
-  <si>
-    <t>Importance</t>
-  </si>
-  <si>
-    <t>ema_20</t>
-  </si>
-  <si>
-    <t>macd_line</t>
-  </si>
-  <si>
-    <t>etf_flow_q_zscore</t>
-  </si>
-  <si>
-    <t>bb_mid</t>
-  </si>
-  <si>
-    <t>us10y_30d_change</t>
-  </si>
-  <si>
-    <t>usd_vnd_zscore_lag1</t>
-  </si>
-  <si>
-    <t>us10y_zscore_1y</t>
-  </si>
-  <si>
-    <t>oil_n_shock_days_ytd</t>
-  </si>
-  <si>
-    <t>etf_flow_q_zscore_live</t>
-  </si>
-  <si>
-    <t>dxy_zscore_60d</t>
-  </si>
-  <si>
-    <t>bb_lower</t>
-  </si>
-  <si>
-    <t>ex_vingroup_pe</t>
-  </si>
-  <si>
-    <t>nff_ex_etf_q_ytd</t>
-  </si>
-  <si>
-    <t>nff_ex_etf_rolling60d</t>
-  </si>
-  <si>
-    <t>rvol_10d</t>
-  </si>
-  <si>
-    <t>FACTOR-LEVEL SCORE DECOMPOSITION — 2026-Q4</t>
-  </si>
-  <si>
-    <t>Every indicator inside each pillar with its parsed 0-100 score. &lt;MISSING&gt; indicators fall back to neutral 50.</t>
-  </si>
-  <si>
-    <t>Pillar Weight</t>
-  </si>
-  <si>
-    <t>Indicator</t>
-  </si>
-  <si>
-    <t>Observed Value / Analysis</t>
-  </si>
-  <si>
-    <t>Score (0-100)</t>
-  </si>
-  <si>
-    <t>Data Status</t>
-  </si>
-  <si>
-    <t>vn1y_yield</t>
-  </si>
-  <si>
-    <t>3.86%</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>ir_trend</t>
-  </si>
-  <si>
-    <t>Δ VN1Y = 0.0044 (→ Hold)</t>
-  </si>
-  <si>
-    <t>usd_vnd</t>
-  </si>
-  <si>
-    <t>Z-score = -1.27</t>
-  </si>
-  <si>
-    <t>m2_yoy_growth</t>
-  </si>
-  <si>
-    <t>MISSING</t>
-  </si>
-  <si>
-    <t>vn_bonds</t>
-  </si>
-  <si>
-    <t>VN10Y 4.48% | Spread 0.53%</t>
-  </si>
-  <si>
-    <t>dxy</t>
-  </si>
-  <si>
-    <t>Z = 1.05</t>
-  </si>
-  <si>
-    <t>us10y</t>
-  </si>
-  <si>
-    <t>5.18%</t>
-  </si>
-  <si>
-    <t>nff_ex_etf</t>
-  </si>
-  <si>
-    <t>Z = 0.21 (Neutral)</t>
-  </si>
-  <si>
-    <t>-0.16% of Market Cap (YTD in Q)</t>
-  </si>
-  <si>
-    <t>jpy_carry</t>
-  </si>
-  <si>
-    <t>Z = -0.16 (Neutral)</t>
-  </si>
-  <si>
-    <t>oil_shock</t>
-  </si>
-  <si>
-    <t>Oil Shock Score = 43.8 (Max Δ5d = 19.5%)</t>
-  </si>
-  <si>
-    <t>P/E Headline: 12.46 | Median: 10.25 | Ex-VG: 10.03 | Z = 0.81 (FAIR VALUE)</t>
-  </si>
-  <si>
-    <t>pb_zscore</t>
-  </si>
-  <si>
-    <t>Z = 0.68 (FAIR VALUE)</t>
-  </si>
-  <si>
-    <t>margin_risk</t>
-  </si>
-  <si>
-    <t>Risk = 20/100 (SAFE)</t>
-  </si>
-  <si>
-    <t>mlr_forecast</t>
-  </si>
-  <si>
-    <t>Forward log-return/day (next ~1M) = -0.0006</t>
-  </si>
-  <si>
-    <t>var_forecast</t>
-  </si>
-  <si>
-    <t>VAR T+5 return = 0.0011</t>
-  </si>
-  <si>
-    <t>mlr_adj_r2</t>
-  </si>
-  <si>
-    <t>Adj-R² = 0.1092 → confidence bonus 1.1</t>
-  </si>
-  <si>
-    <t>granger_leaders</t>
-  </si>
-  <si>
-    <t>1 vars Granger-cause VNI (p&lt;5%)</t>
-  </si>
-  <si>
-    <t>model_quality</t>
-  </si>
-  <si>
-    <t>Accuracy=42.5% F1=0.369 → quality 40</t>
-  </si>
-  <si>
-    <t>ml_signal</t>
-  </si>
-  <si>
-    <t>Forecast: DOWN (conf=50%)</t>
-  </si>
-  <si>
-    <t>ftse_upgrade</t>
-  </si>
-  <si>
-    <t>Status: confirmed</t>
-  </si>
-  <si>
-    <t>rebalancing</t>
-  </si>
-  <si>
-    <t>0 months to rebalancing → bonus +20</t>
-  </si>
-  <si>
-    <t>adtv</t>
-  </si>
-  <si>
-    <t>ADTV data unavailable → neutral score 50</t>
-  </si>
-  <si>
-    <t>etf_flow</t>
-  </si>
-  <si>
-    <t>Z = -0.21 (Neutral)</t>
-  </si>
-  <si>
-    <t>etf_flow_q_ytd</t>
-  </si>
-  <si>
-    <t>0.00% of Market Cap (YTD in Q)</t>
-  </si>
-  <si>
-    <t>SIGNAL EFFICACY — DOES THE SCORE PREDICT NEXT-QUARTER RETURNS?</t>
-  </si>
-  <si>
-    <t>Score at quarter t is evaluated against the VN-Index return over quarter t+1 (point-in-time, no look-ahead).</t>
-  </si>
-  <si>
-    <t>Quarters evaluated (N)</t>
-  </si>
-  <si>
-    <t>Information Coefficient (Pearson)</t>
-  </si>
-  <si>
-    <t>Information Coefficient (Spearman)</t>
-  </si>
-  <si>
-    <t>Directional Hit Rate (score≥50 → up)</t>
-  </si>
-  <si>
-    <t>Strategy total return (score-scaled)</t>
-  </si>
-  <si>
-    <t>Buy &amp; Hold total return</t>
-  </si>
-  <si>
-    <t>Strategy Sharpe (annualised, rf=0)</t>
-  </si>
-  <si>
-    <t>Buy &amp; Hold Sharpe (annualised, rf=0)</t>
-  </si>
-  <si>
-    <t>FORWARD RETURN BY REGIME BUCKET</t>
-  </si>
-  <si>
-    <t>Regime (Label)</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Avg Fwd Return</t>
-  </si>
-  <si>
-    <t>Median Fwd Return</t>
-  </si>
-  <si>
-    <t>Win Rate (fwd&gt;0)</t>
-  </si>
-  <si>
-    <t>QUARTER-BY-QUARTER SIGNAL LEDGER</t>
-  </si>
-  <si>
-    <t>Score (t)</t>
-  </si>
-  <si>
-    <t>Label (t)</t>
-  </si>
-  <si>
-    <t>Equity Allocation</t>
-  </si>
-  <si>
-    <t>Strategy Return</t>
-  </si>
-  <si>
-    <t>Hit?</t>
-  </si>
-  <si>
-    <t>Strategy Index</t>
-  </si>
-  <si>
-    <t>Buy&amp;Hold Index</t>
-  </si>
-  <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>✗</t>
-  </si>
-  <si>
-    <t>Note: strategy holds the mid-point of the recommended equity band (e.g. HOLD = 50%) for the following quarter; residual cash earns 0%. Gross of fees/slippage. Quarterly Sharpe annualised with √4.</t>
-  </si>
-  <si>
-    <t>METHODOLOGY — WEIGHTS, REGIME BANDS &amp; DATA SOURCES</t>
-  </si>
-  <si>
-    <t>REGIME BANDS (config.py SCORE_LABELS — single source of truth)</t>
-  </si>
-  <si>
-    <t>Score Range</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>80–100</t>
-  </si>
-  <si>
-    <t>🟢 BUY</t>
-  </si>
-  <si>
-    <t>Highly favorable environment — Increase exposure aggressively</t>
-  </si>
-  <si>
-    <t>85–100% Equities</t>
-  </si>
-  <si>
-    <t>65–79</t>
-  </si>
-  <si>
-    <t>🔵 ACCUMULATE</t>
-  </si>
-  <si>
-    <t>Gradually accumulate — Controllable risks</t>
-  </si>
-  <si>
-    <t>70–85% Equities</t>
-  </si>
-  <si>
-    <t>50–64</t>
-  </si>
-  <si>
-    <t>Neutral — Await confirming signals</t>
-  </si>
-  <si>
     <t>35–49</t>
   </si>
   <si>
@@ -872,13 +914,19 @@
     <t>ML (XGBoost/RandomForest): trend classification with expanding-window Walk-Forward Validation (no look-ahead).</t>
   </si>
   <si>
-    <t>Composite score: 6 pillar raw scores (0-100) × fixed weights; labels/allocations from config.py SCORE_LABELS.</t>
+    <t>Composite score (TIER 1 - raw): 6 pillar raw scores (0-100) × fixed weights; labels/allocations from config.py SCORE_LABELS. Kept unchanged as the reference layer.</t>
+  </si>
+  <si>
+    <t>Calibrated Action Signal (TIER 2): calibrated = clip(center + z_scale × (raw − μ_hist)/σ_hist, 0, 100) where μ/σ come from PRIOR quarters only (expanding window, point-in-time, no look-ahead); parameters in config.py SCORE_CALIBRATION. First 4 quarters (or σ≈0) keep the raw score. Raw composite is never overwritten.</t>
+  </si>
+  <si>
+    <t>Anti-compression at source: MLR signal gain 20000 (±0.10%/day → 70/30), VAR gain 5000; missing MLR/VAR/ADTV/ETF signals are excluded from pillar averages (renormalized over live signals) instead of defaulting to neutral 50.</t>
   </si>
   <si>
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 08:42:47 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 10:09:07 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1305,7 +1353,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-              <a:t>Composite Score (LHS) vs VN-Index (RHS)</a:t>
+              <a:t>Calibrated Action (solid) + Raw Composite (dashed) vs VN-Index (RHS)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1320,12 +1368,12 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Composite Score</c:v>
+            <c:v>Calibrated Action Score</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="31750">
               <a:solidFill>
-                <a:srgbClr val="3B82F6"/>
+                <a:srgbClr val="8B5CF6"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1414,6 +1462,185 @@
           </c:cat>
           <c:val>
             <c:numRef>
+              <c:f>'01_Score_History'!$E$6:$E$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>61.41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52.98</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54.28</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.83</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>63.34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>39.08</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17.89</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>50.11</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>61.36</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>66.93000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>43.88</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45.97</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>54.51</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>50.47</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>36.51</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>49.08</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>36.71</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44.52</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>14.27</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>40.03</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>35.27</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Raw Composite Score</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="3B82F6"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'01_Score_History'!$B$6:$B$29</c:f>
+              <c:strCache>
+                <c:ptCount val="24"/>
+                <c:pt idx="0">
+                  <c:v>2021-Q1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2021-Q2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2021-Q3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021-Q4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022-Q1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2022-Q2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2022-Q3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2022-Q4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-Q1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-Q2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-Q3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-Q4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2024-Q1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2024-Q2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2024-Q3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2024-Q4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2025-Q1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2025-Q2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2025-Q3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2025-Q4</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2026-Q1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2026-Q2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2026-Q3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2026-Q4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
               <c:f>'01_Score_History'!$C$6:$C$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
@@ -1485,7 +1712,7 @@
                   <c:v>45.8</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>52.77999999999999</c:v>
+                  <c:v>50.96999999999999</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>49.73999999999999</c:v>
@@ -1501,8 +1728,8 @@
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="2"/>
+          <c:order val="2"/>
           <c:tx>
             <c:v>VN-Index Close</c:v>
           </c:tx>
@@ -1599,7 +1826,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'01_Score_History'!$M$6:$M$29</c:f>
+              <c:f>'01_Score_History'!$O$6:$O$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -2389,7 +2616,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-              <a:t>Cumulative Growth: Score-Scaled Allocation vs Buy &amp; Hold</a:t>
+              <a:t>Cumulative Growth: Calibrated-Signal Allocation vs Buy &amp; Hold</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2404,12 +2631,12 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Score-Scaled Strategy (base=100)</c:v>
+            <c:v>Calibrated-Signal Strategy (base=100)</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="31750">
               <a:solidFill>
-                <a:srgbClr val="3B82F6"/>
+                <a:srgbClr val="8B5CF6"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -2418,7 +2645,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'06_Signal_Efficacy'!$B$21:$B$42</c:f>
+              <c:f>'06_Signal_Efficacy'!$B$27:$B$48</c:f>
               <c:strCache>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
@@ -2492,7 +2719,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'06_Signal_Efficacy'!$I$21:$I$42</c:f>
+              <c:f>'06_Signal_Efficacy'!$K$27:$K$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
@@ -2512,55 +2739,55 @@
                   <c:v>101.4015891843619</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>98.62904823760013</c:v>
+                  <c:v>100.8470809950096</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93.18319774132999</c:v>
+                  <c:v>97.50608884778109</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>94.78067950463225</c:v>
+                  <c:v>98.06328586226736</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>97.25293253837476</c:v>
+                  <c:v>100.6211621851513</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>98.72755363423819</c:v>
+                  <c:v>102.1468548771426</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>97.69164783818862</c:v>
+                  <c:v>100.4855911423842</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>104.3558413859018</c:v>
+                  <c:v>104.5984632841567</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>102.7804549369257</c:v>
+                  <c:v>103.6510337998853</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>104.5392410278147</c:v>
+                  <c:v>105.4247172951119</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>103.6804858295335</c:v>
+                  <c:v>104.5586882029319</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>105.3206734990767</c:v>
+                  <c:v>106.2127687154019</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>108.1095123237675</c:v>
+                  <c:v>107.9002453516429</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>119.3296246745338</c:v>
+                  <c:v>114.6192815372562</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>123.7385085325665</c:v>
+                  <c:v>118.8541318652214</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>119.9247477553746</c:v>
+                  <c:v>116.6562006066813</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>126.5680956414704</c:v>
+                  <c:v>120.5335707318928</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>125.0390796098018</c:v>
+                  <c:v>120.0481989087403</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2585,7 +2812,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'06_Signal_Efficacy'!$B$21:$B$42</c:f>
+              <c:f>'06_Signal_Efficacy'!$B$27:$B$48</c:f>
               <c:strCache>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
@@ -2659,7 +2886,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'06_Signal_Efficacy'!$J$21:$J$42</c:f>
+              <c:f>'06_Signal_Efficacy'!$L$27:$L$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
@@ -2824,7 +3051,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:colOff>790575</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2954,13 +3181,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>60</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3350,34 +3577,42 @@
         <v>14</v>
       </c>
     </row>
+    <row r="11" spans="2:7">
+      <c r="E11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="12" spans="2:7">
       <c r="B12" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="9">
         <v>0.25</v>
@@ -3392,12 +3627,12 @@
         <v>0.2730197024527543</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="9">
         <v>0.2</v>
@@ -3412,12 +3647,12 @@
         <v>0.149577804583836</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="9">
         <v>0.2</v>
@@ -3432,12 +3667,12 @@
         <v>0.2312022517088862</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="9">
         <v>0.15</v>
@@ -3452,12 +3687,12 @@
         <v>0.1656614394853237</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="9">
         <v>0.1</v>
@@ -3472,12 +3707,12 @@
         <v>0.05207076799356654</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="2:7">
       <c r="B19" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" s="9">
         <v>0.1</v>
@@ -3492,12 +3727,12 @@
         <v>0.1284680337756333</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="9">
         <v>1</v>
@@ -3510,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -3539,57 +3774,60 @@
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
-  <dimension ref="B2:O29"/>
+  <dimension ref="B2:Q29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="12" width="19.7109375" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="14" width="19.7109375" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" customWidth="1"/>
+    <col min="17" max="17" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15">
+    <row r="2" spans="2:17">
       <c r="B2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="2:15">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
       <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
       <c r="B5" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>28</v>
@@ -3598,1069 +3836,1219 @@
         <v>29</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15">
+        <v>42</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
       <c r="B6" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C6" s="10">
         <v>61.41</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E6" s="10">
+        <v>61.41</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="10">
+        <v>33</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="10">
         <v>14.51</v>
       </c>
-      <c r="H6" s="10">
+      <c r="J6" s="10">
         <v>12.64</v>
       </c>
-      <c r="I6" s="10">
+      <c r="K6" s="10">
         <v>12.5</v>
       </c>
-      <c r="J6" s="10">
+      <c r="L6" s="10">
         <v>8.039999999999999</v>
       </c>
-      <c r="K6" s="10">
+      <c r="M6" s="10">
         <v>8.52</v>
       </c>
-      <c r="L6" s="10">
+      <c r="N6" s="10">
         <v>5.2</v>
       </c>
-      <c r="M6" s="10">
+      <c r="O6" s="10">
         <v>1191.44</v>
       </c>
-      <c r="N6" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" s="11">
+      <c r="P6" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" s="11">
         <v>0.182224870744645</v>
       </c>
     </row>
-    <row r="7" spans="2:15">
+    <row r="7" spans="2:17">
       <c r="B7" s="14" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C7" s="10">
         <v>52.98</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E7" s="10">
+        <v>52.98</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="10">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="10">
         <v>12.05</v>
       </c>
-      <c r="H7" s="10">
+      <c r="J7" s="10">
         <v>11.06</v>
       </c>
-      <c r="I7" s="10">
+      <c r="K7" s="10">
         <v>12.32</v>
       </c>
-      <c r="J7" s="10">
+      <c r="L7" s="10">
         <v>8.460000000000001</v>
       </c>
-      <c r="K7" s="10">
+      <c r="M7" s="10">
         <v>3.89</v>
       </c>
-      <c r="L7" s="10">
+      <c r="N7" s="10">
         <v>5.2</v>
       </c>
-      <c r="M7" s="10">
+      <c r="O7" s="10">
         <v>1408.55</v>
       </c>
-      <c r="N7" s="11">
+      <c r="P7" s="11">
         <v>0.182224870744645</v>
       </c>
-      <c r="O7" s="11">
+      <c r="Q7" s="11">
         <v>-0.04720457207766848</v>
       </c>
     </row>
-    <row r="8" spans="2:15">
+    <row r="8" spans="2:17">
       <c r="B8" s="14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" s="10">
         <v>54.28</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E8" s="10">
+        <v>54.28</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="10">
+        <v>33</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="10">
         <v>12.37</v>
       </c>
-      <c r="H8" s="10">
+      <c r="J8" s="10">
         <v>11.69</v>
       </c>
-      <c r="I8" s="10">
+      <c r="K8" s="10">
         <v>12.48</v>
       </c>
-      <c r="J8" s="10">
+      <c r="L8" s="10">
         <v>9.289999999999999</v>
       </c>
-      <c r="K8" s="10">
+      <c r="M8" s="10">
         <v>3.25</v>
       </c>
-      <c r="L8" s="10">
+      <c r="N8" s="10">
         <v>5.2</v>
       </c>
-      <c r="M8" s="10">
+      <c r="O8" s="10">
         <v>1342.06</v>
       </c>
-      <c r="N8" s="11">
+      <c r="P8" s="11">
         <v>-0.04720457207766848</v>
       </c>
-      <c r="O8" s="11">
+      <c r="Q8" s="11">
         <v>0.1164031414392799</v>
       </c>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:17">
       <c r="B9" s="14" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C9" s="10">
         <v>52.83</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E9" s="10">
+        <v>52.83</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="10">
+        <v>33</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="10">
         <v>12.99</v>
       </c>
-      <c r="H9" s="10">
+      <c r="J9" s="10">
         <v>11.9</v>
       </c>
-      <c r="I9" s="10">
+      <c r="K9" s="10">
         <v>11.76</v>
       </c>
-      <c r="J9" s="10">
+      <c r="L9" s="10">
         <v>7.94</v>
       </c>
-      <c r="K9" s="10">
+      <c r="M9" s="10">
         <v>3.04</v>
       </c>
-      <c r="L9" s="10">
+      <c r="N9" s="10">
         <v>5.2</v>
       </c>
-      <c r="M9" s="10">
+      <c r="O9" s="10">
         <v>1498.28</v>
       </c>
-      <c r="N9" s="11">
+      <c r="P9" s="11">
         <v>0.1164031414392799</v>
       </c>
-      <c r="O9" s="11">
+      <c r="Q9" s="11">
         <v>-0.004091358090610453</v>
       </c>
     </row>
-    <row r="10" spans="2:15">
+    <row r="10" spans="2:17">
       <c r="B10" s="14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" s="10">
         <v>59</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="E10" s="10">
+        <v>63.34</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="10">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="10">
         <v>12.54</v>
       </c>
-      <c r="H10" s="10">
+      <c r="J10" s="10">
         <v>12.85</v>
       </c>
-      <c r="I10" s="10">
+      <c r="K10" s="10">
         <v>12.46</v>
       </c>
-      <c r="J10" s="10">
+      <c r="L10" s="10">
         <v>8.039999999999999</v>
       </c>
-      <c r="K10" s="10">
+      <c r="M10" s="10">
         <v>7.91</v>
       </c>
-      <c r="L10" s="10">
+      <c r="N10" s="10">
         <v>5.2</v>
       </c>
-      <c r="M10" s="10">
+      <c r="O10" s="10">
         <v>1492.15</v>
       </c>
-      <c r="N10" s="11">
+      <c r="P10" s="11">
         <v>-0.004091358090610453</v>
       </c>
-      <c r="O10" s="11">
+      <c r="Q10" s="11">
         <v>-0.197399725228697</v>
       </c>
     </row>
-    <row r="11" spans="2:15">
+    <row r="11" spans="2:17">
       <c r="B11" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C11" s="10">
         <v>50.26000000000001</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="E11" s="10">
+        <v>27.45</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="10">
+        <v>54</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="10">
         <v>11.73</v>
       </c>
-      <c r="H11" s="10">
+      <c r="J11" s="10">
         <v>11.22</v>
       </c>
-      <c r="I11" s="10">
+      <c r="K11" s="10">
         <v>11.97</v>
       </c>
-      <c r="J11" s="10">
+      <c r="L11" s="10">
         <v>7.71</v>
       </c>
-      <c r="K11" s="10">
+      <c r="M11" s="10">
         <v>2.68</v>
       </c>
-      <c r="L11" s="10">
+      <c r="N11" s="10">
         <v>4.95</v>
       </c>
-      <c r="M11" s="10">
+      <c r="O11" s="10">
         <v>1197.6</v>
       </c>
-      <c r="N11" s="11">
+      <c r="P11" s="11">
         <v>-0.197399725228697</v>
       </c>
-      <c r="O11" s="11">
+      <c r="Q11" s="11">
         <v>-0.05468436873747495</v>
       </c>
     </row>
-    <row r="12" spans="2:15">
+    <row r="12" spans="2:17">
       <c r="B12" s="14" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C12" s="10">
         <v>52.06</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="E12" s="10">
+        <v>39.08</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="10">
+        <v>57</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="10">
         <v>11.49</v>
       </c>
-      <c r="H12" s="10">
+      <c r="J12" s="10">
         <v>11.23</v>
       </c>
-      <c r="I12" s="10">
+      <c r="K12" s="10">
         <v>8.5</v>
       </c>
-      <c r="J12" s="10">
+      <c r="L12" s="10">
         <v>8.779999999999999</v>
       </c>
-      <c r="K12" s="10">
+      <c r="M12" s="10">
         <v>7.08</v>
       </c>
-      <c r="L12" s="10">
+      <c r="N12" s="10">
         <v>4.98</v>
       </c>
-      <c r="M12" s="10">
+      <c r="O12" s="10">
         <v>1132.11</v>
       </c>
-      <c r="N12" s="11">
+      <c r="P12" s="11">
         <v>-0.05468436873747495</v>
       </c>
-      <c r="O12" s="11">
+      <c r="Q12" s="11">
         <v>-0.1104309651888949</v>
       </c>
     </row>
-    <row r="13" spans="2:15">
+    <row r="13" spans="2:17">
       <c r="B13" s="14" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C13" s="10">
         <v>46.09</v>
       </c>
       <c r="D13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="10">
+        <v>17.89</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="10">
+      <c r="G13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="10">
         <v>9.34</v>
       </c>
-      <c r="H13" s="10">
+      <c r="J13" s="10">
         <v>10.07</v>
       </c>
-      <c r="I13" s="10">
+      <c r="K13" s="10">
         <v>9.800000000000001</v>
       </c>
-      <c r="J13" s="10">
+      <c r="L13" s="10">
         <v>8.220000000000001</v>
       </c>
-      <c r="K13" s="10">
+      <c r="M13" s="10">
         <v>3.67</v>
       </c>
-      <c r="L13" s="10">
+      <c r="N13" s="10">
         <v>4.99</v>
       </c>
-      <c r="M13" s="10">
+      <c r="O13" s="10">
         <v>1007.09</v>
       </c>
-      <c r="N13" s="11">
+      <c r="P13" s="11">
         <v>-0.1104309651888949</v>
       </c>
-      <c r="O13" s="11">
+      <c r="Q13" s="11">
         <v>0.05714484306268552</v>
       </c>
     </row>
-    <row r="14" spans="2:15">
+    <row r="14" spans="2:17">
       <c r="B14" s="14" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C14" s="10">
         <v>53.65000000000001</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E14" s="10">
+        <v>50.11</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="10">
+        <v>33</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="10">
         <v>12.48</v>
       </c>
-      <c r="H14" s="10">
+      <c r="J14" s="10">
         <v>10.41</v>
       </c>
-      <c r="I14" s="10">
+      <c r="K14" s="10">
         <v>10.74</v>
       </c>
-      <c r="J14" s="10">
+      <c r="L14" s="10">
         <v>8.31</v>
       </c>
-      <c r="K14" s="10">
+      <c r="M14" s="10">
         <v>6.7</v>
       </c>
-      <c r="L14" s="10">
+      <c r="N14" s="10">
         <v>5.01</v>
       </c>
-      <c r="M14" s="10">
+      <c r="O14" s="10">
         <v>1064.64</v>
       </c>
-      <c r="N14" s="11">
+      <c r="P14" s="11">
         <v>0.05714484306268552</v>
       </c>
-      <c r="O14" s="11">
+      <c r="Q14" s="11">
         <v>0.05216786895100678</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:17">
       <c r="B15" s="14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="10">
         <v>57.02</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E15" s="10">
+        <v>61.36</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="10">
+        <v>33</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="10">
         <v>14</v>
       </c>
-      <c r="H15" s="10">
+      <c r="J15" s="10">
         <v>11.49</v>
       </c>
-      <c r="I15" s="10">
+      <c r="K15" s="10">
         <v>11.46</v>
       </c>
-      <c r="J15" s="10">
+      <c r="L15" s="10">
         <v>8.19</v>
       </c>
-      <c r="K15" s="10">
+      <c r="M15" s="10">
         <v>6.86</v>
       </c>
-      <c r="L15" s="10">
+      <c r="N15" s="10">
         <v>5.02</v>
       </c>
-      <c r="M15" s="10">
+      <c r="O15" s="10">
         <v>1120.18</v>
       </c>
-      <c r="N15" s="11">
+      <c r="P15" s="11">
         <v>0.05216786895100678</v>
       </c>
-      <c r="O15" s="11">
+      <c r="Q15" s="11">
         <v>0.03032548340445285</v>
       </c>
     </row>
-    <row r="16" spans="2:15">
+    <row r="16" spans="2:17">
       <c r="B16" s="14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="10">
         <v>58.89</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>48</v>
+        <v>33</v>
+      </c>
+      <c r="E16" s="10">
+        <v>66.93000000000001</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="10">
+        <v>63</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="10">
         <v>12.77</v>
       </c>
-      <c r="H16" s="10">
+      <c r="J16" s="10">
         <v>11.45</v>
       </c>
-      <c r="I16" s="10">
+      <c r="K16" s="10">
         <v>14.5</v>
       </c>
-      <c r="J16" s="10">
+      <c r="L16" s="10">
         <v>8.369999999999999</v>
       </c>
-      <c r="K16" s="10">
+      <c r="M16" s="10">
         <v>6.77</v>
       </c>
-      <c r="L16" s="10">
+      <c r="N16" s="10">
         <v>5.03</v>
       </c>
-      <c r="M16" s="10">
+      <c r="O16" s="10">
         <v>1154.15</v>
       </c>
-      <c r="N16" s="11">
+      <c r="P16" s="11">
         <v>0.03032548340445285</v>
       </c>
-      <c r="O16" s="11">
+      <c r="Q16" s="11">
         <v>-0.0209851405796474</v>
       </c>
     </row>
-    <row r="17" spans="2:15">
+    <row r="17" spans="2:17">
       <c r="B17" s="14" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C17" s="10">
         <v>52.60999999999999</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E17" s="10">
+        <v>43.88</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="10">
+        <v>57</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="10">
         <v>13.95</v>
       </c>
-      <c r="H17" s="10">
+      <c r="J17" s="10">
         <v>9.630000000000001</v>
       </c>
-      <c r="I17" s="10">
+      <c r="K17" s="10">
         <v>12.4</v>
       </c>
-      <c r="J17" s="10">
+      <c r="L17" s="10">
         <v>8.23</v>
       </c>
-      <c r="K17" s="10">
+      <c r="M17" s="10">
         <v>3.36</v>
       </c>
-      <c r="L17" s="10">
+      <c r="N17" s="10">
         <v>5.04</v>
       </c>
-      <c r="M17" s="10">
+      <c r="O17" s="10">
         <v>1129.93</v>
       </c>
-      <c r="N17" s="11">
+      <c r="P17" s="11">
         <v>-0.0209851405796474</v>
       </c>
-      <c r="O17" s="11">
+      <c r="Q17" s="11">
         <v>0.136433230377103</v>
       </c>
     </row>
-    <row r="18" spans="2:15">
+    <row r="18" spans="2:17">
       <c r="B18" s="14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C18" s="10">
         <v>53.12</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E18" s="10">
+        <v>45.97</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="10">
+        <v>57</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="10">
         <v>16.31</v>
       </c>
-      <c r="H18" s="10">
+      <c r="J18" s="10">
         <v>4</v>
       </c>
-      <c r="I18" s="10">
+      <c r="K18" s="10">
         <v>12.94</v>
       </c>
-      <c r="J18" s="10">
+      <c r="L18" s="10">
         <v>8.06</v>
       </c>
-      <c r="K18" s="10">
+      <c r="M18" s="10">
         <v>6.76</v>
       </c>
-      <c r="L18" s="10">
+      <c r="N18" s="10">
         <v>5.05</v>
       </c>
-      <c r="M18" s="10">
+      <c r="O18" s="10">
         <v>1284.09</v>
       </c>
-      <c r="N18" s="11">
+      <c r="P18" s="11">
         <v>0.136433230377103</v>
       </c>
-      <c r="O18" s="11">
+      <c r="Q18" s="11">
         <v>-0.03019258774696476</v>
       </c>
     </row>
-    <row r="19" spans="2:15">
+    <row r="19" spans="2:17">
       <c r="B19" s="14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C19" s="10">
         <v>55.39</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E19" s="10">
+        <v>54.51</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="10">
+        <v>33</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="10">
         <v>14.83</v>
       </c>
-      <c r="H19" s="10">
+      <c r="J19" s="10">
         <v>10.05</v>
       </c>
-      <c r="I19" s="10">
+      <c r="K19" s="10">
         <v>10.29</v>
       </c>
-      <c r="J19" s="10">
+      <c r="L19" s="10">
         <v>8.210000000000001</v>
       </c>
-      <c r="K19" s="10">
+      <c r="M19" s="10">
         <v>6.96</v>
       </c>
-      <c r="L19" s="10">
+      <c r="N19" s="10">
         <v>5.05</v>
       </c>
-      <c r="M19" s="10">
+      <c r="O19" s="10">
         <v>1245.32</v>
       </c>
-      <c r="N19" s="11">
+      <c r="P19" s="11">
         <v>-0.03019258774696476</v>
       </c>
-      <c r="O19" s="11">
+      <c r="Q19" s="11">
         <v>0.0342241351620467</v>
       </c>
     </row>
-    <row r="20" spans="2:15">
+    <row r="20" spans="2:17">
       <c r="B20" s="14" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C20" s="10">
         <v>54.38000000000001</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E20" s="10">
+        <v>50.47</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" s="10">
+        <v>33</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="10">
         <v>14.55</v>
       </c>
-      <c r="H20" s="10">
+      <c r="J20" s="10">
         <v>10.86</v>
       </c>
-      <c r="I20" s="10">
+      <c r="K20" s="10">
         <v>8.470000000000001</v>
       </c>
-      <c r="J20" s="10">
+      <c r="L20" s="10">
         <v>7.91</v>
       </c>
-      <c r="K20" s="10">
+      <c r="M20" s="10">
         <v>7.53</v>
       </c>
-      <c r="L20" s="10">
+      <c r="N20" s="10">
         <v>5.06</v>
       </c>
-      <c r="M20" s="10">
+      <c r="O20" s="10">
         <v>1287.94</v>
       </c>
-      <c r="N20" s="11">
+      <c r="P20" s="11">
         <v>0.0342241351620467</v>
       </c>
-      <c r="O20" s="11">
+      <c r="Q20" s="11">
         <v>-0.01642933677034653</v>
       </c>
     </row>
-    <row r="21" spans="2:15">
+    <row r="21" spans="2:17">
       <c r="B21" s="14" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C21" s="10">
         <v>55.02</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E21" s="10">
+        <v>53</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" s="10">
+        <v>33</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="10">
         <v>16.84</v>
       </c>
-      <c r="H21" s="10">
+      <c r="J21" s="10">
         <v>10.9</v>
       </c>
-      <c r="I21" s="10">
+      <c r="K21" s="10">
         <v>9.529999999999999</v>
       </c>
-      <c r="J21" s="10">
+      <c r="L21" s="10">
         <v>7.95</v>
       </c>
-      <c r="K21" s="10">
+      <c r="M21" s="10">
         <v>4.73</v>
       </c>
-      <c r="L21" s="10">
+      <c r="N21" s="10">
         <v>5.07</v>
       </c>
-      <c r="M21" s="10">
+      <c r="O21" s="10">
         <v>1266.78</v>
       </c>
-      <c r="N21" s="11">
+      <c r="P21" s="11">
         <v>-0.01642933677034653</v>
       </c>
-      <c r="O21" s="11">
+      <c r="Q21" s="11">
         <v>0.03163927438071323</v>
       </c>
     </row>
-    <row r="22" spans="2:15">
+    <row r="22" spans="2:17">
       <c r="B22" s="14" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C22" s="10">
         <v>52.17</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="E22" s="10">
+        <v>41.2</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="10">
+        <v>57</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="10">
         <v>14.59</v>
       </c>
-      <c r="H22" s="10">
+      <c r="J22" s="10">
         <v>9.27</v>
       </c>
-      <c r="I22" s="10">
+      <c r="K22" s="10">
         <v>8.31</v>
       </c>
-      <c r="J22" s="10">
+      <c r="L22" s="10">
         <v>7.92</v>
       </c>
-      <c r="K22" s="10">
+      <c r="M22" s="10">
         <v>7.01</v>
       </c>
-      <c r="L22" s="10">
+      <c r="N22" s="10">
         <v>5.07</v>
       </c>
-      <c r="M22" s="10">
+      <c r="O22" s="10">
         <v>1306.86</v>
       </c>
-      <c r="N22" s="11">
+      <c r="P22" s="11">
         <v>0.03163927438071323</v>
       </c>
-      <c r="O22" s="11">
+      <c r="Q22" s="11">
         <v>0.05295900096414319</v>
       </c>
     </row>
-    <row r="23" spans="2:15">
+    <row r="23" spans="2:17">
       <c r="B23" s="14" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C23" s="10">
         <v>50.97000000000001</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="E23" s="10">
+        <v>36.51</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="10">
+        <v>57</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="10">
         <v>14.58</v>
       </c>
-      <c r="H23" s="10">
+      <c r="J23" s="10">
         <v>10.69</v>
       </c>
-      <c r="I23" s="10">
+      <c r="K23" s="10">
         <v>7.97</v>
       </c>
-      <c r="J23" s="10">
+      <c r="L23" s="10">
         <v>7.99</v>
       </c>
-      <c r="K23" s="10">
+      <c r="M23" s="10">
         <v>4.67</v>
       </c>
-      <c r="L23" s="10">
+      <c r="N23" s="10">
         <v>5.07</v>
       </c>
-      <c r="M23" s="10">
+      <c r="O23" s="10">
         <v>1376.07</v>
       </c>
-      <c r="N23" s="11">
+      <c r="P23" s="11">
         <v>0.05295900096414319</v>
       </c>
-      <c r="O23" s="11">
+      <c r="Q23" s="11">
         <v>0.2075693823715363</v>
       </c>
     </row>
-    <row r="24" spans="2:15">
+    <row r="24" spans="2:17">
       <c r="B24" s="14" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C24" s="10">
         <v>53.79000000000001</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E24" s="10">
+        <v>49.08</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="10">
+        <v>33</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="10">
         <v>13.39</v>
       </c>
-      <c r="H24" s="10">
+      <c r="J24" s="10">
         <v>11.38</v>
       </c>
-      <c r="I24" s="10">
+      <c r="K24" s="10">
         <v>8.1</v>
       </c>
-      <c r="J24" s="10">
+      <c r="L24" s="10">
         <v>8.699999999999999</v>
       </c>
-      <c r="K24" s="10">
+      <c r="M24" s="10">
         <v>6.97</v>
       </c>
-      <c r="L24" s="10">
+      <c r="N24" s="10">
         <v>5.25</v>
       </c>
-      <c r="M24" s="10">
+      <c r="O24" s="10">
         <v>1661.7</v>
       </c>
-      <c r="N24" s="11">
+      <c r="P24" s="11">
         <v>0.2075693823715363</v>
       </c>
-      <c r="O24" s="11">
+      <c r="Q24" s="11">
         <v>0.07389420473009567</v>
       </c>
     </row>
-    <row r="25" spans="2:15">
+    <row r="25" spans="2:17">
       <c r="B25" s="14" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C25" s="10">
         <v>50.94</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="E25" s="10">
+        <v>36.71</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="10">
+        <v>57</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="10">
         <v>13.06</v>
       </c>
-      <c r="H25" s="10">
+      <c r="J25" s="10">
         <v>11.33</v>
       </c>
-      <c r="I25" s="10">
+      <c r="K25" s="10">
         <v>5.95</v>
       </c>
-      <c r="J25" s="10">
+      <c r="L25" s="10">
         <v>8.43</v>
       </c>
-      <c r="K25" s="10">
+      <c r="M25" s="10">
         <v>6.92</v>
       </c>
-      <c r="L25" s="10">
+      <c r="N25" s="10">
         <v>5.25</v>
       </c>
-      <c r="M25" s="10">
+      <c r="O25" s="10">
         <v>1784.49</v>
       </c>
-      <c r="N25" s="11">
+      <c r="P25" s="11">
         <v>0.07389420473009567</v>
       </c>
-      <c r="O25" s="11">
+      <c r="Q25" s="11">
         <v>-0.06164226193478251</v>
       </c>
     </row>
-    <row r="26" spans="2:15">
+    <row r="26" spans="2:17">
       <c r="B26" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C26" s="10">
         <v>52.59</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E26" s="10">
+        <v>44.52</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G26" s="10">
+        <v>57</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I26" s="10">
         <v>16.02</v>
       </c>
-      <c r="H26" s="10">
+      <c r="J26" s="10">
         <v>11.84</v>
       </c>
-      <c r="I26" s="10">
+      <c r="K26" s="10">
         <v>5.98</v>
       </c>
-      <c r="J26" s="10">
+      <c r="L26" s="10">
         <v>8.609999999999999</v>
       </c>
-      <c r="K26" s="10">
+      <c r="M26" s="10">
         <v>4.89</v>
       </c>
-      <c r="L26" s="10">
+      <c r="N26" s="10">
         <v>5.25</v>
       </c>
-      <c r="M26" s="10">
+      <c r="O26" s="10">
         <v>1674.49</v>
       </c>
-      <c r="N26" s="11">
+      <c r="P26" s="11">
         <v>-0.06164226193478251</v>
       </c>
-      <c r="O26" s="11">
+      <c r="Q26" s="11">
         <v>0.1107919426213355</v>
       </c>
     </row>
-    <row r="27" spans="2:15">
+    <row r="27" spans="2:17">
       <c r="B27" s="14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C27" s="10">
         <v>45.8</v>
       </c>
       <c r="D27" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="10">
+        <v>14.27</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G27" s="10">
+      <c r="G27" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I27" s="10">
         <v>11.71</v>
       </c>
-      <c r="H27" s="10">
+      <c r="J27" s="10">
         <v>8.33</v>
       </c>
-      <c r="I27" s="10">
+      <c r="K27" s="10">
         <v>4.69</v>
       </c>
-      <c r="J27" s="10">
+      <c r="L27" s="10">
         <v>8.82</v>
       </c>
-      <c r="K27" s="10">
+      <c r="M27" s="10">
         <v>7</v>
       </c>
-      <c r="L27" s="10">
+      <c r="N27" s="10">
         <v>5.25</v>
       </c>
-      <c r="M27" s="10">
+      <c r="O27" s="10">
         <v>1860.01</v>
       </c>
-      <c r="N27" s="11">
+      <c r="P27" s="11">
         <v>0.1107919426213355</v>
       </c>
-      <c r="O27" s="11">
+      <c r="Q27" s="11">
         <v>-0.04026860070644789</v>
       </c>
     </row>
-    <row r="28" spans="2:15">
+    <row r="28" spans="2:17">
       <c r="B28" s="14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C28" s="10">
-        <v>52.77999999999999</v>
+        <v>50.96999999999999</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="E28" s="10">
+        <v>40.03</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="10">
-        <v>13.96</v>
-      </c>
-      <c r="H28" s="10">
-        <v>7.7</v>
+        <v>57</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="I28" s="10">
-        <v>12.25</v>
+        <v>14.41</v>
       </c>
       <c r="J28" s="10">
-        <v>7.5</v>
+        <v>8.99</v>
       </c>
       <c r="K28" s="10">
-        <v>5</v>
+        <v>6.84</v>
       </c>
       <c r="L28" s="10">
-        <v>6.37</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M28" s="10">
+        <v>6.86</v>
+      </c>
+      <c r="N28" s="10">
+        <v>5.26</v>
+      </c>
+      <c r="O28" s="10">
         <v>1785.11</v>
       </c>
-      <c r="N28" s="11">
+      <c r="P28" s="11">
         <v>-0.04026860070644789</v>
       </c>
-      <c r="O28" s="14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15">
+      <c r="Q28" s="14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
       <c r="B29" s="14" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C29" s="10">
         <v>49.73999999999999</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>8</v>
+        <v>33</v>
+      </c>
+      <c r="E29" s="10">
+        <v>35.27</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G29" s="10">
+        <v>57</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I29" s="10">
         <v>13.58</v>
       </c>
-      <c r="H29" s="10">
+      <c r="J29" s="10">
         <v>7.44</v>
       </c>
-      <c r="I29" s="10">
+      <c r="K29" s="10">
         <v>11.5</v>
       </c>
-      <c r="J29" s="10">
+      <c r="L29" s="10">
         <v>8.24</v>
       </c>
-      <c r="K29" s="10">
+      <c r="M29" s="10">
         <v>2.59</v>
       </c>
-      <c r="L29" s="10">
+      <c r="N29" s="10">
         <v>6.39</v>
       </c>
-      <c r="M29" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="N29" s="14" t="s">
-        <v>43</v>
-      </c>
       <c r="O29" s="14" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="P29" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q29" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4676,8 +5064,20 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N6:O29">
+  <conditionalFormatting sqref="E6:E29">
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFEF4444"/>
+        <color rgb="FFFDE047"/>
+        <color rgb="FF22C55E"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6:Q29">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-0.2"/>
         <cfvo type="num" val="0"/>
@@ -4709,46 +5109,46 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C6" s="15">
         <v>-0.036358</v>
@@ -4757,27 +5157,27 @@
         <v>0.0278</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I6" s="14">
         <v>1</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C7" s="15">
         <v>0.000137</v>
@@ -4786,27 +5186,27 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I7" s="14">
         <v>10</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C8" s="15">
         <v>-0.032628</v>
@@ -4815,27 +5215,27 @@
         <v>0.0592</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I8" s="14">
         <v>2</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C9" s="15">
         <v>-0.002719</v>
@@ -4844,27 +5244,27 @@
         <v>0.7492</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F9" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I9" s="14">
         <v>7</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C10" s="15">
         <v>9.899999999999999E-05</v>
@@ -4873,27 +5273,27 @@
         <v>0.0223</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F10" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I10" s="14">
         <v>11</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C11" s="15">
         <v>-8.000000000000001E-05</v>
@@ -4902,27 +5302,27 @@
         <v>0.2363</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F11" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I11" s="14">
         <v>12</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C12" s="15">
         <v>-0.000221</v>
@@ -4931,27 +5331,27 @@
         <v>0.8799</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F12" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I12" s="14">
         <v>9</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C13" s="15">
         <v>-0.002852</v>
@@ -4960,27 +5360,27 @@
         <v>0.3781</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F13" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G13" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I13" s="14">
         <v>6</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C14" s="15">
         <v>-0.029501</v>
@@ -4989,27 +5389,27 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F14" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I14" s="14">
         <v>3</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C15" s="15">
         <v>0.006628</v>
@@ -5018,27 +5418,27 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C16" s="15">
         <v>-0.005037</v>
@@ -5047,27 +5447,27 @@
         <v>0.2276</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F16" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C17" s="15">
         <v>-0.000575</v>
@@ -5076,120 +5476,120 @@
         <v>0.8627</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F17" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="13" t="s">
         <v>96</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="I17" s="14">
         <v>8</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="S40" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="T40" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="U40" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="V40" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="W40" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C40" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L40" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="M40" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="N40" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="P40" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q40" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S40" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="T40" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="U40" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="V40" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="W40" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="X40" s="7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Y40" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="Z40" s="7" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="AA40" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C41" s="16">
         <v>0.050404</v>
@@ -5269,7 +5669,7 @@
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C42" s="16">
         <v>0.006803</v>
@@ -5349,7 +5749,7 @@
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C43" s="16">
         <v>0.033473</v>
@@ -5429,7 +5829,7 @@
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C44" s="16">
         <v>0.005801</v>
@@ -5509,7 +5909,7 @@
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C45" s="16">
         <v>0.000145</v>
@@ -5589,7 +5989,7 @@
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C46" s="16">
         <v>-6E-06</v>
@@ -5669,7 +6069,7 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C47" s="16">
         <v>-0.00157</v>
@@ -5720,13 +6120,13 @@
         <v>3.8E-05</v>
       </c>
       <c r="S47" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="T47" s="16">
         <v>0.000618</v>
       </c>
       <c r="U47" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="V47" s="16">
         <v>0.000495</v>
@@ -5749,7 +6149,7 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="8" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C48" s="16">
         <v>-0.013109</v>
@@ -5829,7 +6229,7 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" s="8" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C49" s="16">
         <v>-0.045005</v>
@@ -5909,7 +6309,7 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C50" s="16">
         <v>0.004475</v>
@@ -5989,7 +6389,7 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="8" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C51" s="16">
         <v>-0.010339</v>
@@ -6069,10 +6469,10 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" s="8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D52" s="16">
         <v>0.023665</v>
@@ -6210,37 +6610,37 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="8" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C6" s="16">
         <v>7.2336</v>
@@ -6249,18 +6649,18 @@
         <v>0.0072</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="8" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C7" s="16">
         <v>0.5046</v>
@@ -6269,18 +6669,18 @@
         <v>0.4775</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C8" s="16">
         <v>0.3229</v>
@@ -6289,18 +6689,18 @@
         <v>0.5699</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C9" s="16">
         <v>0.2242</v>
@@ -6309,18 +6709,18 @@
         <v>0.6359</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C10" s="16">
         <v>0.004</v>
@@ -6329,13 +6729,13 @@
         <v>0.9498</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6367,36 +6767,36 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C8" s="16">
         <v>0.425</v>
@@ -6404,7 +6804,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C9" s="16">
         <v>0.1599</v>
@@ -6412,7 +6812,7 @@
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C10" s="16">
         <v>0.3692</v>
@@ -6420,15 +6820,15 @@
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C12" s="16">
         <v>0.5031</v>
@@ -6436,27 +6836,27 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="6" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -6621,18 +7021,18 @@
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="7" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -6640,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D28" s="16">
         <v>0.02178040146827698</v>
@@ -6651,7 +7051,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D29" s="16">
         <v>0.02076428011059761</v>
@@ -6662,7 +7062,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D30" s="16">
         <v>0.01783575303852558</v>
@@ -6673,7 +7073,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D31" s="16">
         <v>0.01772940717637539</v>
@@ -6684,7 +7084,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D32" s="16">
         <v>0.01733604446053505</v>
@@ -6695,7 +7095,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D33" s="16">
         <v>0.0167862419039011</v>
@@ -6706,7 +7106,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D34" s="16">
         <v>0.01557330787181854</v>
@@ -6717,7 +7117,7 @@
         <v>8</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D35" s="16">
         <v>0.01539521757513285</v>
@@ -6728,7 +7128,7 @@
         <v>9</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D36" s="16">
         <v>0.01488733943551779</v>
@@ -6739,7 +7139,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D37" s="16">
         <v>0.01360253803431988</v>
@@ -6750,7 +7150,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="D38" s="16">
         <v>0.0134799899533391</v>
@@ -6761,7 +7161,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D39" s="16">
         <v>0.01324111688882113</v>
@@ -6772,7 +7172,7 @@
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="D40" s="16">
         <v>0.01247525215148926</v>
@@ -6783,7 +7183,7 @@
         <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D41" s="16">
         <v>0.01242704410105944</v>
@@ -6794,7 +7194,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D42" s="16">
         <v>0.01225554849952459</v>
@@ -6834,532 +7234,532 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9">
         <v>0.25</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F6" s="10">
         <v>60</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="9">
         <v>0.25</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F7" s="10">
         <v>50</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="9">
         <v>0.25</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F8" s="10">
         <v>69</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="9">
         <v>0.25</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F9" s="10">
         <v>50</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="9">
         <v>0.25</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F10" s="10">
         <v>43</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="9">
         <v>0.2</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F11" s="10">
         <v>29</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="9">
         <v>0.2</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F12" s="10">
         <v>0</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" s="9">
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F13" s="10">
         <v>53</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C14" s="9">
         <v>0.2</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="9">
         <v>0.2</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F15" s="10">
         <v>48</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="9">
         <v>0.2</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F16" s="10">
         <v>56</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C17" s="9">
         <v>0.2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F17" s="10">
         <v>30</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" s="9">
         <v>0.2</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F18" s="10">
         <v>33</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:7">
       <c r="B19" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" s="9">
         <v>0.2</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F19" s="10">
         <v>80</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C20" s="9">
         <v>0.15</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F20" s="10">
         <v>48</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C21" s="9">
         <v>0.15</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F21" s="10">
         <v>53</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C22" s="9">
         <v>0.15</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="9">
         <v>0.15</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="9">
         <v>0.1</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" s="9">
         <v>0.1</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C26" s="9">
         <v>0.1</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F26" s="10">
         <v>75</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C27" s="9">
         <v>0.1</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28" s="9">
         <v>0.1</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C29" s="9">
         <v>0.1</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="F29" s="10">
         <v>47</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C30" s="9">
         <v>0.1</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -7385,823 +7785,1029 @@
   <sheetPr>
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
-  <dimension ref="B2:J63"/>
+  <dimension ref="B2:L69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
       <c r="B5" s="4" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C5" s="14">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C6" s="16">
+        <v>0.004156386627439163</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
+      <c r="B7" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.01637492941840768</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="16">
         <v>0.02840623638565849</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="16">
+    <row r="9" spans="2:3">
+      <c r="B9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="16">
         <v>0.09203839638622249</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C8" s="11">
+    <row r="10" spans="2:3">
+      <c r="B10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="11">
         <v>0.5454545454545454</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C9" s="11">
+    <row r="12" spans="2:3">
+      <c r="B12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.2004819890874032</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="11">
         <v>0.2503907960980185</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C10" s="11">
+    <row r="14" spans="2:3">
+      <c r="B14" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="11">
         <v>0.4982793930034239</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C11" s="10">
-        <v>0.4772669097784704</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" s="10">
+    <row r="15" spans="2:3">
+      <c r="B15" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0.4656941087978428</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="B16" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="10">
         <v>0.4801617850137476</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="14">
-        <v>20</v>
-      </c>
-      <c r="D16" s="11">
-        <v>0.02427861093956355</v>
-      </c>
-      <c r="E16" s="11">
-        <v>0.03098237889258304</v>
-      </c>
-      <c r="F16" s="11">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="14" t="s">
+    <row r="18" spans="2:12">
+      <c r="B18" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11">
+        <v>-0.0209851405796474</v>
+      </c>
+      <c r="E20" s="11">
+        <v>-0.0209851405796474</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="14">
+        <v>11</v>
+      </c>
+      <c r="D21" s="11">
+        <v>0.02325036242226524</v>
+      </c>
+      <c r="E21" s="11">
+        <v>0.03163927438071323</v>
+      </c>
+      <c r="F21" s="11">
+        <v>0.6363636363636364</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="14">
+        <v>7</v>
+      </c>
+      <c r="D22" s="11">
+        <v>0.04364110592335368</v>
+      </c>
+      <c r="E22" s="11">
+        <v>0.05295900096414319</v>
+      </c>
+      <c r="F22" s="11">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="14">
-        <v>2</v>
-      </c>
-      <c r="D17" s="11">
-        <v>0.008438121178118818</v>
-      </c>
-      <c r="E17" s="11">
-        <v>0.008438121178118818</v>
-      </c>
-      <c r="F17" s="11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="F20" s="7" t="s">
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="11">
+        <v>-0.01260270879374577</v>
+      </c>
+      <c r="E23" s="11">
+        <v>-0.04026860070644789</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="B26" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G20" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="10">
+      <c r="E26" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="10">
         <v>61.41</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="11">
-        <v>0.182224870744645</v>
-      </c>
-      <c r="G21" s="11">
-        <v>0.0911124353723225</v>
-      </c>
-      <c r="H21" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I21" s="10">
-        <v>109.1112435372323</v>
-      </c>
-      <c r="J21" s="10">
-        <v>118.2224870744645</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="10">
-        <v>52.98</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F22" s="11">
-        <v>-0.04720457207766848</v>
-      </c>
-      <c r="G22" s="11">
-        <v>-0.02360228603883424</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I22" s="10">
-        <v>106.5359687572136</v>
-      </c>
-      <c r="J22" s="10">
-        <v>112.6418451621567</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="10">
-        <v>54.28</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F23" s="11">
-        <v>0.1164031414392799</v>
-      </c>
-      <c r="G23" s="11">
-        <v>0.05820157071963994</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I23" s="10">
-        <v>112.7365294770219</v>
-      </c>
-      <c r="J23" s="10">
-        <v>125.7537097965487</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="10">
-        <v>52.83</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F24" s="11">
-        <v>-0.004091358090610453</v>
-      </c>
-      <c r="G24" s="11">
-        <v>-0.002045679045305226</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I24" s="10">
-        <v>112.5059067210303</v>
-      </c>
-      <c r="J24" s="10">
-        <v>125.2392063385483</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="10">
-        <v>59</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F25" s="11">
-        <v>-0.197399725228697</v>
-      </c>
-      <c r="G25" s="11">
-        <v>-0.09869986261434849</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I25" s="10">
-        <v>101.4015891843619</v>
-      </c>
-      <c r="J25" s="10">
-        <v>100.5170214194588</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="10">
-        <v>50.26000000000001</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F26" s="11">
-        <v>-0.05468436873747495</v>
-      </c>
-      <c r="G26" s="11">
-        <v>-0.02734218436873748</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I26" s="10">
-        <v>98.62904823760013</v>
-      </c>
-      <c r="J26" s="10">
-        <v>95.02031155576445</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="10">
-        <v>52.06</v>
-      </c>
       <c r="D27" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E27" s="9">
         <v>0.5</v>
       </c>
-      <c r="F27" s="11">
-        <v>-0.1104309651888949</v>
-      </c>
-      <c r="G27" s="11">
-        <v>-0.05521548259444747</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I27" s="10">
-        <v>93.18319774132999</v>
-      </c>
-      <c r="J27" s="10">
-        <v>84.52712683811188</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
+      <c r="F27" s="10">
+        <v>61.41</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.182224870744645</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0.0911124353723225</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K27" s="10">
+        <v>109.1112435372323</v>
+      </c>
+      <c r="L27" s="10">
+        <v>118.2224870744645</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
       <c r="B28" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C28" s="10">
-        <v>46.09</v>
+        <v>52.98</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E28" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="F28" s="11">
-        <v>0.05714484306268552</v>
-      </c>
-      <c r="G28" s="11">
-        <v>0.01714345291880566</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I28" s="10">
-        <v>94.78067950463225</v>
-      </c>
-      <c r="J28" s="10">
-        <v>89.35741623581549</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
+        <v>0.5</v>
+      </c>
+      <c r="F28" s="10">
+        <v>52.98</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="11">
+        <v>-0.04720457207766848</v>
+      </c>
+      <c r="I28" s="11">
+        <v>-0.02360228603883424</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K28" s="10">
+        <v>106.5359687572136</v>
+      </c>
+      <c r="L28" s="10">
+        <v>112.6418451621567</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12">
       <c r="B29" s="14" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C29" s="10">
-        <v>53.65000000000001</v>
+        <v>54.28</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E29" s="9">
         <v>0.5</v>
       </c>
-      <c r="F29" s="11">
-        <v>0.05216786895100678</v>
-      </c>
-      <c r="G29" s="11">
-        <v>0.02608393447550339</v>
-      </c>
-      <c r="H29" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I29" s="10">
-        <v>97.25293253837476</v>
-      </c>
-      <c r="J29" s="10">
-        <v>94.01900221580608</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
+      <c r="F29" s="10">
+        <v>54.28</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="11">
+        <v>0.1164031414392799</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.05820157071963994</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K29" s="10">
+        <v>112.7365294770219</v>
+      </c>
+      <c r="L29" s="10">
+        <v>125.7537097965487</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
       <c r="B30" s="14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C30" s="10">
-        <v>57.02</v>
+        <v>52.83</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30" s="9">
         <v>0.5</v>
       </c>
-      <c r="F30" s="11">
-        <v>0.03032548340445285</v>
-      </c>
-      <c r="G30" s="11">
-        <v>0.01516274170222642</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I30" s="10">
-        <v>98.72755363423819</v>
-      </c>
-      <c r="J30" s="10">
-        <v>96.87017390720473</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
+      <c r="F30" s="10">
+        <v>52.83</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="11">
+        <v>-0.004091358090610453</v>
+      </c>
+      <c r="I30" s="11">
+        <v>-0.002045679045305226</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K30" s="10">
+        <v>112.5059067210303</v>
+      </c>
+      <c r="L30" s="10">
+        <v>125.2392063385483</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12">
       <c r="B31" s="14" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C31" s="10">
-        <v>58.89</v>
+        <v>63.34</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E31" s="9">
         <v>0.5</v>
       </c>
-      <c r="F31" s="11">
-        <v>-0.0209851405796474</v>
-      </c>
-      <c r="G31" s="11">
-        <v>-0.0104925702898237</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I31" s="10">
-        <v>97.69164783818862</v>
-      </c>
-      <c r="J31" s="10">
-        <v>94.83733968978714</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
+      <c r="F31" s="10">
+        <v>59</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="11">
+        <v>-0.197399725228697</v>
+      </c>
+      <c r="I31" s="11">
+        <v>-0.09869986261434849</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K31" s="10">
+        <v>101.4015891843619</v>
+      </c>
+      <c r="L31" s="10">
+        <v>100.5170214194588</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12">
       <c r="B32" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C32" s="10">
-        <v>52.60999999999999</v>
+        <v>27.45</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E32" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F32" s="11">
-        <v>0.136433230377103</v>
-      </c>
-      <c r="G32" s="11">
-        <v>0.06821661518855149</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I32" s="10">
-        <v>104.3558413859018</v>
-      </c>
-      <c r="J32" s="10">
-        <v>107.7763043040354</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
+        <v>0.1</v>
+      </c>
+      <c r="F32" s="10">
+        <v>50.26000000000001</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="11">
+        <v>-0.05468436873747495</v>
+      </c>
+      <c r="I32" s="11">
+        <v>-0.005468436873747495</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K32" s="10">
+        <v>100.8470809950096</v>
+      </c>
+      <c r="L32" s="10">
+        <v>95.02031155576445</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12">
       <c r="B33" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="10">
+        <v>39.08</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F33" s="10">
+        <v>52.06</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="11">
+        <v>-0.1104309651888949</v>
+      </c>
+      <c r="I33" s="11">
+        <v>-0.03312928955666848</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K33" s="10">
+        <v>97.50608884778109</v>
+      </c>
+      <c r="L33" s="10">
+        <v>84.52712683811188</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="10">
-        <v>53.12</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F33" s="11">
-        <v>-0.03019258774696476</v>
-      </c>
-      <c r="G33" s="11">
-        <v>-0.01509629387348238</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I33" s="10">
-        <v>102.7804549369257</v>
-      </c>
-      <c r="J33" s="10">
-        <v>104.5222587792923</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34" s="14" t="s">
+      <c r="C34" s="10">
+        <v>17.89</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F34" s="10">
+        <v>46.09</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H34" s="11">
+        <v>0.05714484306268552</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.005714484306268553</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K34" s="10">
+        <v>98.06328586226736</v>
+      </c>
+      <c r="L34" s="10">
+        <v>89.35741623581549</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="10">
-        <v>55.39</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F34" s="11">
-        <v>0.0342241351620467</v>
-      </c>
-      <c r="G34" s="11">
-        <v>0.01711206758102335</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I34" s="10">
-        <v>104.5392410278147</v>
-      </c>
-      <c r="J34" s="10">
-        <v>108.0994426911972</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35" s="14" t="s">
-        <v>61</v>
-      </c>
       <c r="C35" s="10">
-        <v>54.38000000000001</v>
+        <v>50.11</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E35" s="9">
         <v>0.5</v>
       </c>
-      <c r="F35" s="11">
-        <v>-0.01642933677034653</v>
-      </c>
-      <c r="G35" s="11">
-        <v>-0.008214668385173263</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I35" s="10">
-        <v>103.6804858295335</v>
-      </c>
-      <c r="J35" s="10">
-        <v>106.3234405425367</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
+      <c r="F35" s="10">
+        <v>53.65000000000001</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="11">
+        <v>0.05216786895100678</v>
+      </c>
+      <c r="I35" s="11">
+        <v>0.02608393447550339</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K35" s="10">
+        <v>100.6211621851513</v>
+      </c>
+      <c r="L35" s="10">
+        <v>94.01900221580608</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12">
       <c r="B36" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="10">
-        <v>55.02</v>
+        <v>61.36</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E36" s="9">
         <v>0.5</v>
       </c>
-      <c r="F36" s="11">
-        <v>0.03163927438071323</v>
-      </c>
-      <c r="G36" s="11">
-        <v>0.01581963719035662</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I36" s="10">
-        <v>105.3206734990767</v>
-      </c>
-      <c r="J36" s="10">
-        <v>109.6874370509635</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
+      <c r="F36" s="10">
+        <v>57.02</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.03032548340445285</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0.01516274170222642</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K36" s="10">
+        <v>102.1468548771426</v>
+      </c>
+      <c r="L36" s="10">
+        <v>96.87017390720473</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12">
       <c r="B37" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="10">
+        <v>66.93000000000001</v>
+      </c>
+      <c r="D37" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="10">
-        <v>52.17</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>31</v>
-      </c>
       <c r="E37" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F37" s="11">
-        <v>0.05295900096414319</v>
-      </c>
-      <c r="G37" s="11">
-        <v>0.02647950048207159</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I37" s="10">
-        <v>108.1095123237675</v>
-      </c>
-      <c r="J37" s="10">
-        <v>115.4963741354999</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
+        <v>0.775</v>
+      </c>
+      <c r="F37" s="10">
+        <v>58.89</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="11">
+        <v>-0.0209851405796474</v>
+      </c>
+      <c r="I37" s="11">
+        <v>-0.01626348394922673</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K37" s="10">
+        <v>100.4855911423842</v>
+      </c>
+      <c r="L37" s="10">
+        <v>94.83733968978714</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12">
       <c r="B38" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C38" s="10">
-        <v>50.97000000000001</v>
+        <v>43.88</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E38" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F38" s="11">
-        <v>0.2075693823715363</v>
-      </c>
-      <c r="G38" s="11">
-        <v>0.1037846911857682</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I38" s="10">
-        <v>119.3296246745338</v>
-      </c>
-      <c r="J38" s="10">
-        <v>139.4698851809575</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
+        <v>0.3</v>
+      </c>
+      <c r="F38" s="10">
+        <v>52.60999999999999</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" s="11">
+        <v>0.136433230377103</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0.04092996911313089</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K38" s="10">
+        <v>104.5984632841567</v>
+      </c>
+      <c r="L38" s="10">
+        <v>107.7763043040354</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12">
       <c r="B39" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C39" s="10">
-        <v>53.79000000000001</v>
+        <v>45.97</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E39" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="F39" s="11">
-        <v>0.07389420473009567</v>
-      </c>
-      <c r="G39" s="11">
-        <v>0.03694710236504783</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I39" s="10">
-        <v>123.7385085325665</v>
-      </c>
-      <c r="J39" s="10">
-        <v>149.7759014302021</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
+        <v>0.3</v>
+      </c>
+      <c r="F39" s="10">
+        <v>53.12</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="11">
+        <v>-0.03019258774696476</v>
+      </c>
+      <c r="I39" s="11">
+        <v>-0.009057776324089427</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K39" s="10">
+        <v>103.6510337998853</v>
+      </c>
+      <c r="L39" s="10">
+        <v>104.5222587792923</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12">
       <c r="B40" s="14" t="s">
         <v>66</v>
       </c>
       <c r="C40" s="10">
-        <v>50.94</v>
+        <v>54.51</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E40" s="9">
         <v>0.5</v>
       </c>
-      <c r="F40" s="11">
-        <v>-0.06164226193478251</v>
-      </c>
-      <c r="G40" s="11">
-        <v>-0.03082113096739125</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="I40" s="10">
-        <v>119.9247477553746</v>
-      </c>
-      <c r="J40" s="10">
-        <v>140.5433760827234</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
+      <c r="F40" s="10">
+        <v>55.39</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" s="11">
+        <v>0.0342241351620467</v>
+      </c>
+      <c r="I40" s="11">
+        <v>0.01711206758102335</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K40" s="10">
+        <v>105.4247172951119</v>
+      </c>
+      <c r="L40" s="10">
+        <v>108.0994426911972</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12">
       <c r="B41" s="14" t="s">
         <v>67</v>
       </c>
       <c r="C41" s="10">
-        <v>52.59</v>
+        <v>50.47</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E41" s="9">
         <v>0.5</v>
       </c>
-      <c r="F41" s="11">
-        <v>0.1107919426213355</v>
-      </c>
-      <c r="G41" s="11">
-        <v>0.05539597131066776</v>
-      </c>
-      <c r="H41" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I41" s="10">
-        <v>126.5680956414704</v>
-      </c>
-      <c r="J41" s="10">
-        <v>156.1144497414892</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
+      <c r="F41" s="10">
+        <v>54.38000000000001</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" s="11">
+        <v>-0.01642933677034653</v>
+      </c>
+      <c r="I41" s="11">
+        <v>-0.008214668385173263</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K41" s="10">
+        <v>104.5586882029319</v>
+      </c>
+      <c r="L41" s="10">
+        <v>106.3234405425367</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12">
       <c r="B42" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C42" s="10">
+        <v>53</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F42" s="10">
+        <v>55.02</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="11">
+        <v>0.03163927438071323</v>
+      </c>
+      <c r="I42" s="11">
+        <v>0.01581963719035662</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K42" s="10">
+        <v>106.2127687154019</v>
+      </c>
+      <c r="L42" s="10">
+        <v>109.6874370509635</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="B43" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="10">
+        <v>41.2</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F43" s="10">
+        <v>52.17</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H43" s="11">
+        <v>0.05295900096414319</v>
+      </c>
+      <c r="I43" s="11">
+        <v>0.01588770028924296</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K43" s="10">
+        <v>107.9002453516429</v>
+      </c>
+      <c r="L43" s="10">
+        <v>115.4963741354999</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="B44" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="10">
+        <v>36.51</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F44" s="10">
+        <v>50.97000000000001</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H44" s="11">
+        <v>0.2075693823715363</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0.0622708147114609</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K44" s="10">
+        <v>114.6192815372562</v>
+      </c>
+      <c r="L44" s="10">
+        <v>139.4698851809575</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="10">
+        <v>49.08</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="F45" s="10">
+        <v>53.79000000000001</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="11">
+        <v>0.07389420473009567</v>
+      </c>
+      <c r="I45" s="11">
+        <v>0.03694710236504783</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K45" s="10">
+        <v>118.8541318652214</v>
+      </c>
+      <c r="L45" s="10">
+        <v>149.7759014302021</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12">
+      <c r="B46" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46" s="10">
+        <v>36.71</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="10">
+        <v>50.94</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="11">
+        <v>-0.06164226193478251</v>
+      </c>
+      <c r="I46" s="11">
+        <v>-0.01849267858043475</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K46" s="10">
+        <v>116.6562006066813</v>
+      </c>
+      <c r="L46" s="10">
+        <v>140.5433760827234</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
+      <c r="B47" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="10">
+        <v>44.52</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="F47" s="10">
+        <v>52.59</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="11">
+        <v>0.1107919426213355</v>
+      </c>
+      <c r="I47" s="11">
+        <v>0.03323758278640065</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="K47" s="10">
+        <v>120.5335707318928</v>
+      </c>
+      <c r="L47" s="10">
+        <v>156.1144497414892</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12">
+      <c r="B48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C48" s="10">
+        <v>14.27</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F48" s="10">
         <v>45.8</v>
       </c>
-      <c r="D42" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="F42" s="11">
+      <c r="G48" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" s="11">
         <v>-0.04026860070644789</v>
       </c>
-      <c r="G42" s="11">
-        <v>-0.01208058021193437</v>
-      </c>
-      <c r="H42" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="I42" s="10">
-        <v>125.0390796098018</v>
-      </c>
-      <c r="J42" s="10">
+      <c r="I48" s="11">
+        <v>-0.004026860070644789</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="K48" s="10">
+        <v>120.0481989087403</v>
+      </c>
+      <c r="L48" s="10">
         <v>149.8279393003424</v>
       </c>
     </row>
-    <row r="63" spans="2:2">
-      <c r="B63" s="19" t="s">
-        <v>254</v>
+    <row r="69" spans="2:2">
+      <c r="B69" s="19" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -8215,7 +8821,7 @@
   <sheetPr>
     <tabColor rgb="FF64748B"/>
   </sheetPr>
-  <dimension ref="B2:I28"/>
+  <dimension ref="B2:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -8227,20 +8833,20 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="9">
         <v>0.25</v>
@@ -8248,7 +8854,7 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="9">
         <v>0.2</v>
@@ -8256,7 +8862,7 @@
     </row>
     <row r="8" spans="2:5">
       <c r="B8" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="9">
         <v>0.2</v>
@@ -8264,7 +8870,7 @@
     </row>
     <row r="9" spans="2:5">
       <c r="B9" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="9">
         <v>0.15</v>
@@ -8272,7 +8878,7 @@
     </row>
     <row r="10" spans="2:5">
       <c r="B10" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="9">
         <v>0.1</v>
@@ -8280,7 +8886,7 @@
     </row>
     <row r="11" spans="2:5">
       <c r="B11" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="9">
         <v>0.1</v>
@@ -8288,104 +8894,104 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="7" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>36</v>
+        <v>269</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="14" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="14" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="14" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>4</v>
+        <v>280</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>6</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="14" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="14" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="6" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -8396,10 +9002,10 @@
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -8410,10 +9016,10 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -8424,10 +9030,10 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -8438,10 +9044,10 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -8452,10 +9058,10 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -8466,10 +9072,10 @@
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="14" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -8478,8 +9084,36 @@
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
     </row>
+    <row r="29" spans="2:9">
+      <c r="B29" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C24:I24"/>
@@ -8487,6 +9121,8 @@
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="C27:I27"/>
     <mergeCell ref="C28:I28"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C30:I30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -17,22 +17,22 @@
     <sheet name="07_Methodology" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Factor_Scores'!$B$5:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Factor_Scores'!$B$5:$G$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="304">
   <si>
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 10:09:07  |  Source: output/exports/score_*.json</t>
-  </si>
-  <si>
-    <t>49.7</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 11:09:13  |  Source: output/exports/score_*.json</t>
+  </si>
+  <si>
+    <t>49.4</t>
   </si>
   <si>
     <t>Raw Regime / Label</t>
@@ -44,13 +44,13 @@
     <t>CALIBRATED ACTION</t>
   </si>
   <si>
-    <t>🟠 REDUCE — 35.3</t>
+    <t>🟡 HOLD — 34.5</t>
   </si>
   <si>
     <t>Recommended Equity</t>
   </si>
   <si>
-    <t>20–40% Equities (calibrated)</t>
+    <t>40–60% Equities (calibrated)</t>
   </si>
   <si>
     <t>Percentile Signal</t>
@@ -62,7 +62,7 @@
     <t>Pillar Dispersion</t>
   </si>
   <si>
-    <t>HIGH (σ=14.36)</t>
+    <t>HIGH (σ=13.61)</t>
   </si>
   <si>
     <t>Data As-Of</t>
@@ -185,24 +185,24 @@
     <t>BUY/ACCUMULATE</t>
   </si>
   <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>2022-Q2</t>
   </si>
   <si>
     <t>SELL</t>
   </si>
   <si>
+    <t>2022-Q3</t>
+  </si>
+  <si>
+    <t>REDUCE</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
-    <t>2022-Q3</t>
-  </si>
-  <si>
-    <t>REDUCE</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>2022-Q4</t>
   </si>
   <si>
@@ -713,7 +713,7 @@
     <t>adtv</t>
   </si>
   <si>
-    <t>ADTV data unavailable → neutral score 50</t>
+    <t>ADTV change -11.9% QoQ</t>
   </si>
   <si>
     <t>etf_flow</t>
@@ -728,6 +728,12 @@
     <t>0.00% of Market Cap (YTD in Q)</t>
   </si>
   <si>
+    <t>pillar_components_used</t>
+  </si>
+  <si>
+    <t>3/3 components with data → average over 3</t>
+  </si>
+  <si>
     <t>SIGNAL EFFICACY — DOES THE CALIBRATED ACTION SIGNAL PREDICT NEXT-QUARTER RETURNS?</t>
   </si>
   <si>
@@ -926,7 +932,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 10:09:07 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 11:09:13 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1292,7 +1298,7 @@
                   <c:v>2.59</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.39</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1467,76 +1473,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>61.41</c:v>
+                  <c:v>64.01000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.98</c:v>
+                  <c:v>55.19</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.28</c:v>
+                  <c:v>54.94</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.83</c:v>
+                  <c:v>52.61</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63.34</c:v>
+                  <c:v>62.17</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.45</c:v>
+                  <c:v>26.12</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>39.08</c:v>
+                  <c:v>35.08</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>17.89</c:v>
+                  <c:v>21.68</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>50.11</c:v>
+                  <c:v>49.98</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>61.36</c:v>
+                  <c:v>55.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>66.93000000000001</c:v>
+                  <c:v>66.42</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>43.88</c:v>
+                  <c:v>45.84</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>45.97</c:v>
+                  <c:v>41.76</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>54.51</c:v>
+                  <c:v>54.84</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>50.47</c:v>
+                  <c:v>47.88</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>53</c:v>
+                  <c:v>48.34</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>41.2</c:v>
+                  <c:v>39.85</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>36.51</c:v>
+                  <c:v>39.78</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>49.08</c:v>
+                  <c:v>53.01</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>36.71</c:v>
+                  <c:v>43.29</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>44.52</c:v>
+                  <c:v>38.67</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>14.27</c:v>
+                  <c:v>20.48</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>40.03</c:v>
+                  <c:v>36.76</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>35.27</c:v>
+                  <c:v>34.51</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1646,76 +1652,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>61.41</c:v>
+                  <c:v>64.01000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>52.98</c:v>
+                  <c:v>55.19</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.28</c:v>
+                  <c:v>54.94</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.83</c:v>
+                  <c:v>52.61</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>59</c:v>
+                  <c:v>60.76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.26000000000001</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>52.06</c:v>
+                  <c:v>51.07</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46.09</c:v>
+                  <c:v>45.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>53.65000000000001</c:v>
+                  <c:v>54.29</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>57.02</c:v>
+                  <c:v>56.39</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>58.89</c:v>
+                  <c:v>60.22</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>52.60999999999999</c:v>
+                  <c:v>53.57</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>53.12</c:v>
+                  <c:v>52.15</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>55.39</c:v>
+                  <c:v>56.26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>54.38000000000001</c:v>
+                  <c:v>54.14</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>55.02</c:v>
+                  <c:v>54.26</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52.17</c:v>
+                  <c:v>51.77</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>50.97000000000001</c:v>
+                  <c:v>51.63</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>53.79000000000001</c:v>
+                  <c:v>55.24</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>50.94</c:v>
+                  <c:v>52.6</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>52.59</c:v>
+                  <c:v>51.31</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>45.8</c:v>
+                  <c:v>46.38</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>50.96999999999999</c:v>
+                  <c:v>50.12</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>49.73999999999999</c:v>
+                  <c:v>49.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1897,7 +1903,7 @@
                   <c:v>1860.01</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1785.11</c:v>
+                  <c:v>1780.68</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -2766,28 +2772,28 @@
                   <c:v>105.4247172951119</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>104.5586882029319</c:v>
+                  <c:v>104.9050998398039</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>106.2127687154019</c:v>
+                  <c:v>105.9008362111342</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>107.9002453516429</c:v>
+                  <c:v>107.5833569572369</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>114.6192815372562</c:v>
+                  <c:v>114.2826602443579</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>118.8541318652214</c:v>
+                  <c:v>118.5050733909562</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>116.6562006066813</c:v>
+                  <c:v>116.3135971585864</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>120.5335707318928</c:v>
+                  <c:v>120.179579973329</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>120.0481989087403</c:v>
+                  <c:v>119.6670103592256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2954,7 +2960,7 @@
                   <c:v>156.1144497414892</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>149.8279393003424</c:v>
+                  <c:v>149.4561203249849</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3624,7 +3630,7 @@
         <v>13.58</v>
       </c>
       <c r="F14" s="11">
-        <v>0.2730197024527543</v>
+        <v>0.275177304964539</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>25</v>
@@ -3644,7 +3650,7 @@
         <v>7.44</v>
       </c>
       <c r="F15" s="11">
-        <v>0.149577804583836</v>
+        <v>0.1507598784194529</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -3664,7 +3670,7 @@
         <v>11.5</v>
       </c>
       <c r="F16" s="11">
-        <v>0.2312022517088862</v>
+        <v>0.2330293819655522</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>25</v>
@@ -3684,7 +3690,7 @@
         <v>8.24</v>
       </c>
       <c r="F17" s="11">
-        <v>0.1656614394853237</v>
+        <v>0.1669706180344478</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>25</v>
@@ -3704,7 +3710,7 @@
         <v>2.59</v>
       </c>
       <c r="F18" s="11">
-        <v>0.05207076799356654</v>
+        <v>0.05248226950354609</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>27</v>
@@ -3718,13 +3724,13 @@
         <v>0.1</v>
       </c>
       <c r="D19" s="10">
-        <v>63.94</v>
+        <v>59.97</v>
       </c>
       <c r="E19" s="10">
-        <v>6.39</v>
+        <v>6</v>
       </c>
       <c r="F19" s="11">
-        <v>0.1284680337756333</v>
+        <v>0.121580547112462</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>25</v>
@@ -3739,7 +3745,7 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="10">
-        <v>49.74</v>
+        <v>49.35</v>
       </c>
       <c r="F20" s="11">
         <v>1</v>
@@ -3856,13 +3862,13 @@
         <v>45</v>
       </c>
       <c r="C6" s="10">
-        <v>61.41</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="10">
-        <v>61.41</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>33</v>
@@ -3889,7 +3895,7 @@
         <v>8.52</v>
       </c>
       <c r="N6" s="10">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="O6" s="10">
         <v>1191.44</v>
@@ -3906,13 +3912,13 @@
         <v>48</v>
       </c>
       <c r="C7" s="10">
-        <v>52.98</v>
+        <v>55.19</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="10">
-        <v>52.98</v>
+        <v>55.19</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>33</v>
@@ -3939,7 +3945,7 @@
         <v>3.89</v>
       </c>
       <c r="N7" s="10">
-        <v>5.2</v>
+        <v>7.41</v>
       </c>
       <c r="O7" s="10">
         <v>1408.55</v>
@@ -3956,13 +3962,13 @@
         <v>49</v>
       </c>
       <c r="C8" s="10">
-        <v>54.28</v>
+        <v>54.94</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="10">
-        <v>54.28</v>
+        <v>54.94</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>33</v>
@@ -3989,7 +3995,7 @@
         <v>3.25</v>
       </c>
       <c r="N8" s="10">
-        <v>5.2</v>
+        <v>5.86</v>
       </c>
       <c r="O8" s="10">
         <v>1342.06</v>
@@ -4006,13 +4012,13 @@
         <v>50</v>
       </c>
       <c r="C9" s="10">
-        <v>52.83</v>
+        <v>52.61</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="10">
-        <v>52.83</v>
+        <v>52.61</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>33</v>
@@ -4039,7 +4045,7 @@
         <v>3.04</v>
       </c>
       <c r="N9" s="10">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
       <c r="O9" s="10">
         <v>1498.28</v>
@@ -4056,13 +4062,13 @@
         <v>51</v>
       </c>
       <c r="C10" s="10">
-        <v>59</v>
+        <v>60.76</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E10" s="10">
-        <v>63.34</v>
+        <v>62.17</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>33</v>
@@ -4071,7 +4077,7 @@
         <v>52</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I10" s="10">
         <v>12.54</v>
@@ -4089,7 +4095,7 @@
         <v>7.91</v>
       </c>
       <c r="N10" s="10">
-        <v>5.2</v>
+        <v>6.96</v>
       </c>
       <c r="O10" s="10">
         <v>1492.15</v>
@@ -4103,25 +4109,25 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="10">
-        <v>50.26000000000001</v>
+        <v>50</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E11" s="10">
-        <v>27.45</v>
+        <v>26.12</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I11" s="10">
         <v>11.73</v>
@@ -4139,7 +4145,7 @@
         <v>2.68</v>
       </c>
       <c r="N11" s="10">
-        <v>4.95</v>
+        <v>4.69</v>
       </c>
       <c r="O11" s="10">
         <v>1197.6</v>
@@ -4156,13 +4162,13 @@
         <v>56</v>
       </c>
       <c r="C12" s="10">
-        <v>52.06</v>
+        <v>51.07</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="10">
-        <v>39.08</v>
+        <v>35.08</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>57</v>
@@ -4189,7 +4195,7 @@
         <v>7.08</v>
       </c>
       <c r="N12" s="10">
-        <v>4.98</v>
+        <v>3.99</v>
       </c>
       <c r="O12" s="10">
         <v>1132.11</v>
@@ -4206,22 +4212,22 @@
         <v>59</v>
       </c>
       <c r="C13" s="10">
-        <v>46.09</v>
+        <v>45.8</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>57</v>
       </c>
       <c r="E13" s="10">
-        <v>17.89</v>
+        <v>21.68</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I13" s="10">
         <v>9.34</v>
@@ -4239,7 +4245,7 @@
         <v>3.67</v>
       </c>
       <c r="N13" s="10">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="O13" s="10">
         <v>1007.09</v>
@@ -4256,13 +4262,13 @@
         <v>60</v>
       </c>
       <c r="C14" s="10">
-        <v>53.65000000000001</v>
+        <v>54.29</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E14" s="10">
-        <v>50.11</v>
+        <v>49.98</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>33</v>
@@ -4271,7 +4277,7 @@
         <v>33</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I14" s="10">
         <v>12.48</v>
@@ -4289,7 +4295,7 @@
         <v>6.7</v>
       </c>
       <c r="N14" s="10">
-        <v>5.01</v>
+        <v>5.65</v>
       </c>
       <c r="O14" s="10">
         <v>1064.64</v>
@@ -4306,13 +4312,13 @@
         <v>61</v>
       </c>
       <c r="C15" s="10">
-        <v>57.02</v>
+        <v>56.39</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E15" s="10">
-        <v>61.36</v>
+        <v>55.72</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>33</v>
@@ -4321,7 +4327,7 @@
         <v>33</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I15" s="10">
         <v>14</v>
@@ -4339,7 +4345,7 @@
         <v>6.86</v>
       </c>
       <c r="N15" s="10">
-        <v>5.02</v>
+        <v>4.39</v>
       </c>
       <c r="O15" s="10">
         <v>1120.18</v>
@@ -4356,13 +4362,13 @@
         <v>62</v>
       </c>
       <c r="C16" s="10">
-        <v>58.89</v>
+        <v>60.22</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E16" s="10">
-        <v>66.93000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>63</v>
@@ -4371,7 +4377,7 @@
         <v>52</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="I16" s="10">
         <v>12.77</v>
@@ -4389,7 +4395,7 @@
         <v>6.77</v>
       </c>
       <c r="N16" s="10">
-        <v>5.03</v>
+        <v>6.36</v>
       </c>
       <c r="O16" s="10">
         <v>1154.15</v>
@@ -4406,13 +4412,13 @@
         <v>64</v>
       </c>
       <c r="C17" s="10">
-        <v>52.60999999999999</v>
+        <v>53.57</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E17" s="10">
-        <v>43.88</v>
+        <v>45.84</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>57</v>
@@ -4439,7 +4445,7 @@
         <v>3.36</v>
       </c>
       <c r="N17" s="10">
-        <v>5.04</v>
+        <v>6</v>
       </c>
       <c r="O17" s="10">
         <v>1129.93</v>
@@ -4456,13 +4462,13 @@
         <v>65</v>
       </c>
       <c r="C18" s="10">
-        <v>53.12</v>
+        <v>52.15</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E18" s="10">
-        <v>45.97</v>
+        <v>41.76</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>57</v>
@@ -4471,7 +4477,7 @@
         <v>33</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I18" s="10">
         <v>16.31</v>
@@ -4489,7 +4495,7 @@
         <v>6.76</v>
       </c>
       <c r="N18" s="10">
-        <v>5.05</v>
+        <v>4.08</v>
       </c>
       <c r="O18" s="10">
         <v>1284.09</v>
@@ -4506,13 +4512,13 @@
         <v>66</v>
       </c>
       <c r="C19" s="10">
-        <v>55.39</v>
+        <v>56.26</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E19" s="10">
-        <v>54.51</v>
+        <v>54.84</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>33</v>
@@ -4521,7 +4527,7 @@
         <v>33</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I19" s="10">
         <v>14.83</v>
@@ -4539,7 +4545,7 @@
         <v>6.96</v>
       </c>
       <c r="N19" s="10">
-        <v>5.05</v>
+        <v>5.92</v>
       </c>
       <c r="O19" s="10">
         <v>1245.32</v>
@@ -4556,22 +4562,22 @@
         <v>67</v>
       </c>
       <c r="C20" s="10">
-        <v>54.38000000000001</v>
+        <v>54.14</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="10">
-        <v>50.47</v>
+        <v>47.88</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>33</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I20" s="10">
         <v>14.55</v>
@@ -4589,7 +4595,7 @@
         <v>7.53</v>
       </c>
       <c r="N20" s="10">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="O20" s="10">
         <v>1287.94</v>
@@ -4606,22 +4612,22 @@
         <v>68</v>
       </c>
       <c r="C21" s="10">
-        <v>55.02</v>
+        <v>54.26</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E21" s="10">
-        <v>53</v>
+        <v>48.34</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="G21" s="14" t="s">
         <v>33</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I21" s="10">
         <v>16.84</v>
@@ -4639,7 +4645,7 @@
         <v>4.73</v>
       </c>
       <c r="N21" s="10">
-        <v>5.07</v>
+        <v>4.31</v>
       </c>
       <c r="O21" s="10">
         <v>1266.78</v>
@@ -4656,19 +4662,19 @@
         <v>69</v>
       </c>
       <c r="C22" s="10">
-        <v>52.17</v>
+        <v>51.77</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E22" s="10">
-        <v>41.2</v>
+        <v>39.85</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H22" s="14" t="s">
         <v>46</v>
@@ -4689,7 +4695,7 @@
         <v>7.01</v>
       </c>
       <c r="N22" s="10">
-        <v>5.07</v>
+        <v>4.67</v>
       </c>
       <c r="O22" s="10">
         <v>1306.86</v>
@@ -4706,22 +4712,22 @@
         <v>70</v>
       </c>
       <c r="C23" s="10">
-        <v>50.97000000000001</v>
+        <v>51.63</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="10">
-        <v>36.51</v>
+        <v>39.78</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I23" s="10">
         <v>14.58</v>
@@ -4739,7 +4745,7 @@
         <v>4.67</v>
       </c>
       <c r="N23" s="10">
-        <v>5.07</v>
+        <v>5.73</v>
       </c>
       <c r="O23" s="10">
         <v>1376.07</v>
@@ -4756,13 +4762,13 @@
         <v>71</v>
       </c>
       <c r="C24" s="10">
-        <v>53.79000000000001</v>
+        <v>55.24</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E24" s="10">
-        <v>49.08</v>
+        <v>53.01</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>33</v>
@@ -4789,7 +4795,7 @@
         <v>6.97</v>
       </c>
       <c r="N24" s="10">
-        <v>5.25</v>
+        <v>6.7</v>
       </c>
       <c r="O24" s="10">
         <v>1661.7</v>
@@ -4806,22 +4812,22 @@
         <v>72</v>
       </c>
       <c r="C25" s="10">
-        <v>50.94</v>
+        <v>52.6</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E25" s="10">
-        <v>36.71</v>
+        <v>43.29</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I25" s="10">
         <v>13.06</v>
@@ -4839,7 +4845,7 @@
         <v>6.92</v>
       </c>
       <c r="N25" s="10">
-        <v>5.25</v>
+        <v>6.91</v>
       </c>
       <c r="O25" s="10">
         <v>1784.49</v>
@@ -4856,22 +4862,22 @@
         <v>73</v>
       </c>
       <c r="C26" s="10">
-        <v>52.59</v>
+        <v>51.31</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E26" s="10">
-        <v>44.52</v>
+        <v>38.67</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I26" s="10">
         <v>16.02</v>
@@ -4889,7 +4895,7 @@
         <v>4.89</v>
       </c>
       <c r="N26" s="10">
-        <v>5.25</v>
+        <v>3.97</v>
       </c>
       <c r="O26" s="10">
         <v>1674.49</v>
@@ -4906,22 +4912,22 @@
         <v>74</v>
       </c>
       <c r="C27" s="10">
-        <v>45.8</v>
+        <v>46.38</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>57</v>
       </c>
       <c r="E27" s="10">
-        <v>14.27</v>
+        <v>20.48</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I27" s="10">
         <v>11.71</v>
@@ -4939,7 +4945,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="10">
-        <v>5.25</v>
+        <v>5.83</v>
       </c>
       <c r="O27" s="10">
         <v>1860.01</v>
@@ -4948,7 +4954,7 @@
         <v>0.1107919426213355</v>
       </c>
       <c r="Q27" s="11">
-        <v>-0.04026860070644789</v>
+        <v>-0.0426503083316756</v>
       </c>
     </row>
     <row r="28" spans="2:17">
@@ -4956,22 +4962,22 @@
         <v>75</v>
       </c>
       <c r="C28" s="10">
-        <v>50.96999999999999</v>
+        <v>50.12</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E28" s="10">
-        <v>40.03</v>
+        <v>36.76</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I28" s="10">
         <v>14.41</v>
@@ -4989,13 +4995,13 @@
         <v>6.86</v>
       </c>
       <c r="N28" s="10">
-        <v>5.26</v>
+        <v>4.41</v>
       </c>
       <c r="O28" s="10">
-        <v>1785.11</v>
+        <v>1780.68</v>
       </c>
       <c r="P28" s="11">
-        <v>-0.04026860070644789</v>
+        <v>-0.0426503083316756</v>
       </c>
       <c r="Q28" s="14" t="s">
         <v>47</v>
@@ -5006,22 +5012,22 @@
         <v>76</v>
       </c>
       <c r="C29" s="10">
-        <v>49.73999999999999</v>
+        <v>49.35</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="10">
-        <v>35.27</v>
+        <v>34.51</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I29" s="10">
         <v>13.58</v>
@@ -5039,7 +5045,7 @@
         <v>2.59</v>
       </c>
       <c r="N29" s="10">
-        <v>6.39</v>
+        <v>6</v>
       </c>
       <c r="O29" s="14" t="s">
         <v>47</v>
@@ -5527,7 +5533,7 @@
         <v>51</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>56</v>
@@ -7220,7 +7226,7 @@
   <sheetPr>
     <tabColor rgb="FFF97316"/>
   </sheetPr>
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -7715,11 +7721,11 @@
       <c r="E28" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>193</v>
+      <c r="F28" s="10">
+        <v>38</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -7762,9 +7768,29 @@
         <v>187</v>
       </c>
     </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:G30"/>
-  <conditionalFormatting sqref="F6:F30">
+  <autoFilter ref="B5:G31"/>
+  <conditionalFormatting sqref="F6:F31">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7801,17 +7827,17 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C5" s="14">
         <v>22</v>
@@ -7819,39 +7845,39 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C6" s="16">
-        <v>0.004156386627439163</v>
+        <v>0.05191697881001582</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C7" s="16">
-        <v>0.01637492941840768</v>
+        <v>0.05138339920948617</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C8" s="16">
-        <v>0.02840623638565849</v>
+        <v>0.03936735417591136</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C9" s="16">
-        <v>0.09203839638622249</v>
+        <v>0.07735742518351214</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C10" s="11">
         <v>0.5</v>
@@ -7859,7 +7885,7 @@
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C11" s="11">
         <v>0.5454545454545454</v>
@@ -7867,64 +7893,64 @@
     </row>
     <row r="12" spans="2:3">
       <c r="B12" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C12" s="11">
-        <v>0.2004819890874032</v>
+        <v>0.1966701035922562</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C13" s="11">
-        <v>0.2503907960980185</v>
+        <v>0.249486451502519</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C14" s="11">
-        <v>0.4982793930034239</v>
+        <v>0.4945612032498485</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C15" s="10">
-        <v>0.4656941087978428</v>
+        <v>0.4590638734741476</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C16" s="10">
-        <v>0.4801617850137476</v>
+        <v>0.4775014136300051</v>
       </c>
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -7949,16 +7975,16 @@
         <v>33</v>
       </c>
       <c r="C21" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D21" s="11">
-        <v>0.02325036242226524</v>
+        <v>0.02672711655939455</v>
       </c>
       <c r="E21" s="11">
-        <v>0.03163927438071323</v>
+        <v>0.0342241351620467</v>
       </c>
       <c r="F21" s="11">
-        <v>0.6363636363636364</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -7966,30 +7992,30 @@
         <v>57</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" s="11">
-        <v>0.04364110592335368</v>
+        <v>0.03563307545264917</v>
       </c>
       <c r="E22" s="11">
-        <v>0.05295900096414319</v>
+        <v>0.03163927438071323</v>
       </c>
       <c r="F22" s="11">
-        <v>0.5714285714285714</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="14">
         <v>3</v>
       </c>
       <c r="D23" s="11">
-        <v>-0.01260270879374577</v>
+        <v>-0.01339661133548834</v>
       </c>
       <c r="E23" s="11">
-        <v>-0.04026860070644789</v>
+        <v>-0.0426503083316756</v>
       </c>
       <c r="F23" s="11">
         <v>0.3333333333333333</v>
@@ -7997,7 +8023,7 @@
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -8005,34 +8031,34 @@
         <v>36</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -8040,7 +8066,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="10">
-        <v>61.41</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>33</v>
@@ -8049,7 +8075,7 @@
         <v>0.5</v>
       </c>
       <c r="F27" s="10">
-        <v>61.41</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>33</v>
@@ -8061,7 +8087,7 @@
         <v>0.0911124353723225</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K27" s="10">
         <v>109.1112435372323</v>
@@ -8075,7 +8101,7 @@
         <v>48</v>
       </c>
       <c r="C28" s="10">
-        <v>52.98</v>
+        <v>55.19</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>33</v>
@@ -8084,7 +8110,7 @@
         <v>0.5</v>
       </c>
       <c r="F28" s="10">
-        <v>52.98</v>
+        <v>55.19</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>33</v>
@@ -8096,7 +8122,7 @@
         <v>-0.02360228603883424</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K28" s="10">
         <v>106.5359687572136</v>
@@ -8110,7 +8136,7 @@
         <v>49</v>
       </c>
       <c r="C29" s="10">
-        <v>54.28</v>
+        <v>54.94</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>33</v>
@@ -8119,7 +8145,7 @@
         <v>0.5</v>
       </c>
       <c r="F29" s="10">
-        <v>54.28</v>
+        <v>54.94</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>33</v>
@@ -8131,7 +8157,7 @@
         <v>0.05820157071963994</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K29" s="10">
         <v>112.7365294770219</v>
@@ -8145,7 +8171,7 @@
         <v>50</v>
       </c>
       <c r="C30" s="10">
-        <v>52.83</v>
+        <v>52.61</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>33</v>
@@ -8154,7 +8180,7 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="10">
-        <v>52.83</v>
+        <v>52.61</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>33</v>
@@ -8166,7 +8192,7 @@
         <v>-0.002045679045305226</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K30" s="10">
         <v>112.5059067210303</v>
@@ -8180,7 +8206,7 @@
         <v>51</v>
       </c>
       <c r="C31" s="10">
-        <v>63.34</v>
+        <v>62.17</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>33</v>
@@ -8189,7 +8215,7 @@
         <v>0.5</v>
       </c>
       <c r="F31" s="10">
-        <v>59</v>
+        <v>60.76</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>33</v>
@@ -8201,7 +8227,7 @@
         <v>-0.09869986261434849</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K31" s="10">
         <v>101.4015891843619</v>
@@ -8212,19 +8238,19 @@
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" s="10">
-        <v>27.45</v>
+        <v>26.12</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E32" s="9">
         <v>0.1</v>
       </c>
       <c r="F32" s="10">
-        <v>50.26000000000001</v>
+        <v>50</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>33</v>
@@ -8236,7 +8262,7 @@
         <v>-0.005468436873747495</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K32" s="10">
         <v>100.8470809950096</v>
@@ -8250,7 +8276,7 @@
         <v>56</v>
       </c>
       <c r="C33" s="10">
-        <v>39.08</v>
+        <v>35.08</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>57</v>
@@ -8259,7 +8285,7 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="10">
-        <v>52.06</v>
+        <v>51.07</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>33</v>
@@ -8271,7 +8297,7 @@
         <v>-0.03312928955666848</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K33" s="10">
         <v>97.50608884778109</v>
@@ -8285,16 +8311,16 @@
         <v>59</v>
       </c>
       <c r="C34" s="10">
-        <v>17.89</v>
+        <v>21.68</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E34" s="9">
         <v>0.1</v>
       </c>
       <c r="F34" s="10">
-        <v>46.09</v>
+        <v>45.8</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>57</v>
@@ -8306,7 +8332,7 @@
         <v>0.005714484306268553</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K34" s="10">
         <v>98.06328586226736</v>
@@ -8320,7 +8346,7 @@
         <v>60</v>
       </c>
       <c r="C35" s="10">
-        <v>50.11</v>
+        <v>49.98</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>33</v>
@@ -8329,7 +8355,7 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="10">
-        <v>53.65000000000001</v>
+        <v>54.29</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>33</v>
@@ -8340,8 +8366,8 @@
       <c r="I35" s="11">
         <v>0.02608393447550339</v>
       </c>
-      <c r="J35" s="17" t="s">
-        <v>263</v>
+      <c r="J35" s="13" t="s">
+        <v>266</v>
       </c>
       <c r="K35" s="10">
         <v>100.6211621851513</v>
@@ -8355,7 +8381,7 @@
         <v>61</v>
       </c>
       <c r="C36" s="10">
-        <v>61.36</v>
+        <v>55.72</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>33</v>
@@ -8364,7 +8390,7 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="10">
-        <v>57.02</v>
+        <v>56.39</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>33</v>
@@ -8376,7 +8402,7 @@
         <v>0.01516274170222642</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K36" s="10">
         <v>102.1468548771426</v>
@@ -8390,7 +8416,7 @@
         <v>62</v>
       </c>
       <c r="C37" s="10">
-        <v>66.93000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>63</v>
@@ -8399,7 +8425,7 @@
         <v>0.775</v>
       </c>
       <c r="F37" s="10">
-        <v>58.89</v>
+        <v>60.22</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>33</v>
@@ -8411,7 +8437,7 @@
         <v>-0.01626348394922673</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K37" s="10">
         <v>100.4855911423842</v>
@@ -8425,7 +8451,7 @@
         <v>64</v>
       </c>
       <c r="C38" s="10">
-        <v>43.88</v>
+        <v>45.84</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>57</v>
@@ -8434,7 +8460,7 @@
         <v>0.3</v>
       </c>
       <c r="F38" s="10">
-        <v>52.60999999999999</v>
+        <v>53.57</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>33</v>
@@ -8446,7 +8472,7 @@
         <v>0.04092996911313089</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K38" s="10">
         <v>104.5984632841567</v>
@@ -8460,7 +8486,7 @@
         <v>65</v>
       </c>
       <c r="C39" s="10">
-        <v>45.97</v>
+        <v>41.76</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>57</v>
@@ -8469,7 +8495,7 @@
         <v>0.3</v>
       </c>
       <c r="F39" s="10">
-        <v>53.12</v>
+        <v>52.15</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>33</v>
@@ -8481,7 +8507,7 @@
         <v>-0.009057776324089427</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K39" s="10">
         <v>103.6510337998853</v>
@@ -8495,7 +8521,7 @@
         <v>66</v>
       </c>
       <c r="C40" s="10">
-        <v>54.51</v>
+        <v>54.84</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>33</v>
@@ -8504,7 +8530,7 @@
         <v>0.5</v>
       </c>
       <c r="F40" s="10">
-        <v>55.39</v>
+        <v>56.26</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>33</v>
@@ -8516,7 +8542,7 @@
         <v>0.01711206758102335</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K40" s="10">
         <v>105.4247172951119</v>
@@ -8530,16 +8556,16 @@
         <v>67</v>
       </c>
       <c r="C41" s="10">
-        <v>50.47</v>
+        <v>47.88</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E41" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F41" s="10">
-        <v>54.38000000000001</v>
+        <v>54.14</v>
       </c>
       <c r="G41" s="14" t="s">
         <v>33</v>
@@ -8548,13 +8574,13 @@
         <v>-0.01642933677034653</v>
       </c>
       <c r="I41" s="11">
-        <v>-0.008214668385173263</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>264</v>
+        <v>-0.004928801031103957</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="K41" s="10">
-        <v>104.5586882029319</v>
+        <v>104.9050998398039</v>
       </c>
       <c r="L41" s="10">
         <v>106.3234405425367</v>
@@ -8565,16 +8591,16 @@
         <v>68</v>
       </c>
       <c r="C42" s="10">
-        <v>53</v>
+        <v>48.34</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E42" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F42" s="10">
-        <v>55.02</v>
+        <v>54.26</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>33</v>
@@ -8583,13 +8609,13 @@
         <v>0.03163927438071323</v>
       </c>
       <c r="I42" s="11">
-        <v>0.01581963719035662</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>263</v>
+        <v>0.00949178231421397</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>266</v>
       </c>
       <c r="K42" s="10">
-        <v>106.2127687154019</v>
+        <v>105.9008362111342</v>
       </c>
       <c r="L42" s="10">
         <v>109.6874370509635</v>
@@ -8600,7 +8626,7 @@
         <v>69</v>
       </c>
       <c r="C43" s="10">
-        <v>41.2</v>
+        <v>39.85</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>57</v>
@@ -8609,7 +8635,7 @@
         <v>0.3</v>
       </c>
       <c r="F43" s="10">
-        <v>52.17</v>
+        <v>51.77</v>
       </c>
       <c r="G43" s="14" t="s">
         <v>33</v>
@@ -8621,10 +8647,10 @@
         <v>0.01588770028924296</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K43" s="10">
-        <v>107.9002453516429</v>
+        <v>107.5833569572369</v>
       </c>
       <c r="L43" s="10">
         <v>115.4963741354999</v>
@@ -8635,7 +8661,7 @@
         <v>70</v>
       </c>
       <c r="C44" s="10">
-        <v>36.51</v>
+        <v>39.78</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>57</v>
@@ -8644,7 +8670,7 @@
         <v>0.3</v>
       </c>
       <c r="F44" s="10">
-        <v>50.97000000000001</v>
+        <v>51.63</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>33</v>
@@ -8656,10 +8682,10 @@
         <v>0.0622708147114609</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K44" s="10">
-        <v>114.6192815372562</v>
+        <v>114.2826602443579</v>
       </c>
       <c r="L44" s="10">
         <v>139.4698851809575</v>
@@ -8670,7 +8696,7 @@
         <v>71</v>
       </c>
       <c r="C45" s="10">
-        <v>49.08</v>
+        <v>53.01</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>33</v>
@@ -8679,7 +8705,7 @@
         <v>0.5</v>
       </c>
       <c r="F45" s="10">
-        <v>53.79000000000001</v>
+        <v>55.24</v>
       </c>
       <c r="G45" s="14" t="s">
         <v>33</v>
@@ -8690,11 +8716,11 @@
       <c r="I45" s="11">
         <v>0.03694710236504783</v>
       </c>
-      <c r="J45" s="13" t="s">
-        <v>264</v>
+      <c r="J45" s="17" t="s">
+        <v>265</v>
       </c>
       <c r="K45" s="10">
-        <v>118.8541318652214</v>
+        <v>118.5050733909562</v>
       </c>
       <c r="L45" s="10">
         <v>149.7759014302021</v>
@@ -8705,7 +8731,7 @@
         <v>72</v>
       </c>
       <c r="C46" s="10">
-        <v>36.71</v>
+        <v>43.29</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>57</v>
@@ -8714,7 +8740,7 @@
         <v>0.3</v>
       </c>
       <c r="F46" s="10">
-        <v>50.94</v>
+        <v>52.6</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>33</v>
@@ -8726,10 +8752,10 @@
         <v>-0.01849267858043475</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K46" s="10">
-        <v>116.6562006066813</v>
+        <v>116.3135971585864</v>
       </c>
       <c r="L46" s="10">
         <v>140.5433760827234</v>
@@ -8740,7 +8766,7 @@
         <v>73</v>
       </c>
       <c r="C47" s="10">
-        <v>44.52</v>
+        <v>38.67</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>57</v>
@@ -8749,7 +8775,7 @@
         <v>0.3</v>
       </c>
       <c r="F47" s="10">
-        <v>52.59</v>
+        <v>51.31</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>33</v>
@@ -8761,10 +8787,10 @@
         <v>0.03323758278640065</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K47" s="10">
-        <v>120.5335707318928</v>
+        <v>120.179579973329</v>
       </c>
       <c r="L47" s="10">
         <v>156.1144497414892</v>
@@ -8775,39 +8801,39 @@
         <v>74</v>
       </c>
       <c r="C48" s="10">
-        <v>14.27</v>
+        <v>20.48</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E48" s="9">
         <v>0.1</v>
       </c>
       <c r="F48" s="10">
-        <v>45.8</v>
+        <v>46.38</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>57</v>
       </c>
       <c r="H48" s="11">
-        <v>-0.04026860070644789</v>
+        <v>-0.0426503083316756</v>
       </c>
       <c r="I48" s="11">
-        <v>-0.004026860070644789</v>
+        <v>-0.004265030833167561</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K48" s="10">
-        <v>120.0481989087403</v>
+        <v>119.6670103592256</v>
       </c>
       <c r="L48" s="10">
-        <v>149.8279393003424</v>
+        <v>149.4561203249849</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="19" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -8833,7 +8859,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -8894,104 +8920,104 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -9002,10 +9028,10 @@
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -9016,10 +9042,10 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -9030,10 +9056,10 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -9044,10 +9070,10 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -9058,10 +9084,10 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -9072,10 +9098,10 @@
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -9086,10 +9112,10 @@
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -9100,10 +9126,10 @@
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -29,7 +29,7 @@
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 11:09:13  |  Source: output/exports/score_*.json</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 11:15:45  |  Source: output/exports/score_*.json</t>
   </si>
   <si>
     <t>49.4</t>
@@ -38,19 +38,19 @@
     <t>Raw Regime / Label</t>
   </si>
   <si>
-    <t>🟡 HOLD (raw composite)</t>
+    <t>🟠 REDUCE (raw composite)</t>
   </si>
   <si>
     <t>CALIBRATED ACTION</t>
   </si>
   <si>
-    <t>🟡 HOLD — 34.5</t>
+    <t>🔴 SELL — 34.5</t>
   </si>
   <si>
     <t>Recommended Equity</t>
   </si>
   <si>
-    <t>40–60% Equities (calibrated)</t>
+    <t>0–20% Equities (calibrated)</t>
   </si>
   <si>
     <t>Percentile Signal</t>
@@ -125,45 +125,48 @@
     <t>TOTAL COMPOSITE</t>
   </si>
   <si>
+    <t>REDUCE</t>
+  </si>
+  <si>
+    <t>COMPOSITE SCORE HISTORY vs VN-INDEX</t>
+  </si>
+  <si>
+    <t>Two-tier scores: Total Score = raw composite (reference) | Calibrated Score = action signal (z-score vs prior quarters, point-in-time). Pillar columns are weighted contributions (raw × weight). Fwd Return = VN-Index return of the NEXT quarter (signal evaluation).</t>
+  </si>
+  <si>
+    <t>Quarter</t>
+  </si>
+  <si>
+    <t>Total Score</t>
+  </si>
+  <si>
+    <t>Label (Raw)</t>
+  </si>
+  <si>
+    <t>Calibrated Score</t>
+  </si>
+  <si>
+    <t>Calibrated Label</t>
+  </si>
+  <si>
+    <t>Dispersion</t>
+  </si>
+  <si>
+    <t>VN-Index Close</t>
+  </si>
+  <si>
+    <t>QoQ Return</t>
+  </si>
+  <si>
+    <t>Fwd Return (t+1)</t>
+  </si>
+  <si>
+    <t>2021-Q1</t>
+  </si>
+  <si>
     <t>HOLD</t>
   </si>
   <si>
-    <t>COMPOSITE SCORE HISTORY vs VN-INDEX</t>
-  </si>
-  <si>
-    <t>Two-tier scores: Total Score = raw composite (reference) | Calibrated Score = action signal (z-score vs prior quarters, point-in-time). Pillar columns are weighted contributions (raw × weight). Fwd Return = VN-Index return of the NEXT quarter (signal evaluation).</t>
-  </si>
-  <si>
-    <t>Quarter</t>
-  </si>
-  <si>
-    <t>Total Score</t>
-  </si>
-  <si>
-    <t>Label (Raw)</t>
-  </si>
-  <si>
-    <t>Calibrated Score</t>
-  </si>
-  <si>
-    <t>Calibrated Label</t>
-  </si>
-  <si>
-    <t>Dispersion</t>
-  </si>
-  <si>
-    <t>VN-Index Close</t>
-  </si>
-  <si>
-    <t>QoQ Return</t>
-  </si>
-  <si>
-    <t>Fwd Return (t+1)</t>
-  </si>
-  <si>
-    <t>2021-Q1</t>
-  </si>
-  <si>
     <t>MEDIUM</t>
   </si>
   <si>
@@ -197,9 +200,6 @@
     <t>2022-Q3</t>
   </si>
   <si>
-    <t>REDUCE</t>
-  </si>
-  <si>
     <t>HIGH</t>
   </si>
   <si>
@@ -932,7 +932,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 11:09:13 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 11:15:45 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -2754,46 +2754,46 @@
                   <c:v>98.06328586226736</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>100.6211621851513</c:v>
+                  <c:v>99.59801165599774</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>102.1468548771426</c:v>
+                  <c:v>101.108190580793</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>100.4855911423842</c:v>
+                  <c:v>99.46381914614688</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>104.5984632841567</c:v>
+                  <c:v>103.5348701916727</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>103.6510337998853</c:v>
+                  <c:v>102.5970744957329</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>105.4247172951119</c:v>
+                  <c:v>104.3527225681192</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>104.9050998398039</c:v>
+                  <c:v>103.8383887615269</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>105.9008362111342</c:v>
+                  <c:v>104.8240001435101</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>107.5833569572369</c:v>
+                  <c:v>106.4894124409097</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>114.2826602443579</c:v>
+                  <c:v>113.1205949117499</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>118.5050733909562</c:v>
+                  <c:v>117.3000731115495</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>116.3135971585864</c:v>
+                  <c:v>115.1308805620361</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>120.179579973329</c:v>
+                  <c:v>118.957552735988</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>119.6670103592256</c:v>
+                  <c:v>118.4501951057308</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3865,19 +3865,19 @@
         <v>64.01000000000001</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E6" s="10">
         <v>64.01000000000001</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I6" s="10">
         <v>14.51</v>
@@ -3901,7 +3901,7 @@
         <v>1191.44</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="11">
         <v>0.182224870744645</v>
@@ -3909,25 +3909,25 @@
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="10">
         <v>55.19</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10">
         <v>55.19</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" s="10">
         <v>12.05</v>
@@ -3959,25 +3959,25 @@
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="10">
         <v>54.94</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E8" s="10">
         <v>54.94</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I8" s="10">
         <v>12.37</v>
@@ -4009,25 +4009,25 @@
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="10">
         <v>52.61</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E9" s="10">
         <v>52.61</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I9" s="10">
         <v>12.99</v>
@@ -4059,25 +4059,25 @@
     </row>
     <row r="10" spans="2:17">
       <c r="B10" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C10" s="10">
         <v>60.76</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E10" s="10">
         <v>62.17</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I10" s="10">
         <v>12.54</v>
@@ -4109,25 +4109,25 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" s="10">
         <v>50</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10">
         <v>26.12</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I11" s="10">
         <v>11.73</v>
@@ -4159,19 +4159,19 @@
     </row>
     <row r="12" spans="2:17">
       <c r="B12" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="10">
         <v>51.07</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E12" s="10">
         <v>35.08</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>10</v>
@@ -4215,19 +4215,19 @@
         <v>45.8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E13" s="10">
         <v>21.68</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I13" s="10">
         <v>9.34</v>
@@ -4265,7 +4265,7 @@
         <v>54.29</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E14" s="10">
         <v>49.98</v>
@@ -4274,10 +4274,10 @@
         <v>33</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I14" s="10">
         <v>12.48</v>
@@ -4315,19 +4315,19 @@
         <v>56.39</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E15" s="10">
         <v>55.72</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I15" s="10">
         <v>14</v>
@@ -4365,7 +4365,7 @@
         <v>60.22</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E16" s="10">
         <v>66.42</v>
@@ -4374,10 +4374,10 @@
         <v>63</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I16" s="10">
         <v>12.77</v>
@@ -4415,19 +4415,19 @@
         <v>53.57</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E17" s="10">
         <v>45.84</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I17" s="10">
         <v>13.95</v>
@@ -4465,16 +4465,16 @@
         <v>52.15</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E18" s="10">
         <v>41.76</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H18" s="14" t="s">
         <v>58</v>
@@ -4515,19 +4515,19 @@
         <v>56.26</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E19" s="10">
         <v>54.84</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I19" s="10">
         <v>14.83</v>
@@ -4565,19 +4565,19 @@
         <v>54.14</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E20" s="10">
         <v>47.88</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I20" s="10">
         <v>14.55</v>
@@ -4615,19 +4615,19 @@
         <v>54.26</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E21" s="10">
         <v>48.34</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I21" s="10">
         <v>16.84</v>
@@ -4665,19 +4665,19 @@
         <v>51.77</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E22" s="10">
         <v>39.85</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I22" s="10">
         <v>14.59</v>
@@ -4715,19 +4715,19 @@
         <v>51.63</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E23" s="10">
         <v>39.78</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I23" s="10">
         <v>14.58</v>
@@ -4765,19 +4765,19 @@
         <v>55.24</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E24" s="10">
         <v>53.01</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" s="10">
         <v>13.39</v>
@@ -4815,16 +4815,16 @@
         <v>52.6</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E25" s="10">
         <v>43.29</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>58</v>
@@ -4865,13 +4865,13 @@
         <v>51.31</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E26" s="10">
         <v>38.67</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>10</v>
@@ -4915,13 +4915,13 @@
         <v>46.38</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E27" s="10">
         <v>20.48</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>10</v>
@@ -4965,13 +4965,13 @@
         <v>50.12</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E28" s="10">
         <v>36.76</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>10</v>
@@ -5004,7 +5004,7 @@
         <v>-0.0426503083316756</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -5021,7 +5021,7 @@
         <v>34.51</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
@@ -5048,13 +5048,13 @@
         <v>6</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -5521,22 +5521,22 @@
         <v>45</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>59</v>
@@ -7339,7 +7339,7 @@
         <v>192</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F9" s="10">
         <v>50</v>
@@ -7896,7 +7896,7 @@
         <v>245</v>
       </c>
       <c r="C12" s="11">
-        <v>0.1966701035922562</v>
+        <v>0.1845019510573085</v>
       </c>
     </row>
     <row r="13" spans="2:3">
@@ -7920,7 +7920,7 @@
         <v>248</v>
       </c>
       <c r="C15" s="10">
-        <v>0.4590638734741476</v>
+        <v>0.4364053247997207</v>
       </c>
     </row>
     <row r="16" spans="2:3">
@@ -7972,41 +7972,41 @@
     </row>
     <row r="21" spans="2:12">
       <c r="B21" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C21" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="11">
-        <v>0.02672711655939455</v>
+        <v>0.02354702251044302</v>
       </c>
       <c r="E21" s="11">
-        <v>0.0342241351620467</v>
+        <v>0.03227480928324977</v>
       </c>
       <c r="F21" s="11">
-        <v>0.6666666666666666</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="C22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="11">
-        <v>0.03563307545264917</v>
+        <v>0.03728655480248493</v>
       </c>
       <c r="E22" s="11">
-        <v>0.03163927438071323</v>
+        <v>0.04190357166586001</v>
       </c>
       <c r="F22" s="11">
-        <v>0.5555555555555556</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="14">
         <v>3</v>
@@ -8069,7 +8069,7 @@
         <v>64.01000000000001</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E27" s="9">
         <v>0.5</v>
@@ -8078,7 +8078,7 @@
         <v>64.01000000000001</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H27" s="11">
         <v>0.182224870744645</v>
@@ -8098,13 +8098,13 @@
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28" s="10">
         <v>55.19</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E28" s="9">
         <v>0.5</v>
@@ -8113,7 +8113,7 @@
         <v>55.19</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H28" s="11">
         <v>-0.04720457207766848</v>
@@ -8133,13 +8133,13 @@
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C29" s="10">
         <v>54.94</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E29" s="9">
         <v>0.5</v>
@@ -8148,7 +8148,7 @@
         <v>54.94</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H29" s="11">
         <v>0.1164031414392799</v>
@@ -8168,13 +8168,13 @@
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30" s="10">
         <v>52.61</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E30" s="9">
         <v>0.5</v>
@@ -8183,7 +8183,7 @@
         <v>52.61</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H30" s="11">
         <v>-0.004091358090610453</v>
@@ -8203,13 +8203,13 @@
     </row>
     <row r="31" spans="2:12">
       <c r="B31" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C31" s="10">
         <v>62.17</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E31" s="9">
         <v>0.5</v>
@@ -8218,7 +8218,7 @@
         <v>60.76</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H31" s="11">
         <v>-0.197399725228697</v>
@@ -8238,13 +8238,13 @@
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C32" s="10">
         <v>26.12</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E32" s="9">
         <v>0.1</v>
@@ -8253,7 +8253,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H32" s="11">
         <v>-0.05468436873747495</v>
@@ -8273,13 +8273,13 @@
     </row>
     <row r="33" spans="2:12">
       <c r="B33" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C33" s="10">
         <v>35.08</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E33" s="9">
         <v>0.3</v>
@@ -8288,7 +8288,7 @@
         <v>51.07</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H33" s="11">
         <v>-0.1104309651888949</v>
@@ -8314,7 +8314,7 @@
         <v>21.68</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E34" s="9">
         <v>0.1</v>
@@ -8323,7 +8323,7 @@
         <v>45.8</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="H34" s="11">
         <v>0.05714484306268552</v>
@@ -8352,25 +8352,25 @@
         <v>33</v>
       </c>
       <c r="E35" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F35" s="10">
         <v>54.29</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H35" s="11">
         <v>0.05216786895100678</v>
       </c>
       <c r="I35" s="11">
-        <v>0.02608393447550339</v>
+        <v>0.01565036068530203</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>266</v>
       </c>
       <c r="K35" s="10">
-        <v>100.6211621851513</v>
+        <v>99.59801165599774</v>
       </c>
       <c r="L35" s="10">
         <v>94.01900221580608</v>
@@ -8384,7 +8384,7 @@
         <v>55.72</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E36" s="9">
         <v>0.5</v>
@@ -8393,7 +8393,7 @@
         <v>56.39</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H36" s="11">
         <v>0.03032548340445285</v>
@@ -8405,7 +8405,7 @@
         <v>265</v>
       </c>
       <c r="K36" s="10">
-        <v>102.1468548771426</v>
+        <v>101.108190580793</v>
       </c>
       <c r="L36" s="10">
         <v>96.87017390720473</v>
@@ -8428,7 +8428,7 @@
         <v>60.22</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H37" s="11">
         <v>-0.0209851405796474</v>
@@ -8440,7 +8440,7 @@
         <v>266</v>
       </c>
       <c r="K37" s="10">
-        <v>100.4855911423842</v>
+        <v>99.46381914614688</v>
       </c>
       <c r="L37" s="10">
         <v>94.83733968978714</v>
@@ -8454,7 +8454,7 @@
         <v>45.84</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E38" s="9">
         <v>0.3</v>
@@ -8463,7 +8463,7 @@
         <v>53.57</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H38" s="11">
         <v>0.136433230377103</v>
@@ -8475,7 +8475,7 @@
         <v>266</v>
       </c>
       <c r="K38" s="10">
-        <v>104.5984632841567</v>
+        <v>103.5348701916727</v>
       </c>
       <c r="L38" s="10">
         <v>107.7763043040354</v>
@@ -8489,7 +8489,7 @@
         <v>41.76</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E39" s="9">
         <v>0.3</v>
@@ -8498,7 +8498,7 @@
         <v>52.15</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H39" s="11">
         <v>-0.03019258774696476</v>
@@ -8510,7 +8510,7 @@
         <v>265</v>
       </c>
       <c r="K39" s="10">
-        <v>103.6510337998853</v>
+        <v>102.5970744957329</v>
       </c>
       <c r="L39" s="10">
         <v>104.5222587792923</v>
@@ -8524,7 +8524,7 @@
         <v>54.84</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E40" s="9">
         <v>0.5</v>
@@ -8533,7 +8533,7 @@
         <v>56.26</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H40" s="11">
         <v>0.0342241351620467</v>
@@ -8545,7 +8545,7 @@
         <v>265</v>
       </c>
       <c r="K40" s="10">
-        <v>105.4247172951119</v>
+        <v>104.3527225681192</v>
       </c>
       <c r="L40" s="10">
         <v>108.0994426911972</v>
@@ -8559,7 +8559,7 @@
         <v>47.88</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E41" s="9">
         <v>0.3</v>
@@ -8568,7 +8568,7 @@
         <v>54.14</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H41" s="11">
         <v>-0.01642933677034653</v>
@@ -8580,7 +8580,7 @@
         <v>265</v>
       </c>
       <c r="K41" s="10">
-        <v>104.9050998398039</v>
+        <v>103.8383887615269</v>
       </c>
       <c r="L41" s="10">
         <v>106.3234405425367</v>
@@ -8594,7 +8594,7 @@
         <v>48.34</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E42" s="9">
         <v>0.3</v>
@@ -8603,7 +8603,7 @@
         <v>54.26</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H42" s="11">
         <v>0.03163927438071323</v>
@@ -8615,7 +8615,7 @@
         <v>266</v>
       </c>
       <c r="K42" s="10">
-        <v>105.9008362111342</v>
+        <v>104.8240001435101</v>
       </c>
       <c r="L42" s="10">
         <v>109.6874370509635</v>
@@ -8629,7 +8629,7 @@
         <v>39.85</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E43" s="9">
         <v>0.3</v>
@@ -8638,7 +8638,7 @@
         <v>51.77</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H43" s="11">
         <v>0.05295900096414319</v>
@@ -8650,7 +8650,7 @@
         <v>266</v>
       </c>
       <c r="K43" s="10">
-        <v>107.5833569572369</v>
+        <v>106.4894124409097</v>
       </c>
       <c r="L43" s="10">
         <v>115.4963741354999</v>
@@ -8664,7 +8664,7 @@
         <v>39.78</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E44" s="9">
         <v>0.3</v>
@@ -8673,7 +8673,7 @@
         <v>51.63</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H44" s="11">
         <v>0.2075693823715363</v>
@@ -8685,7 +8685,7 @@
         <v>266</v>
       </c>
       <c r="K44" s="10">
-        <v>114.2826602443579</v>
+        <v>113.1205949117499</v>
       </c>
       <c r="L44" s="10">
         <v>139.4698851809575</v>
@@ -8699,7 +8699,7 @@
         <v>53.01</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E45" s="9">
         <v>0.5</v>
@@ -8708,7 +8708,7 @@
         <v>55.24</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H45" s="11">
         <v>0.07389420473009567</v>
@@ -8720,7 +8720,7 @@
         <v>265</v>
       </c>
       <c r="K45" s="10">
-        <v>118.5050733909562</v>
+        <v>117.3000731115495</v>
       </c>
       <c r="L45" s="10">
         <v>149.7759014302021</v>
@@ -8734,7 +8734,7 @@
         <v>43.29</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E46" s="9">
         <v>0.3</v>
@@ -8743,7 +8743,7 @@
         <v>52.6</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H46" s="11">
         <v>-0.06164226193478251</v>
@@ -8755,7 +8755,7 @@
         <v>265</v>
       </c>
       <c r="K46" s="10">
-        <v>116.3135971585864</v>
+        <v>115.1308805620361</v>
       </c>
       <c r="L46" s="10">
         <v>140.5433760827234</v>
@@ -8769,7 +8769,7 @@
         <v>38.67</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="E47" s="9">
         <v>0.3</v>
@@ -8778,7 +8778,7 @@
         <v>51.31</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H47" s="11">
         <v>0.1107919426213355</v>
@@ -8790,7 +8790,7 @@
         <v>266</v>
       </c>
       <c r="K47" s="10">
-        <v>120.179579973329</v>
+        <v>118.957552735988</v>
       </c>
       <c r="L47" s="10">
         <v>156.1144497414892</v>
@@ -8804,7 +8804,7 @@
         <v>20.48</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E48" s="9">
         <v>0.1</v>
@@ -8813,7 +8813,7 @@
         <v>46.38</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="H48" s="11">
         <v>-0.0426503083316756</v>
@@ -8825,7 +8825,7 @@
         <v>265</v>
       </c>
       <c r="K48" s="10">
-        <v>119.6670103592256</v>
+        <v>118.4501951057308</v>
       </c>
       <c r="L48" s="10">
         <v>149.4561203249849</v>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -29,7 +29,7 @@
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 11:15:45  |  Source: output/exports/score_*.json</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 11:17:50  |  Source: output/exports/score_*.json</t>
   </si>
   <si>
     <t>49.4</t>
@@ -932,7 +932,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 11:15:45 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 11:17:50 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -17,22 +17,22 @@
     <sheet name="07_Methodology" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Factor_Scores'!$B$5:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Factor_Scores'!$B$5:$G$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="305">
   <si>
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 11:17:50  |  Source: output/exports/score_*.json</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 12:05:04  |  Source: output/exports/score_*.json</t>
+  </si>
+  <si>
+    <t>47.3</t>
   </si>
   <si>
     <t>Raw Regime / Label</t>
@@ -44,7 +44,7 @@
     <t>CALIBRATED ACTION</t>
   </si>
   <si>
-    <t>🔴 SELL — 34.5</t>
+    <t>🔴 SELL — 28.2</t>
   </si>
   <si>
     <t>Recommended Equity</t>
@@ -62,7 +62,7 @@
     <t>Pillar Dispersion</t>
   </si>
   <si>
-    <t>HIGH (σ=13.61)</t>
+    <t>MEDIUM (σ=13.47)</t>
   </si>
   <si>
     <t>Data As-Of</t>
@@ -164,6 +164,9 @@
     <t>2021-Q1</t>
   </si>
   <si>
+    <t>ACCUMULATE</t>
+  </si>
+  <si>
     <t>HOLD</t>
   </si>
   <si>
@@ -185,24 +188,21 @@
     <t>2022-Q1</t>
   </si>
   <si>
-    <t>BUY/ACCUMULATE</t>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>2022-Q2</t>
+  </si>
+  <si>
+    <t>SELL</t>
+  </si>
+  <si>
+    <t>2022-Q3</t>
   </si>
   <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>2022-Q2</t>
-  </si>
-  <si>
-    <t>SELL</t>
-  </si>
-  <si>
-    <t>2022-Q3</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>2022-Q4</t>
   </si>
   <si>
@@ -215,9 +215,6 @@
     <t>2023-Q3</t>
   </si>
   <si>
-    <t>ACCUMULATE</t>
-  </si>
-  <si>
     <t>2023-Q4</t>
   </si>
   <si>
@@ -605,7 +602,7 @@
     <t>m2_yoy_growth</t>
   </si>
   <si>
-    <t>MISSING</t>
+    <t>15.0% YoY</t>
   </si>
   <si>
     <t>vn_bonds</t>
@@ -662,6 +659,12 @@
     <t>Risk = 20/100 (SAFE)</t>
   </si>
   <si>
+    <t>eyg_zscore</t>
+  </si>
+  <si>
+    <t>EYG Z-score = -1.25</t>
+  </si>
+  <si>
     <t>mlr_forecast</t>
   </si>
   <si>
@@ -932,7 +935,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 11:17:50 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 12:05:04 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1283,13 +1286,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>13.58</c:v>
+                  <c:v>14.48</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>7.44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.5</c:v>
+                  <c:v>8.57</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>8.24</c:v>
@@ -1473,76 +1476,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>64.01000000000001</c:v>
+                  <c:v>70.13</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55.19</c:v>
+                  <c:v>61.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.94</c:v>
+                  <c:v>60.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.61</c:v>
+                  <c:v>58.17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>62.17</c:v>
+                  <c:v>46.08</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26.12</c:v>
+                  <c:v>11.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35.08</c:v>
+                  <c:v>43.58</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21.68</c:v>
+                  <c:v>22.14</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>49.98</c:v>
+                  <c:v>52.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>55.72</c:v>
+                  <c:v>52.96</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>66.42</c:v>
+                  <c:v>51.43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>45.84</c:v>
+                  <c:v>32.74</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>41.76</c:v>
+                  <c:v>30.74</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>54.84</c:v>
+                  <c:v>46.17</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>47.88</c:v>
+                  <c:v>40.55</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>48.34</c:v>
+                  <c:v>41.03</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>39.85</c:v>
+                  <c:v>35.01</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>39.78</c:v>
+                  <c:v>35.27</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>53.01</c:v>
+                  <c:v>46.39</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>43.29</c:v>
+                  <c:v>39.19</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>38.67</c:v>
+                  <c:v>33.62</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>20.48</c:v>
+                  <c:v>16.99</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>36.76</c:v>
+                  <c:v>30.46</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>34.51</c:v>
+                  <c:v>28.24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1652,76 +1655,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>64.01000000000001</c:v>
+                  <c:v>70.13</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55.19</c:v>
+                  <c:v>61.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.94</c:v>
+                  <c:v>60.67</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.61</c:v>
+                  <c:v>58.17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60.76</c:v>
+                  <c:v>61.19</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50</c:v>
+                  <c:v>50.64</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>51.07</c:v>
+                  <c:v>57.66</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>45.8</c:v>
+                  <c:v>49.17</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54.29</c:v>
+                  <c:v>59.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>56.39</c:v>
+                  <c:v>59.94</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>60.22</c:v>
+                  <c:v>59.4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>53.57</c:v>
+                  <c:v>52.52</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>52.15</c:v>
+                  <c:v>51.18</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56.26</c:v>
+                  <c:v>56.35</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>54.14</c:v>
+                  <c:v>54.24</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>54.26</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>51.77</c:v>
+                  <c:v>52.02</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>51.63</c:v>
+                  <c:v>51.81</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>55.24</c:v>
+                  <c:v>55.42</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>52.6</c:v>
+                  <c:v>52.94</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>51.31</c:v>
+                  <c:v>50.94</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>46.38</c:v>
+                  <c:v>45.07</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>50.12</c:v>
+                  <c:v>48.55</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>49.35</c:v>
+                  <c:v>47.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2730,70 +2733,70 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>109.1112435372323</c:v>
+                  <c:v>114.12242748271</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>106.5359687572136</c:v>
+                  <c:v>111.4288773058169</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>112.7365294770219</c:v>
+                  <c:v>117.9142129885415</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>112.5059067210303</c:v>
+                  <c:v>117.6729983538872</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>101.4015891843619</c:v>
+                  <c:v>110.7044130913189</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>100.8470809950096</c:v>
+                  <c:v>110.0990329966838</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>97.50608884778109</c:v>
+                  <c:v>106.4515302526274</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>98.06328586226736</c:v>
+                  <c:v>107.0598458516343</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>99.59801165599774</c:v>
+                  <c:v>109.8523878557859</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>101.108190580793</c:v>
+                  <c:v>111.518051238216</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>99.46381914614688</c:v>
+                  <c:v>110.3479402470148</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>103.5348701916727</c:v>
+                  <c:v>111.8534528423508</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>102.5970744957329</c:v>
+                  <c:v>111.5157383233764</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>104.3527225681192</c:v>
+                  <c:v>112.6606972336988</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>103.8383887615269</c:v>
+                  <c:v>112.1054150730085</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>104.8240001435101</c:v>
+                  <c:v>113.1694952691261</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>106.4894124409097</c:v>
+                  <c:v>114.9674982918469</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>113.1205949117499</c:v>
+                  <c:v>122.1266180758187</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>117.3000731115495</c:v>
+                  <c:v>124.8339528715453</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>115.1308805620361</c:v>
+                  <c:v>122.5254387051666</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>118.957552735988</c:v>
+                  <c:v>123.8829218426343</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>118.4501951057308</c:v>
+                  <c:v>123.3545573612726</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3624,13 +3627,13 @@
         <v>0.25</v>
       </c>
       <c r="D14" s="10">
-        <v>54.32</v>
+        <v>57.92</v>
       </c>
       <c r="E14" s="10">
-        <v>13.58</v>
+        <v>14.48</v>
       </c>
       <c r="F14" s="11">
-        <v>0.275177304964539</v>
+        <v>0.3060016906170752</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>25</v>
@@ -3650,7 +3653,7 @@
         <v>7.44</v>
       </c>
       <c r="F15" s="11">
-        <v>0.1507598784194529</v>
+        <v>0.1572273879966188</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -3664,16 +3667,16 @@
         <v>0.2</v>
       </c>
       <c r="D16" s="10">
-        <v>57.51</v>
+        <v>42.87</v>
       </c>
       <c r="E16" s="10">
-        <v>11.5</v>
+        <v>8.57</v>
       </c>
       <c r="F16" s="11">
-        <v>0.2330293819655522</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>25</v>
+        <v>0.1811073541842773</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -3690,7 +3693,7 @@
         <v>8.24</v>
       </c>
       <c r="F17" s="11">
-        <v>0.1669706180344478</v>
+        <v>0.1741335587489434</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>25</v>
@@ -3710,7 +3713,7 @@
         <v>2.59</v>
       </c>
       <c r="F18" s="11">
-        <v>0.05248226950354609</v>
+        <v>0.05473372781065088</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>27</v>
@@ -3730,7 +3733,7 @@
         <v>6</v>
       </c>
       <c r="F19" s="11">
-        <v>0.121580547112462</v>
+        <v>0.1267962806424345</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>25</v>
@@ -3745,7 +3748,7 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="10">
-        <v>49.35</v>
+        <v>47.32</v>
       </c>
       <c r="F20" s="11">
         <v>1</v>
@@ -3862,25 +3865,25 @@
         <v>45</v>
       </c>
       <c r="C6" s="10">
-        <v>64.01000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="10">
-        <v>64.01000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>46</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" s="10">
-        <v>14.51</v>
+        <v>20.63</v>
       </c>
       <c r="J6" s="10">
         <v>12.64</v>
@@ -3901,7 +3904,7 @@
         <v>1191.44</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q6" s="11">
         <v>0.182224870744645</v>
@@ -3909,28 +3912,28 @@
     </row>
     <row r="7" spans="2:17">
       <c r="B7" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="10">
-        <v>55.19</v>
+        <v>61.25</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" s="10">
-        <v>55.19</v>
+        <v>61.25</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I7" s="10">
-        <v>12.05</v>
+        <v>18.11</v>
       </c>
       <c r="J7" s="10">
         <v>11.06</v>
@@ -3959,28 +3962,28 @@
     </row>
     <row r="8" spans="2:17">
       <c r="B8" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="10">
-        <v>54.94</v>
+        <v>60.67</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="10">
-        <v>54.94</v>
+        <v>60.67</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I8" s="10">
-        <v>12.37</v>
+        <v>18.1</v>
       </c>
       <c r="J8" s="10">
         <v>11.69</v>
@@ -4009,28 +4012,28 @@
     </row>
     <row r="9" spans="2:17">
       <c r="B9" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" s="10">
-        <v>52.61</v>
+        <v>58.17</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E9" s="10">
-        <v>52.61</v>
+        <v>58.17</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="10">
-        <v>12.99</v>
+        <v>18.55</v>
       </c>
       <c r="J9" s="10">
         <v>11.9</v>
@@ -4059,34 +4062,34 @@
     </row>
     <row r="10" spans="2:17">
       <c r="B10" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="10">
-        <v>60.76</v>
+        <v>61.19</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E10" s="10">
-        <v>62.17</v>
+        <v>46.08</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H10" s="14" t="s">
         <v>54</v>
       </c>
       <c r="I10" s="10">
-        <v>12.54</v>
+        <v>18.62</v>
       </c>
       <c r="J10" s="10">
         <v>12.85</v>
       </c>
       <c r="K10" s="10">
-        <v>12.46</v>
+        <v>6.81</v>
       </c>
       <c r="L10" s="10">
         <v>8.039999999999999</v>
@@ -4112,13 +4115,13 @@
         <v>55</v>
       </c>
       <c r="C11" s="10">
-        <v>50</v>
+        <v>50.64</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="10">
-        <v>26.12</v>
+        <v>11.75</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>56</v>
@@ -4127,16 +4130,16 @@
         <v>10</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I11" s="10">
-        <v>11.73</v>
+        <v>17.21</v>
       </c>
       <c r="J11" s="10">
         <v>11.22</v>
       </c>
       <c r="K11" s="10">
-        <v>11.97</v>
+        <v>7.13</v>
       </c>
       <c r="L11" s="10">
         <v>7.71</v>
@@ -4162,31 +4165,31 @@
         <v>57</v>
       </c>
       <c r="C12" s="10">
-        <v>51.07</v>
+        <v>57.66</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" s="10">
-        <v>35.08</v>
+        <v>43.58</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="H12" s="14" t="s">
         <v>58</v>
       </c>
       <c r="I12" s="10">
-        <v>11.49</v>
+        <v>16.1</v>
       </c>
       <c r="J12" s="10">
         <v>11.23</v>
       </c>
       <c r="K12" s="10">
-        <v>8.5</v>
+        <v>10.48</v>
       </c>
       <c r="L12" s="10">
         <v>8.779999999999999</v>
@@ -4212,13 +4215,13 @@
         <v>59</v>
       </c>
       <c r="C13" s="10">
-        <v>45.8</v>
+        <v>49.17</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="10">
-        <v>21.68</v>
+        <v>22.14</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>56</v>
@@ -4227,16 +4230,16 @@
         <v>10</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I13" s="10">
-        <v>9.34</v>
+        <v>10.57</v>
       </c>
       <c r="J13" s="10">
         <v>10.07</v>
       </c>
       <c r="K13" s="10">
-        <v>9.800000000000001</v>
+        <v>11.94</v>
       </c>
       <c r="L13" s="10">
         <v>8.220000000000001</v>
@@ -4262,31 +4265,31 @@
         <v>60</v>
       </c>
       <c r="C14" s="10">
-        <v>54.29</v>
+        <v>59.6</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" s="10">
-        <v>49.98</v>
+        <v>52.25</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I14" s="10">
-        <v>12.48</v>
+        <v>13.72</v>
       </c>
       <c r="J14" s="10">
         <v>10.41</v>
       </c>
       <c r="K14" s="10">
-        <v>10.74</v>
+        <v>14.81</v>
       </c>
       <c r="L14" s="10">
         <v>8.31</v>
@@ -4312,31 +4315,31 @@
         <v>61</v>
       </c>
       <c r="C15" s="10">
-        <v>56.39</v>
+        <v>59.94</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E15" s="10">
-        <v>55.72</v>
+        <v>52.96</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I15" s="10">
-        <v>14</v>
+        <v>14.34</v>
       </c>
       <c r="J15" s="10">
         <v>11.49</v>
       </c>
       <c r="K15" s="10">
-        <v>11.46</v>
+        <v>14.67</v>
       </c>
       <c r="L15" s="10">
         <v>8.19</v>
@@ -4362,31 +4365,31 @@
         <v>62</v>
       </c>
       <c r="C16" s="10">
-        <v>60.22</v>
+        <v>59.4</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="10">
-        <v>66.42</v>
+        <v>51.43</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I16" s="10">
-        <v>12.77</v>
+        <v>13.1</v>
       </c>
       <c r="J16" s="10">
         <v>11.45</v>
       </c>
       <c r="K16" s="10">
-        <v>14.5</v>
+        <v>13.35</v>
       </c>
       <c r="L16" s="10">
         <v>8.369999999999999</v>
@@ -4409,34 +4412,34 @@
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="10">
-        <v>53.57</v>
+        <v>52.52</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="10">
-        <v>45.84</v>
+        <v>32.74</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I17" s="10">
-        <v>13.95</v>
+        <v>14.28</v>
       </c>
       <c r="J17" s="10">
         <v>9.630000000000001</v>
       </c>
       <c r="K17" s="10">
-        <v>12.4</v>
+        <v>11.02</v>
       </c>
       <c r="L17" s="10">
         <v>8.23</v>
@@ -4459,34 +4462,34 @@
     </row>
     <row r="18" spans="2:17">
       <c r="B18" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="10">
-        <v>52.15</v>
+        <v>51.18</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E18" s="10">
-        <v>41.76</v>
+        <v>30.74</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I18" s="10">
-        <v>16.31</v>
+        <v>16.64</v>
       </c>
       <c r="J18" s="10">
         <v>4</v>
       </c>
       <c r="K18" s="10">
-        <v>12.94</v>
+        <v>11.64</v>
       </c>
       <c r="L18" s="10">
         <v>8.06</v>
@@ -4509,34 +4512,34 @@
     </row>
     <row r="19" spans="2:17">
       <c r="B19" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="10">
-        <v>56.26</v>
+        <v>56.35</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E19" s="10">
-        <v>54.84</v>
+        <v>46.17</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I19" s="10">
-        <v>14.83</v>
+        <v>16.24</v>
       </c>
       <c r="J19" s="10">
         <v>10.05</v>
       </c>
       <c r="K19" s="10">
-        <v>10.29</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="L19" s="10">
         <v>8.210000000000001</v>
@@ -4559,34 +4562,34 @@
     </row>
     <row r="20" spans="2:17">
       <c r="B20" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="10">
-        <v>54.14</v>
+        <v>54.24</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E20" s="10">
-        <v>47.88</v>
+        <v>40.55</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I20" s="10">
-        <v>14.55</v>
+        <v>15.96</v>
       </c>
       <c r="J20" s="10">
         <v>10.86</v>
       </c>
       <c r="K20" s="10">
-        <v>8.470000000000001</v>
+        <v>7.16</v>
       </c>
       <c r="L20" s="10">
         <v>7.91</v>
@@ -4609,34 +4612,34 @@
     </row>
     <row r="21" spans="2:17">
       <c r="B21" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="10">
         <v>54.26</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" s="10">
-        <v>48.34</v>
+        <v>41.03</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I21" s="10">
-        <v>16.84</v>
+        <v>18.25</v>
       </c>
       <c r="J21" s="10">
         <v>10.9</v>
       </c>
       <c r="K21" s="10">
-        <v>9.529999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L21" s="10">
         <v>7.95</v>
@@ -4659,34 +4662,34 @@
     </row>
     <row r="22" spans="2:17">
       <c r="B22" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C22" s="10">
-        <v>51.77</v>
+        <v>52.02</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E22" s="10">
-        <v>39.85</v>
+        <v>35.01</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I22" s="10">
-        <v>14.59</v>
+        <v>16.09</v>
       </c>
       <c r="J22" s="10">
         <v>9.27</v>
       </c>
       <c r="K22" s="10">
-        <v>8.31</v>
+        <v>7.06</v>
       </c>
       <c r="L22" s="10">
         <v>7.92</v>
@@ -4709,34 +4712,34 @@
     </row>
     <row r="23" spans="2:17">
       <c r="B23" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C23" s="10">
-        <v>51.63</v>
+        <v>51.81</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" s="10">
-        <v>39.78</v>
+        <v>35.27</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I23" s="10">
-        <v>14.58</v>
+        <v>16.07</v>
       </c>
       <c r="J23" s="10">
         <v>10.69</v>
       </c>
       <c r="K23" s="10">
-        <v>7.97</v>
+        <v>6.66</v>
       </c>
       <c r="L23" s="10">
         <v>7.99</v>
@@ -4759,34 +4762,34 @@
     </row>
     <row r="24" spans="2:17">
       <c r="B24" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="10">
-        <v>55.24</v>
+        <v>55.42</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="10">
-        <v>53.01</v>
+        <v>46.39</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" s="10">
-        <v>13.39</v>
+        <v>14.89</v>
       </c>
       <c r="J24" s="10">
         <v>11.38</v>
       </c>
       <c r="K24" s="10">
-        <v>8.1</v>
+        <v>6.78</v>
       </c>
       <c r="L24" s="10">
         <v>8.699999999999999</v>
@@ -4809,34 +4812,34 @@
     </row>
     <row r="25" spans="2:17">
       <c r="B25" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" s="10">
-        <v>52.6</v>
+        <v>52.94</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" s="10">
-        <v>43.29</v>
+        <v>39.19</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>33</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I25" s="10">
-        <v>13.06</v>
+        <v>14.56</v>
       </c>
       <c r="J25" s="10">
         <v>11.33</v>
       </c>
       <c r="K25" s="10">
-        <v>5.95</v>
+        <v>4.79</v>
       </c>
       <c r="L25" s="10">
         <v>8.43</v>
@@ -4859,34 +4862,34 @@
     </row>
     <row r="26" spans="2:17">
       <c r="B26" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="10">
-        <v>51.31</v>
+        <v>50.94</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E26" s="10">
-        <v>38.67</v>
+        <v>33.62</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I26" s="10">
-        <v>16.02</v>
+        <v>16.93</v>
       </c>
       <c r="J26" s="10">
         <v>11.84</v>
       </c>
       <c r="K26" s="10">
-        <v>5.98</v>
+        <v>4.7</v>
       </c>
       <c r="L26" s="10">
         <v>8.609999999999999</v>
@@ -4909,16 +4912,16 @@
     </row>
     <row r="27" spans="2:17">
       <c r="B27" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C27" s="10">
-        <v>46.38</v>
+        <v>45.07</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E27" s="10">
-        <v>20.48</v>
+        <v>16.99</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>56</v>
@@ -4927,16 +4930,16 @@
         <v>10</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I27" s="10">
-        <v>11.71</v>
+        <v>12.61</v>
       </c>
       <c r="J27" s="10">
         <v>8.33</v>
       </c>
       <c r="K27" s="10">
-        <v>4.69</v>
+        <v>2.48</v>
       </c>
       <c r="L27" s="10">
         <v>8.82</v>
@@ -4959,34 +4962,34 @@
     </row>
     <row r="28" spans="2:17">
       <c r="B28" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="10">
-        <v>50.12</v>
+        <v>48.55</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E28" s="10">
-        <v>36.76</v>
+        <v>30.46</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I28" s="10">
-        <v>14.41</v>
+        <v>15.32</v>
       </c>
       <c r="J28" s="10">
         <v>8.99</v>
       </c>
       <c r="K28" s="10">
-        <v>6.84</v>
+        <v>4.36</v>
       </c>
       <c r="L28" s="10">
         <v>8.609999999999999</v>
@@ -5004,21 +5007,21 @@
         <v>-0.0426503083316756</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="2:17">
       <c r="B29" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C29" s="10">
-        <v>49.35</v>
+        <v>47.32</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="10">
-        <v>34.51</v>
+        <v>28.24</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>56</v>
@@ -5027,16 +5030,16 @@
         <v>10</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I29" s="10">
-        <v>13.58</v>
+        <v>14.48</v>
       </c>
       <c r="J29" s="10">
         <v>7.44</v>
       </c>
       <c r="K29" s="10">
-        <v>11.5</v>
+        <v>8.57</v>
       </c>
       <c r="L29" s="10">
         <v>8.24</v>
@@ -5048,13 +5051,13 @@
         <v>6</v>
       </c>
       <c r="O29" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -5115,46 +5118,46 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="15">
         <v>-0.036358</v>
@@ -5163,27 +5166,27 @@
         <v>0.0278</v>
       </c>
       <c r="E6" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="G6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>90</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>91</v>
       </c>
       <c r="I6" s="14">
         <v>1</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="15">
         <v>0.000137</v>
@@ -5192,27 +5195,27 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="E7" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="I7" s="14">
         <v>10</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" s="15">
         <v>-0.032628</v>
@@ -5221,27 +5224,27 @@
         <v>0.0592</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F8" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="I8" s="14">
         <v>2</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="15">
         <v>-0.002719</v>
@@ -5250,27 +5253,27 @@
         <v>0.7492</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I9" s="14">
         <v>7</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" s="15">
         <v>9.899999999999999E-05</v>
@@ -5279,27 +5282,27 @@
         <v>0.0223</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="I10" s="14">
         <v>11</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" s="15">
         <v>-8.000000000000001E-05</v>
@@ -5308,27 +5311,27 @@
         <v>0.2363</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I11" s="14">
         <v>12</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="15">
         <v>-0.000221</v>
@@ -5337,27 +5340,27 @@
         <v>0.8799</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I12" s="14">
         <v>9</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C13" s="15">
         <v>-0.002852</v>
@@ -5366,27 +5369,27 @@
         <v>0.3781</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I13" s="14">
         <v>6</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C14" s="15">
         <v>-0.029501</v>
@@ -5395,27 +5398,27 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I14" s="14">
         <v>3</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C15" s="15">
         <v>0.006628</v>
@@ -5424,27 +5427,27 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G15" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="15">
         <v>-0.005037</v>
@@ -5453,27 +5456,27 @@
         <v>0.2276</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" s="15">
         <v>-0.000575</v>
@@ -5482,55 +5485,55 @@
         <v>0.8627</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I17" s="14">
         <v>8</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>45</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>55</v>
@@ -5551,51 +5554,51 @@
         <v>62</v>
       </c>
       <c r="N40" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O40" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="O40" s="7" t="s">
+      <c r="P40" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="P40" s="7" t="s">
+      <c r="Q40" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Q40" s="7" t="s">
+      <c r="R40" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="R40" s="7" t="s">
+      <c r="S40" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="S40" s="7" t="s">
+      <c r="T40" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="T40" s="7" t="s">
+      <c r="U40" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="U40" s="7" t="s">
+      <c r="V40" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="V40" s="7" t="s">
+      <c r="W40" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="W40" s="7" t="s">
+      <c r="X40" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="X40" s="7" t="s">
+      <c r="Y40" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="Y40" s="7" t="s">
+      <c r="Z40" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="Z40" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="AA40" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="16">
         <v>0.050404</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C42" s="16">
         <v>0.006803</v>
@@ -5755,7 +5758,7 @@
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C43" s="16">
         <v>0.033473</v>
@@ -5835,7 +5838,7 @@
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="16">
         <v>0.005801</v>
@@ -5915,7 +5918,7 @@
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C45" s="16">
         <v>0.000145</v>
@@ -5995,7 +5998,7 @@
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="16">
         <v>-6E-06</v>
@@ -6075,7 +6078,7 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C47" s="16">
         <v>-0.00157</v>
@@ -6126,13 +6129,13 @@
         <v>3.8E-05</v>
       </c>
       <c r="S47" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T47" s="16">
         <v>0.000618</v>
       </c>
       <c r="U47" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V47" s="16">
         <v>0.000495</v>
@@ -6155,7 +6158,7 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C48" s="16">
         <v>-0.013109</v>
@@ -6235,7 +6238,7 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C49" s="16">
         <v>-0.045005</v>
@@ -6315,7 +6318,7 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C50" s="16">
         <v>0.004475</v>
@@ -6395,7 +6398,7 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="16">
         <v>-0.010339</v>
@@ -6475,10 +6478,10 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D52" s="16">
         <v>0.023665</v>
@@ -6616,37 +6619,37 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" s="16">
         <v>7.2336</v>
@@ -6655,18 +6658,18 @@
         <v>0.0072</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F6" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="18" t="s">
         <v>130</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="16">
         <v>0.5046</v>
@@ -6675,18 +6678,18 @@
         <v>0.4775</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="18" t="s">
         <v>133</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C8" s="16">
         <v>0.3229</v>
@@ -6695,18 +6698,18 @@
         <v>0.5699</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C9" s="16">
         <v>0.2242</v>
@@ -6715,18 +6718,18 @@
         <v>0.6359</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="16">
         <v>0.004</v>
@@ -6735,13 +6738,13 @@
         <v>0.9498</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -6773,36 +6776,36 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C8" s="16">
         <v>0.425</v>
@@ -6810,7 +6813,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C9" s="16">
         <v>0.1599</v>
@@ -6818,7 +6821,7 @@
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" s="16">
         <v>0.3692</v>
@@ -6826,15 +6829,15 @@
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C12" s="16">
         <v>0.5031</v>
@@ -6842,27 +6845,27 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="G15" s="7" t="s">
         <v>157</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -7027,18 +7030,18 @@
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="7" t="s">
         <v>161</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -7046,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D28" s="16">
         <v>0.02178040146827698</v>
@@ -7057,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D29" s="16">
         <v>0.02076428011059761</v>
@@ -7068,7 +7071,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D30" s="16">
         <v>0.01783575303852558</v>
@@ -7079,7 +7082,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D31" s="16">
         <v>0.01772940717637539</v>
@@ -7090,7 +7093,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D32" s="16">
         <v>0.01733604446053505</v>
@@ -7101,7 +7104,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D33" s="16">
         <v>0.0167862419039011</v>
@@ -7112,7 +7115,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D34" s="16">
         <v>0.01557330787181854</v>
@@ -7123,7 +7126,7 @@
         <v>8</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D35" s="16">
         <v>0.01539521757513285</v>
@@ -7134,7 +7137,7 @@
         <v>9</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="16">
         <v>0.01488733943551779</v>
@@ -7145,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" s="16">
         <v>0.01360253803431988</v>
@@ -7156,7 +7159,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D38" s="16">
         <v>0.0134799899533391</v>
@@ -7167,7 +7170,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D39" s="16">
         <v>0.01324111688882113</v>
@@ -7178,7 +7181,7 @@
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D40" s="16">
         <v>0.01247525215148926</v>
@@ -7189,7 +7192,7 @@
         <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D41" s="16">
         <v>0.01242704410105944</v>
@@ -7200,7 +7203,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D42" s="16">
         <v>0.01225554849952459</v>
@@ -7226,7 +7229,7 @@
   <sheetPr>
     <tabColor rgb="FFF97316"/>
   </sheetPr>
-  <dimension ref="B2:G31"/>
+  <dimension ref="B2:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -7240,12 +7243,12 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -7253,19 +7256,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -7276,16 +7279,16 @@
         <v>0.25</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" s="18" t="s">
         <v>185</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>186</v>
       </c>
       <c r="F6" s="10">
         <v>60</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -7296,16 +7299,16 @@
         <v>0.25</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E7" s="18" t="s">
         <v>188</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>189</v>
       </c>
       <c r="F7" s="10">
         <v>50</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -7316,16 +7319,16 @@
         <v>0.25</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>190</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>191</v>
       </c>
       <c r="F8" s="10">
         <v>69</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -7336,16 +7339,16 @@
         <v>0.25</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="E9" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>48</v>
-      </c>
       <c r="F9" s="10">
-        <v>50</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>193</v>
+        <v>68</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="2:7">
@@ -7356,16 +7359,16 @@
         <v>0.25</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="18" t="s">
         <v>194</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>195</v>
       </c>
       <c r="F10" s="10">
         <v>43</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -7376,16 +7379,16 @@
         <v>0.2</v>
       </c>
       <c r="D11" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>196</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>197</v>
       </c>
       <c r="F11" s="10">
         <v>29</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -7396,16 +7399,16 @@
         <v>0.2</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>198</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>199</v>
       </c>
       <c r="F12" s="10">
         <v>0</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="2:7">
@@ -7416,16 +7419,16 @@
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>200</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>201</v>
       </c>
       <c r="F13" s="10">
         <v>53</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -7436,16 +7439,16 @@
         <v>0.2</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="2:7">
@@ -7456,16 +7459,16 @@
         <v>0.2</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>203</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>204</v>
       </c>
       <c r="F15" s="10">
         <v>48</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -7476,16 +7479,16 @@
         <v>0.2</v>
       </c>
       <c r="D16" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>205</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>206</v>
       </c>
       <c r="F16" s="10">
         <v>56</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -7496,16 +7499,16 @@
         <v>0.2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F17" s="10">
         <v>30</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -7516,16 +7519,16 @@
         <v>0.2</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>208</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>209</v>
       </c>
       <c r="F18" s="10">
         <v>33</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -7536,36 +7539,36 @@
         <v>0.2</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>210</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>211</v>
       </c>
       <c r="F19" s="10">
         <v>80</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="9">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D20" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>213</v>
-      </c>
       <c r="F20" s="10">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -7576,16 +7579,16 @@
         <v>0.15</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>215</v>
-      </c>
       <c r="F21" s="10">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -7596,16 +7599,16 @@
         <v>0.15</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>94</v>
+      <c r="F22" s="10">
+        <v>53</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -7616,36 +7619,36 @@
         <v>0.15</v>
       </c>
       <c r="D23" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="E23" s="18" t="s">
-        <v>219</v>
-      </c>
       <c r="F23" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>221</v>
-      </c>
       <c r="F24" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -7656,36 +7659,36 @@
         <v>0.1</v>
       </c>
       <c r="D25" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>223</v>
-      </c>
       <c r="F25" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" s="9">
         <v>0.1</v>
       </c>
       <c r="D26" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="E26" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="F26" s="10">
-        <v>75</v>
+      <c r="F26" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -7696,16 +7699,16 @@
         <v>0.1</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="E27" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="F27" s="14" t="s">
-        <v>94</v>
+      <c r="F27" s="10">
+        <v>75</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -7716,16 +7719,16 @@
         <v>0.1</v>
       </c>
       <c r="D28" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="E28" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="F28" s="10">
-        <v>38</v>
+      <c r="F28" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -7736,16 +7739,16 @@
         <v>0.1</v>
       </c>
       <c r="D29" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>231</v>
-      </c>
       <c r="F29" s="10">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -7756,16 +7759,16 @@
         <v>0.1</v>
       </c>
       <c r="D30" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>94</v>
+      <c r="F30" s="10">
+        <v>47</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -7776,21 +7779,41 @@
         <v>0.1</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="E31" s="18" t="s">
+      <c r="F31" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="F31" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>187</v>
+      <c r="E32" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B5:G31"/>
-  <conditionalFormatting sqref="F6:F31">
+  <autoFilter ref="B5:G32"/>
+  <conditionalFormatting sqref="F6:F32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7827,17 +7850,17 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C5" s="14">
         <v>22</v>
@@ -7845,39 +7868,39 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C6" s="16">
-        <v>0.05191697881001582</v>
+        <v>0.1550909362864956</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C7" s="16">
-        <v>0.05138339920948617</v>
+        <v>0.1078486730660644</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C8" s="16">
-        <v>0.03936735417591136</v>
+        <v>0.0539510747016974</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C9" s="16">
-        <v>0.07735742518351214</v>
+        <v>-0.04912478825522304</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C10" s="11">
         <v>0.5</v>
@@ -7885,7 +7908,7 @@
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C11" s="11">
         <v>0.5454545454545454</v>
@@ -7893,23 +7916,23 @@
     </row>
     <row r="12" spans="2:3">
       <c r="B12" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C12" s="11">
-        <v>0.1845019510573085</v>
+        <v>0.2335455736127263</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C13" s="11">
-        <v>0.249486451502519</v>
+        <v>0.306871980645762</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C14" s="11">
         <v>0.4945612032498485</v>
@@ -7917,15 +7940,15 @@
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C15" s="10">
-        <v>0.4364053247997207</v>
+        <v>0.5213441818233974</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C16" s="10">
         <v>0.4775014136300051</v>
@@ -7933,58 +7956,58 @@
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="2:12">
       <c r="B20" s="14" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C20" s="14">
         <v>1</v>
       </c>
       <c r="D20" s="11">
-        <v>-0.0209851405796474</v>
+        <v>0.182224870744645</v>
       </c>
       <c r="E20" s="11">
-        <v>-0.0209851405796474</v>
+        <v>0.182224870744645</v>
       </c>
       <c r="F20" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:12">
       <c r="B21" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21" s="11">
-        <v>0.02354702251044302</v>
+        <v>0.02110257050780219</v>
       </c>
       <c r="E21" s="11">
-        <v>0.03227480928324977</v>
+        <v>0.0131170626569212</v>
       </c>
       <c r="F21" s="11">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -7992,16 +8015,16 @@
         <v>33</v>
       </c>
       <c r="C22" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="11">
-        <v>0.03728655480248493</v>
+        <v>0.001598189831757129</v>
       </c>
       <c r="E22" s="11">
-        <v>0.04190357166586001</v>
+        <v>0.03163927438071323</v>
       </c>
       <c r="F22" s="11">
-        <v>0.6</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -8009,21 +8032,21 @@
         <v>56</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" s="11">
-        <v>-0.01339661133548834</v>
+        <v>0.02947379187416812</v>
       </c>
       <c r="E23" s="11">
-        <v>-0.0426503083316756</v>
+        <v>0.01347612765786038</v>
       </c>
       <c r="F23" s="11">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -8031,34 +8054,34 @@
         <v>36</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -8066,16 +8089,16 @@
         <v>45</v>
       </c>
       <c r="C27" s="10">
-        <v>64.01000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E27" s="9">
-        <v>0.5</v>
+        <v>0.775</v>
       </c>
       <c r="F27" s="10">
-        <v>64.01000000000001</v>
+        <v>70.13</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>46</v>
@@ -8084,13 +8107,13 @@
         <v>0.182224870744645</v>
       </c>
       <c r="I27" s="11">
-        <v>0.0911124353723225</v>
+        <v>0.1412242748270999</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K27" s="10">
-        <v>109.1112435372323</v>
+        <v>114.12242748271</v>
       </c>
       <c r="L27" s="10">
         <v>118.2224870744645</v>
@@ -8098,22 +8121,22 @@
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" s="10">
-        <v>55.19</v>
+        <v>61.25</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" s="9">
         <v>0.5</v>
       </c>
       <c r="F28" s="10">
-        <v>55.19</v>
+        <v>61.25</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H28" s="11">
         <v>-0.04720457207766848</v>
@@ -8122,10 +8145,10 @@
         <v>-0.02360228603883424</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K28" s="10">
-        <v>106.5359687572136</v>
+        <v>111.4288773058169</v>
       </c>
       <c r="L28" s="10">
         <v>112.6418451621567</v>
@@ -8133,22 +8156,22 @@
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C29" s="10">
-        <v>54.94</v>
+        <v>60.67</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="9">
         <v>0.5</v>
       </c>
       <c r="F29" s="10">
-        <v>54.94</v>
+        <v>60.67</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H29" s="11">
         <v>0.1164031414392799</v>
@@ -8157,10 +8180,10 @@
         <v>0.05820157071963994</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K29" s="10">
-        <v>112.7365294770219</v>
+        <v>117.9142129885415</v>
       </c>
       <c r="L29" s="10">
         <v>125.7537097965487</v>
@@ -8168,22 +8191,22 @@
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C30" s="10">
-        <v>52.61</v>
+        <v>58.17</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" s="9">
         <v>0.5</v>
       </c>
       <c r="F30" s="10">
-        <v>52.61</v>
+        <v>58.17</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H30" s="11">
         <v>-0.004091358090610453</v>
@@ -8192,10 +8215,10 @@
         <v>-0.002045679045305226</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K30" s="10">
-        <v>112.5059067210303</v>
+        <v>117.6729983538872</v>
       </c>
       <c r="L30" s="10">
         <v>125.2392063385483</v>
@@ -8203,34 +8226,34 @@
     </row>
     <row r="31" spans="2:12">
       <c r="B31" s="14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C31" s="10">
-        <v>62.17</v>
+        <v>46.08</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E31" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F31" s="10">
-        <v>60.76</v>
+        <v>61.19</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" s="11">
         <v>-0.197399725228697</v>
       </c>
       <c r="I31" s="11">
-        <v>-0.09869986261434849</v>
-      </c>
-      <c r="J31" s="13" t="s">
+        <v>-0.05921991756860909</v>
+      </c>
+      <c r="J31" s="17" t="s">
         <v>266</v>
       </c>
       <c r="K31" s="10">
-        <v>101.4015891843619</v>
+        <v>110.7044130913189</v>
       </c>
       <c r="L31" s="10">
         <v>100.5170214194588</v>
@@ -8241,7 +8264,7 @@
         <v>55</v>
       </c>
       <c r="C32" s="10">
-        <v>26.12</v>
+        <v>11.75</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>56</v>
@@ -8250,10 +8273,10 @@
         <v>0.1</v>
       </c>
       <c r="F32" s="10">
-        <v>50</v>
+        <v>50.64</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" s="11">
         <v>-0.05468436873747495</v>
@@ -8262,10 +8285,10 @@
         <v>-0.005468436873747495</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K32" s="10">
-        <v>100.8470809950096</v>
+        <v>110.0990329966838</v>
       </c>
       <c r="L32" s="10">
         <v>95.02031155576445</v>
@@ -8276,7 +8299,7 @@
         <v>57</v>
       </c>
       <c r="C33" s="10">
-        <v>35.08</v>
+        <v>43.58</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>33</v>
@@ -8285,10 +8308,10 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="10">
-        <v>51.07</v>
+        <v>57.66</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" s="11">
         <v>-0.1104309651888949</v>
@@ -8297,10 +8320,10 @@
         <v>-0.03312928955666848</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K33" s="10">
-        <v>97.50608884778109</v>
+        <v>106.4515302526274</v>
       </c>
       <c r="L33" s="10">
         <v>84.52712683811188</v>
@@ -8311,7 +8334,7 @@
         <v>59</v>
       </c>
       <c r="C34" s="10">
-        <v>21.68</v>
+        <v>22.14</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>56</v>
@@ -8320,7 +8343,7 @@
         <v>0.1</v>
       </c>
       <c r="F34" s="10">
-        <v>45.8</v>
+        <v>49.17</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>33</v>
@@ -8332,10 +8355,10 @@
         <v>0.005714484306268553</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K34" s="10">
-        <v>98.06328586226736</v>
+        <v>107.0598458516343</v>
       </c>
       <c r="L34" s="10">
         <v>89.35741623581549</v>
@@ -8346,31 +8369,31 @@
         <v>60</v>
       </c>
       <c r="C35" s="10">
-        <v>49.98</v>
+        <v>52.25</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E35" s="9">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F35" s="10">
-        <v>54.29</v>
+        <v>59.6</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="11">
         <v>0.05216786895100678</v>
       </c>
       <c r="I35" s="11">
-        <v>0.01565036068530203</v>
-      </c>
-      <c r="J35" s="13" t="s">
+        <v>0.02608393447550339</v>
+      </c>
+      <c r="J35" s="17" t="s">
         <v>266</v>
       </c>
       <c r="K35" s="10">
-        <v>99.59801165599774</v>
+        <v>109.8523878557859</v>
       </c>
       <c r="L35" s="10">
         <v>94.01900221580608</v>
@@ -8381,19 +8404,19 @@
         <v>61</v>
       </c>
       <c r="C36" s="10">
-        <v>55.72</v>
+        <v>52.96</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E36" s="9">
         <v>0.5</v>
       </c>
       <c r="F36" s="10">
-        <v>56.39</v>
+        <v>59.94</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" s="11">
         <v>0.03032548340445285</v>
@@ -8402,10 +8425,10 @@
         <v>0.01516274170222642</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K36" s="10">
-        <v>101.108190580793</v>
+        <v>111.518051238216</v>
       </c>
       <c r="L36" s="10">
         <v>96.87017390720473</v>
@@ -8416,31 +8439,31 @@
         <v>62</v>
       </c>
       <c r="C37" s="10">
-        <v>66.42</v>
+        <v>51.43</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E37" s="9">
-        <v>0.775</v>
+        <v>0.5</v>
       </c>
       <c r="F37" s="10">
-        <v>60.22</v>
+        <v>59.4</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" s="11">
         <v>-0.0209851405796474</v>
       </c>
       <c r="I37" s="11">
-        <v>-0.01626348394922673</v>
+        <v>-0.0104925702898237</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K37" s="10">
-        <v>99.46381914614688</v>
+        <v>110.3479402470148</v>
       </c>
       <c r="L37" s="10">
         <v>94.83733968978714</v>
@@ -8448,34 +8471,34 @@
     </row>
     <row r="38" spans="2:12">
       <c r="B38" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="10">
-        <v>45.84</v>
+        <v>32.74</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E38" s="9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F38" s="10">
-        <v>53.57</v>
+        <v>52.52</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H38" s="11">
         <v>0.136433230377103</v>
       </c>
       <c r="I38" s="11">
-        <v>0.04092996911313089</v>
+        <v>0.0136433230377103</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K38" s="10">
-        <v>103.5348701916727</v>
+        <v>111.8534528423508</v>
       </c>
       <c r="L38" s="10">
         <v>107.7763043040354</v>
@@ -8483,34 +8506,34 @@
     </row>
     <row r="39" spans="2:12">
       <c r="B39" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C39" s="10">
-        <v>41.76</v>
+        <v>30.74</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E39" s="9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F39" s="10">
-        <v>52.15</v>
+        <v>51.18</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H39" s="11">
         <v>-0.03019258774696476</v>
       </c>
       <c r="I39" s="11">
-        <v>-0.009057776324089427</v>
+        <v>-0.003019258774696476</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K39" s="10">
-        <v>102.5970744957329</v>
+        <v>111.5157383233764</v>
       </c>
       <c r="L39" s="10">
         <v>104.5222587792923</v>
@@ -8518,34 +8541,34 @@
     </row>
     <row r="40" spans="2:12">
       <c r="B40" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="10">
-        <v>54.84</v>
+        <v>46.17</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E40" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F40" s="10">
-        <v>56.26</v>
+        <v>56.35</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H40" s="11">
         <v>0.0342241351620467</v>
       </c>
       <c r="I40" s="11">
-        <v>0.01711206758102335</v>
-      </c>
-      <c r="J40" s="17" t="s">
-        <v>265</v>
+        <v>0.01026724054861401</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="K40" s="10">
-        <v>104.3527225681192</v>
+        <v>112.6606972336988</v>
       </c>
       <c r="L40" s="10">
         <v>108.0994426911972</v>
@@ -8553,10 +8576,10 @@
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C41" s="10">
-        <v>47.88</v>
+        <v>40.55</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>33</v>
@@ -8565,10 +8588,10 @@
         <v>0.3</v>
       </c>
       <c r="F41" s="10">
-        <v>54.14</v>
+        <v>54.24</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H41" s="11">
         <v>-0.01642933677034653</v>
@@ -8577,10 +8600,10 @@
         <v>-0.004928801031103957</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K41" s="10">
-        <v>103.8383887615269</v>
+        <v>112.1054150730085</v>
       </c>
       <c r="L41" s="10">
         <v>106.3234405425367</v>
@@ -8588,10 +8611,10 @@
     </row>
     <row r="42" spans="2:12">
       <c r="B42" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C42" s="10">
-        <v>48.34</v>
+        <v>41.03</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>33</v>
@@ -8603,7 +8626,7 @@
         <v>54.26</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H42" s="11">
         <v>0.03163927438071323</v>
@@ -8612,10 +8635,10 @@
         <v>0.00949178231421397</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K42" s="10">
-        <v>104.8240001435101</v>
+        <v>113.1694952691261</v>
       </c>
       <c r="L42" s="10">
         <v>109.6874370509635</v>
@@ -8623,10 +8646,10 @@
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C43" s="10">
-        <v>39.85</v>
+        <v>35.01</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>33</v>
@@ -8635,10 +8658,10 @@
         <v>0.3</v>
       </c>
       <c r="F43" s="10">
-        <v>51.77</v>
+        <v>52.02</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H43" s="11">
         <v>0.05295900096414319</v>
@@ -8647,10 +8670,10 @@
         <v>0.01588770028924296</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K43" s="10">
-        <v>106.4894124409097</v>
+        <v>114.9674982918469</v>
       </c>
       <c r="L43" s="10">
         <v>115.4963741354999</v>
@@ -8658,10 +8681,10 @@
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="10">
-        <v>39.78</v>
+        <v>35.27</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>33</v>
@@ -8670,10 +8693,10 @@
         <v>0.3</v>
       </c>
       <c r="F44" s="10">
-        <v>51.63</v>
+        <v>51.81</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H44" s="11">
         <v>0.2075693823715363</v>
@@ -8682,10 +8705,10 @@
         <v>0.0622708147114609</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K44" s="10">
-        <v>113.1205949117499</v>
+        <v>122.1266180758187</v>
       </c>
       <c r="L44" s="10">
         <v>139.4698851809575</v>
@@ -8693,34 +8716,34 @@
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C45" s="10">
-        <v>53.01</v>
+        <v>46.39</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E45" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F45" s="10">
-        <v>55.24</v>
+        <v>55.42</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H45" s="11">
         <v>0.07389420473009567</v>
       </c>
       <c r="I45" s="11">
-        <v>0.03694710236504783</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>265</v>
+        <v>0.0221682614190287</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>267</v>
       </c>
       <c r="K45" s="10">
-        <v>117.3000731115495</v>
+        <v>124.8339528715453</v>
       </c>
       <c r="L45" s="10">
         <v>149.7759014302021</v>
@@ -8728,10 +8751,10 @@
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C46" s="10">
-        <v>43.29</v>
+        <v>39.19</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>33</v>
@@ -8740,10 +8763,10 @@
         <v>0.3</v>
       </c>
       <c r="F46" s="10">
-        <v>52.6</v>
+        <v>52.94</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" s="11">
         <v>-0.06164226193478251</v>
@@ -8752,10 +8775,10 @@
         <v>-0.01849267858043475</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K46" s="10">
-        <v>115.1308805620361</v>
+        <v>122.5254387051666</v>
       </c>
       <c r="L46" s="10">
         <v>140.5433760827234</v>
@@ -8763,34 +8786,34 @@
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" s="10">
-        <v>38.67</v>
+        <v>33.62</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E47" s="9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F47" s="10">
-        <v>51.31</v>
+        <v>50.94</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H47" s="11">
         <v>0.1107919426213355</v>
       </c>
       <c r="I47" s="11">
-        <v>0.03323758278640065</v>
+        <v>0.01107919426213355</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K47" s="10">
-        <v>118.957552735988</v>
+        <v>123.8829218426343</v>
       </c>
       <c r="L47" s="10">
         <v>156.1144497414892</v>
@@ -8798,10 +8821,10 @@
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C48" s="10">
-        <v>20.48</v>
+        <v>16.99</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>56</v>
@@ -8810,7 +8833,7 @@
         <v>0.1</v>
       </c>
       <c r="F48" s="10">
-        <v>46.38</v>
+        <v>45.07</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>33</v>
@@ -8822,10 +8845,10 @@
         <v>-0.004265030833167561</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K48" s="10">
-        <v>118.4501951057308</v>
+        <v>123.3545573612726</v>
       </c>
       <c r="L48" s="10">
         <v>149.4561203249849</v>
@@ -8833,7 +8856,7 @@
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -8859,7 +8882,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -8920,104 +8943,104 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -9028,10 +9051,10 @@
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -9042,10 +9065,10 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -9056,10 +9079,10 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -9070,10 +9093,10 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -9084,10 +9107,10 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -9098,10 +9121,10 @@
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -9112,10 +9135,10 @@
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -9126,10 +9149,10 @@
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -29,7 +29,7 @@
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 12:05:04  |  Source: output/exports/score_*.json</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 12:11:45  |  Source: output/exports/score_*.json</t>
   </si>
   <si>
     <t>47.3</t>
@@ -935,7 +935,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 12:05:04 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 12:11:45 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -24,15 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="306">
   <si>
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 12:11:45  |  Source: output/exports/score_*.json</t>
-  </si>
-  <si>
-    <t>47.3</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 15:48:37  |  Source: output/exports/score_*.json</t>
+  </si>
+  <si>
+    <t>47.2</t>
   </si>
   <si>
     <t>Raw Regime / Label</t>
@@ -44,7 +44,7 @@
     <t>CALIBRATED ACTION</t>
   </si>
   <si>
-    <t>🔴 SELL — 28.2</t>
+    <t>🔴 SELL — 29.4</t>
   </si>
   <si>
     <t>Recommended Equity</t>
@@ -62,7 +62,7 @@
     <t>Pillar Dispersion</t>
   </si>
   <si>
-    <t>MEDIUM (σ=13.47)</t>
+    <t>MEDIUM (σ=13.67)</t>
   </si>
   <si>
     <t>Data As-Of</t>
@@ -209,6 +209,9 @@
     <t>2023-Q1</t>
   </si>
   <si>
+    <t>BUY/ACCUMULATE</t>
+  </si>
+  <si>
     <t>2023-Q2</t>
   </si>
   <si>
@@ -626,7 +629,7 @@
     <t>nff_ex_etf</t>
   </si>
   <si>
-    <t>Z = 0.21 (Neutral)</t>
+    <t>Z = -0.05 (Neutral)</t>
   </si>
   <si>
     <t>-0.16% of Market Cap (YTD in Q)</t>
@@ -722,7 +725,7 @@
     <t>etf_flow</t>
   </si>
   <si>
-    <t>Z = -0.21 (Neutral)</t>
+    <t>Z = -0.12 (Neutral)</t>
   </si>
   <si>
     <t>etf_flow_q_ytd</t>
@@ -935,7 +938,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 12:11:45 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 15:48:37 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1289,7 +1292,7 @@
                   <c:v>14.48</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.44</c:v>
+                  <c:v>7.28</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>8.57</c:v>
@@ -1301,7 +1304,7 @@
                   <c:v>2.59</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>6.04</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1476,76 +1479,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>70.13</c:v>
+                  <c:v>68.64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61.25</c:v>
+                  <c:v>60.11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60.67</c:v>
+                  <c:v>60.26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58.17</c:v>
+                  <c:v>57.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46.08</c:v>
+                  <c:v>45.35</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.75</c:v>
+                  <c:v>11.29</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.58</c:v>
+                  <c:v>46.77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>22.14</c:v>
+                  <c:v>20.65</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>52.25</c:v>
+                  <c:v>57.76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>52.96</c:v>
+                  <c:v>54.48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.43</c:v>
+                  <c:v>51.08</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>32.74</c:v>
+                  <c:v>31.03</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>30.74</c:v>
+                  <c:v>29.31</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>46.17</c:v>
+                  <c:v>44.81</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>40.55</c:v>
+                  <c:v>37.27</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.03</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>35.01</c:v>
+                  <c:v>34.74</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>35.27</c:v>
+                  <c:v>34.88</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>46.39</c:v>
+                  <c:v>47.09</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>39.19</c:v>
+                  <c:v>37.08</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>33.62</c:v>
+                  <c:v>34.3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>16.99</c:v>
+                  <c:v>17.43</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>30.46</c:v>
+                  <c:v>30.18</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>28.24</c:v>
+                  <c:v>29.37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1655,76 +1658,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>70.13</c:v>
+                  <c:v>68.64</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>61.25</c:v>
+                  <c:v>60.11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60.67</c:v>
+                  <c:v>60.26</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>58.17</c:v>
+                  <c:v>57.42</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>61.19</c:v>
+                  <c:v>60.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.64</c:v>
+                  <c:v>50.29</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>57.66</c:v>
+                  <c:v>58.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>49.17</c:v>
+                  <c:v>48.71</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>59.6</c:v>
+                  <c:v>61.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>59.94</c:v>
+                  <c:v>60.1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>59.4</c:v>
+                  <c:v>58.91</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>52.52</c:v>
+                  <c:v>51.78</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>51.18</c:v>
+                  <c:v>50.45</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>56.35</c:v>
+                  <c:v>55.45</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>54.24</c:v>
+                  <c:v>52.65</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>54.26</c:v>
+                  <c:v>53.91</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>52.02</c:v>
+                  <c:v>51.43</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>51.81</c:v>
+                  <c:v>51.17</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>55.42</c:v>
+                  <c:v>55.14</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>52.94</c:v>
+                  <c:v>51.72</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>50.94</c:v>
+                  <c:v>50.6</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>45.07</c:v>
+                  <c:v>44.66</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>48.55</c:v>
+                  <c:v>47.92</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>47.32</c:v>
+                  <c:v>47.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2781,22 +2784,22 @@
                   <c:v>113.1694952691261</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>114.9674982918469</c:v>
+                  <c:v>113.768829610033</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>122.1266180758187</c:v>
+                  <c:v>116.1303221795618</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>124.8339528715453</c:v>
+                  <c:v>118.7047295203143</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>122.5254387051666</c:v>
+                  <c:v>116.5095611113177</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>123.8829218426343</c:v>
+                  <c:v>117.8003931722659</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>123.3545573612726</c:v>
+                  <c:v>117.2979708632269</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3633,7 +3636,7 @@
         <v>14.48</v>
       </c>
       <c r="F14" s="11">
-        <v>0.3060016906170752</v>
+        <v>0.3067796610169491</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>25</v>
@@ -3647,13 +3650,13 @@
         <v>0.2</v>
       </c>
       <c r="D15" s="10">
-        <v>37.19</v>
+        <v>36.4</v>
       </c>
       <c r="E15" s="10">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
       <c r="F15" s="11">
-        <v>0.1572273879966188</v>
+        <v>0.1542372881355932</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -3673,7 +3676,7 @@
         <v>8.57</v>
       </c>
       <c r="F16" s="11">
-        <v>0.1811073541842773</v>
+        <v>0.1815677966101695</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>27</v>
@@ -3693,7 +3696,7 @@
         <v>8.24</v>
       </c>
       <c r="F17" s="11">
-        <v>0.1741335587489434</v>
+        <v>0.1745762711864407</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>25</v>
@@ -3713,7 +3716,7 @@
         <v>2.59</v>
       </c>
       <c r="F18" s="11">
-        <v>0.05473372781065088</v>
+        <v>0.0548728813559322</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>27</v>
@@ -3727,13 +3730,13 @@
         <v>0.1</v>
       </c>
       <c r="D19" s="10">
-        <v>59.97</v>
+        <v>60.43</v>
       </c>
       <c r="E19" s="10">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="F19" s="11">
-        <v>0.1267962806424345</v>
+        <v>0.1279661016949152</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>25</v>
@@ -3748,7 +3751,7 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="10">
-        <v>47.32</v>
+        <v>47.2</v>
       </c>
       <c r="F20" s="11">
         <v>1</v>
@@ -3865,13 +3868,13 @@
         <v>45</v>
       </c>
       <c r="C6" s="10">
-        <v>70.13</v>
+        <v>68.64</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="10">
-        <v>70.13</v>
+        <v>68.64</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>46</v>
@@ -3886,7 +3889,7 @@
         <v>20.63</v>
       </c>
       <c r="J6" s="10">
-        <v>12.64</v>
+        <v>11.18</v>
       </c>
       <c r="K6" s="10">
         <v>12.5</v>
@@ -3898,7 +3901,7 @@
         <v>8.52</v>
       </c>
       <c r="N6" s="10">
-        <v>7.8</v>
+        <v>7.77</v>
       </c>
       <c r="O6" s="10">
         <v>1191.44</v>
@@ -3915,13 +3918,13 @@
         <v>50</v>
       </c>
       <c r="C7" s="10">
-        <v>61.25</v>
+        <v>60.11</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="10">
-        <v>61.25</v>
+        <v>60.11</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>47</v>
@@ -3936,7 +3939,7 @@
         <v>18.11</v>
       </c>
       <c r="J7" s="10">
-        <v>11.06</v>
+        <v>9.06</v>
       </c>
       <c r="K7" s="10">
         <v>12.32</v>
@@ -3948,7 +3951,7 @@
         <v>3.89</v>
       </c>
       <c r="N7" s="10">
-        <v>7.41</v>
+        <v>8.27</v>
       </c>
       <c r="O7" s="10">
         <v>1408.55</v>
@@ -3965,13 +3968,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="10">
-        <v>60.67</v>
+        <v>60.26</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="10">
-        <v>60.67</v>
+        <v>60.26</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>47</v>
@@ -3986,7 +3989,7 @@
         <v>18.1</v>
       </c>
       <c r="J8" s="10">
-        <v>11.69</v>
+        <v>11.36</v>
       </c>
       <c r="K8" s="10">
         <v>12.48</v>
@@ -3998,7 +4001,7 @@
         <v>3.25</v>
       </c>
       <c r="N8" s="10">
-        <v>5.86</v>
+        <v>5.78</v>
       </c>
       <c r="O8" s="10">
         <v>1342.06</v>
@@ -4015,13 +4018,13 @@
         <v>52</v>
       </c>
       <c r="C9" s="10">
-        <v>58.17</v>
+        <v>57.42</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="10">
-        <v>58.17</v>
+        <v>57.42</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>47</v>
@@ -4036,7 +4039,7 @@
         <v>18.55</v>
       </c>
       <c r="J9" s="10">
-        <v>11.9</v>
+        <v>11.93</v>
       </c>
       <c r="K9" s="10">
         <v>11.76</v>
@@ -4048,7 +4051,7 @@
         <v>3.04</v>
       </c>
       <c r="N9" s="10">
-        <v>4.98</v>
+        <v>4.2</v>
       </c>
       <c r="O9" s="10">
         <v>1498.28</v>
@@ -4065,13 +4068,13 @@
         <v>53</v>
       </c>
       <c r="C10" s="10">
-        <v>61.19</v>
+        <v>60.1</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="10">
-        <v>46.08</v>
+        <v>45.35</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>33</v>
@@ -4086,7 +4089,7 @@
         <v>18.62</v>
       </c>
       <c r="J10" s="10">
-        <v>12.85</v>
+        <v>12.6</v>
       </c>
       <c r="K10" s="10">
         <v>6.81</v>
@@ -4098,7 +4101,7 @@
         <v>7.91</v>
       </c>
       <c r="N10" s="10">
-        <v>6.96</v>
+        <v>6.12</v>
       </c>
       <c r="O10" s="10">
         <v>1492.15</v>
@@ -4115,13 +4118,13 @@
         <v>55</v>
       </c>
       <c r="C11" s="10">
-        <v>50.64</v>
+        <v>50.29</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="10">
-        <v>11.75</v>
+        <v>11.29</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>56</v>
@@ -4130,13 +4133,13 @@
         <v>10</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="I11" s="10">
         <v>17.21</v>
       </c>
       <c r="J11" s="10">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="K11" s="10">
         <v>7.13</v>
@@ -4148,7 +4151,7 @@
         <v>2.68</v>
       </c>
       <c r="N11" s="10">
-        <v>4.69</v>
+        <v>4.56</v>
       </c>
       <c r="O11" s="10">
         <v>1197.6</v>
@@ -4165,13 +4168,13 @@
         <v>57</v>
       </c>
       <c r="C12" s="10">
-        <v>57.66</v>
+        <v>58.2</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="10">
-        <v>43.58</v>
+        <v>46.77</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>33</v>
@@ -4186,7 +4189,7 @@
         <v>16.1</v>
       </c>
       <c r="J12" s="10">
-        <v>11.23</v>
+        <v>11.33</v>
       </c>
       <c r="K12" s="10">
         <v>10.48</v>
@@ -4198,7 +4201,7 @@
         <v>7.08</v>
       </c>
       <c r="N12" s="10">
-        <v>3.99</v>
+        <v>4.43</v>
       </c>
       <c r="O12" s="10">
         <v>1132.11</v>
@@ -4215,13 +4218,13 @@
         <v>59</v>
       </c>
       <c r="C13" s="10">
-        <v>49.17</v>
+        <v>48.71</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="10">
-        <v>22.14</v>
+        <v>20.65</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>56</v>
@@ -4236,7 +4239,7 @@
         <v>10.57</v>
       </c>
       <c r="J13" s="10">
-        <v>10.07</v>
+        <v>10.14</v>
       </c>
       <c r="K13" s="10">
         <v>11.94</v>
@@ -4248,7 +4251,7 @@
         <v>3.67</v>
       </c>
       <c r="N13" s="10">
-        <v>4.7</v>
+        <v>4.17</v>
       </c>
       <c r="O13" s="10">
         <v>1007.09</v>
@@ -4265,19 +4268,19 @@
         <v>60</v>
       </c>
       <c r="C14" s="10">
-        <v>59.6</v>
+        <v>61.2</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="10">
-        <v>52.25</v>
+        <v>57.76</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="H14" s="14" t="s">
         <v>58</v>
@@ -4286,7 +4289,7 @@
         <v>13.72</v>
       </c>
       <c r="J14" s="10">
-        <v>10.41</v>
+        <v>11.48</v>
       </c>
       <c r="K14" s="10">
         <v>14.81</v>
@@ -4298,7 +4301,7 @@
         <v>6.7</v>
       </c>
       <c r="N14" s="10">
-        <v>5.65</v>
+        <v>6.18</v>
       </c>
       <c r="O14" s="10">
         <v>1064.64</v>
@@ -4312,16 +4315,16 @@
     </row>
     <row r="15" spans="2:17">
       <c r="B15" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="10">
-        <v>59.94</v>
+        <v>60.1</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E15" s="10">
-        <v>52.96</v>
+        <v>54.48</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>47</v>
@@ -4336,7 +4339,7 @@
         <v>14.34</v>
       </c>
       <c r="J15" s="10">
-        <v>11.49</v>
+        <v>11.6</v>
       </c>
       <c r="K15" s="10">
         <v>14.67</v>
@@ -4348,7 +4351,7 @@
         <v>6.86</v>
       </c>
       <c r="N15" s="10">
-        <v>4.39</v>
+        <v>4.44</v>
       </c>
       <c r="O15" s="10">
         <v>1120.18</v>
@@ -4362,16 +4365,16 @@
     </row>
     <row r="16" spans="2:17">
       <c r="B16" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="10">
-        <v>59.4</v>
+        <v>58.91</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E16" s="10">
-        <v>51.43</v>
+        <v>51.08</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>47</v>
@@ -4386,7 +4389,7 @@
         <v>13.1</v>
       </c>
       <c r="J16" s="10">
-        <v>11.45</v>
+        <v>11.18</v>
       </c>
       <c r="K16" s="10">
         <v>13.35</v>
@@ -4398,7 +4401,7 @@
         <v>6.77</v>
       </c>
       <c r="N16" s="10">
-        <v>6.36</v>
+        <v>6.14</v>
       </c>
       <c r="O16" s="10">
         <v>1154.15</v>
@@ -4412,16 +4415,16 @@
     </row>
     <row r="17" spans="2:17">
       <c r="B17" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="10">
-        <v>52.52</v>
+        <v>51.78</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="10">
-        <v>32.74</v>
+        <v>31.03</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>56</v>
@@ -4436,7 +4439,7 @@
         <v>14.28</v>
       </c>
       <c r="J17" s="10">
-        <v>9.630000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K17" s="10">
         <v>11.02</v>
@@ -4448,7 +4451,7 @@
         <v>3.36</v>
       </c>
       <c r="N17" s="10">
-        <v>6</v>
+        <v>5.42</v>
       </c>
       <c r="O17" s="10">
         <v>1129.93</v>
@@ -4462,16 +4465,16 @@
     </row>
     <row r="18" spans="2:17">
       <c r="B18" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="10">
-        <v>51.18</v>
+        <v>50.45</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E18" s="10">
-        <v>30.74</v>
+        <v>29.31</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>56</v>
@@ -4498,7 +4501,7 @@
         <v>6.76</v>
       </c>
       <c r="N18" s="10">
-        <v>4.08</v>
+        <v>3.35</v>
       </c>
       <c r="O18" s="10">
         <v>1284.09</v>
@@ -4512,16 +4515,16 @@
     </row>
     <row r="19" spans="2:17">
       <c r="B19" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="10">
-        <v>56.35</v>
+        <v>55.45</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="10">
-        <v>46.17</v>
+        <v>44.81</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>33</v>
@@ -4530,13 +4533,13 @@
         <v>47</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="I19" s="10">
         <v>16.24</v>
       </c>
       <c r="J19" s="10">
-        <v>10.05</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K19" s="10">
         <v>8.970000000000001</v>
@@ -4548,7 +4551,7 @@
         <v>6.96</v>
       </c>
       <c r="N19" s="10">
-        <v>5.92</v>
+        <v>5.19</v>
       </c>
       <c r="O19" s="10">
         <v>1245.32</v>
@@ -4562,16 +4565,16 @@
     </row>
     <row r="20" spans="2:17">
       <c r="B20" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="10">
-        <v>54.24</v>
+        <v>52.65</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E20" s="10">
-        <v>40.55</v>
+        <v>37.27</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>33</v>
@@ -4586,7 +4589,7 @@
         <v>15.96</v>
       </c>
       <c r="J20" s="10">
-        <v>10.86</v>
+        <v>10.15</v>
       </c>
       <c r="K20" s="10">
         <v>7.16</v>
@@ -4598,7 +4601,7 @@
         <v>7.53</v>
       </c>
       <c r="N20" s="10">
-        <v>4.82</v>
+        <v>3.94</v>
       </c>
       <c r="O20" s="10">
         <v>1287.94</v>
@@ -4612,16 +4615,16 @@
     </row>
     <row r="21" spans="2:17">
       <c r="B21" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="10">
-        <v>54.26</v>
+        <v>53.91</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="10">
-        <v>41.03</v>
+        <v>41.5</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>33</v>
@@ -4636,7 +4639,7 @@
         <v>18.25</v>
       </c>
       <c r="J21" s="10">
-        <v>10.9</v>
+        <v>10.57</v>
       </c>
       <c r="K21" s="10">
         <v>8.119999999999999</v>
@@ -4648,7 +4651,7 @@
         <v>4.73</v>
       </c>
       <c r="N21" s="10">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="O21" s="10">
         <v>1266.78</v>
@@ -4662,19 +4665,19 @@
     </row>
     <row r="22" spans="2:17">
       <c r="B22" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C22" s="10">
-        <v>52.02</v>
+        <v>51.43</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E22" s="10">
-        <v>35.01</v>
+        <v>34.74</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>47</v>
@@ -4686,7 +4689,7 @@
         <v>16.09</v>
       </c>
       <c r="J22" s="10">
-        <v>9.27</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K22" s="10">
         <v>7.06</v>
@@ -4698,7 +4701,7 @@
         <v>7.01</v>
       </c>
       <c r="N22" s="10">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="O22" s="10">
         <v>1306.86</v>
@@ -4712,19 +4715,19 @@
     </row>
     <row r="23" spans="2:17">
       <c r="B23" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23" s="10">
-        <v>51.81</v>
+        <v>51.17</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E23" s="10">
-        <v>35.27</v>
+        <v>34.88</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>47</v>
@@ -4736,7 +4739,7 @@
         <v>16.07</v>
       </c>
       <c r="J23" s="10">
-        <v>10.69</v>
+        <v>10.07</v>
       </c>
       <c r="K23" s="10">
         <v>6.66</v>
@@ -4748,7 +4751,7 @@
         <v>4.67</v>
       </c>
       <c r="N23" s="10">
-        <v>5.73</v>
+        <v>5.71</v>
       </c>
       <c r="O23" s="10">
         <v>1376.07</v>
@@ -4762,16 +4765,16 @@
     </row>
     <row r="24" spans="2:17">
       <c r="B24" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="10">
-        <v>55.42</v>
+        <v>55.14</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E24" s="10">
-        <v>46.39</v>
+        <v>47.09</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>33</v>
@@ -4786,7 +4789,7 @@
         <v>14.89</v>
       </c>
       <c r="J24" s="10">
-        <v>11.38</v>
+        <v>11.07</v>
       </c>
       <c r="K24" s="10">
         <v>6.78</v>
@@ -4798,7 +4801,7 @@
         <v>6.97</v>
       </c>
       <c r="N24" s="10">
-        <v>6.7</v>
+        <v>6.73</v>
       </c>
       <c r="O24" s="10">
         <v>1661.7</v>
@@ -4812,16 +4815,16 @@
     </row>
     <row r="25" spans="2:17">
       <c r="B25" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="10">
-        <v>52.94</v>
+        <v>51.72</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E25" s="10">
-        <v>39.19</v>
+        <v>37.08</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>33</v>
@@ -4836,7 +4839,7 @@
         <v>14.56</v>
       </c>
       <c r="J25" s="10">
-        <v>11.33</v>
+        <v>10.2</v>
       </c>
       <c r="K25" s="10">
         <v>4.79</v>
@@ -4848,7 +4851,7 @@
         <v>6.92</v>
       </c>
       <c r="N25" s="10">
-        <v>6.91</v>
+        <v>6.82</v>
       </c>
       <c r="O25" s="10">
         <v>1784.49</v>
@@ -4862,16 +4865,16 @@
     </row>
     <row r="26" spans="2:17">
       <c r="B26" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="10">
-        <v>50.94</v>
+        <v>50.6</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E26" s="10">
-        <v>33.62</v>
+        <v>34.3</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>56</v>
@@ -4886,7 +4889,7 @@
         <v>16.93</v>
       </c>
       <c r="J26" s="10">
-        <v>11.84</v>
+        <v>11.43</v>
       </c>
       <c r="K26" s="10">
         <v>4.7</v>
@@ -4898,7 +4901,7 @@
         <v>4.89</v>
       </c>
       <c r="N26" s="10">
-        <v>3.97</v>
+        <v>4.04</v>
       </c>
       <c r="O26" s="10">
         <v>1674.49</v>
@@ -4912,16 +4915,16 @@
     </row>
     <row r="27" spans="2:17">
       <c r="B27" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="10">
-        <v>45.07</v>
+        <v>44.66</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E27" s="10">
-        <v>16.99</v>
+        <v>17.43</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>56</v>
@@ -4936,7 +4939,7 @@
         <v>12.61</v>
       </c>
       <c r="J27" s="10">
-        <v>8.33</v>
+        <v>8.08</v>
       </c>
       <c r="K27" s="10">
         <v>2.48</v>
@@ -4948,7 +4951,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="10">
-        <v>5.83</v>
+        <v>5.67</v>
       </c>
       <c r="O27" s="10">
         <v>1860.01</v>
@@ -4962,16 +4965,16 @@
     </row>
     <row r="28" spans="2:17">
       <c r="B28" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C28" s="10">
-        <v>48.55</v>
+        <v>47.92</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E28" s="10">
-        <v>30.46</v>
+        <v>30.18</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>56</v>
@@ -4986,7 +4989,7 @@
         <v>15.32</v>
       </c>
       <c r="J28" s="10">
-        <v>8.99</v>
+        <v>8.35</v>
       </c>
       <c r="K28" s="10">
         <v>4.36</v>
@@ -4998,7 +5001,7 @@
         <v>6.86</v>
       </c>
       <c r="N28" s="10">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="O28" s="10">
         <v>1780.68</v>
@@ -5012,16 +5015,16 @@
     </row>
     <row r="29" spans="2:17">
       <c r="B29" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C29" s="10">
-        <v>47.32</v>
+        <v>47.2</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="10">
-        <v>28.24</v>
+        <v>29.37</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>56</v>
@@ -5036,7 +5039,7 @@
         <v>14.48</v>
       </c>
       <c r="J29" s="10">
-        <v>7.44</v>
+        <v>7.28</v>
       </c>
       <c r="K29" s="10">
         <v>8.57</v>
@@ -5048,7 +5051,7 @@
         <v>2.59</v>
       </c>
       <c r="N29" s="10">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="O29" s="14" t="s">
         <v>49</v>
@@ -5118,46 +5121,46 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="15">
         <v>-0.036358</v>
@@ -5166,27 +5169,27 @@
         <v>0.0278</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I6" s="14">
         <v>1</v>
       </c>
       <c r="J6" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="15">
         <v>0.000137</v>
@@ -5195,27 +5198,27 @@
         <v>0.9441000000000001</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="14">
         <v>10</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="15">
         <v>-0.032628</v>
@@ -5224,27 +5227,27 @@
         <v>0.0592</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I8" s="14">
         <v>2</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="15">
         <v>-0.002719</v>
@@ -5253,27 +5256,27 @@
         <v>0.7492</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I9" s="14">
         <v>7</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" s="15">
         <v>9.899999999999999E-05</v>
@@ -5282,27 +5285,27 @@
         <v>0.0223</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I10" s="14">
         <v>11</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="15">
         <v>-8.000000000000001E-05</v>
@@ -5311,27 +5314,27 @@
         <v>0.2363</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" s="14">
         <v>12</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="15">
         <v>-0.000221</v>
@@ -5340,27 +5343,27 @@
         <v>0.8799</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I12" s="14">
         <v>9</v>
       </c>
       <c r="J12" s="18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="15">
         <v>-0.002852</v>
@@ -5369,27 +5372,27 @@
         <v>0.3781</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" s="14">
         <v>6</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="15">
         <v>-0.029501</v>
@@ -5398,27 +5401,27 @@
         <v>0.0005999999999999999</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" s="14">
         <v>3</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="15">
         <v>0.006628</v>
@@ -5427,27 +5430,27 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="15">
         <v>-0.005037</v>
@@ -5456,27 +5459,27 @@
         <v>0.2276</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" s="14">
         <v>5</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C17" s="15">
         <v>-0.000575</v>
@@ -5485,40 +5488,40 @@
         <v>0.8627</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I17" s="14">
         <v>8</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B39" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>45</v>
@@ -5548,57 +5551,57 @@
         <v>60</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N40" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P40" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U40" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V40" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="W40" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="X40" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Y40" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Z40" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AA40" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B41" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C41" s="16">
         <v>0.050404</v>
@@ -5678,7 +5681,7 @@
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B42" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" s="16">
         <v>0.006803</v>
@@ -5758,7 +5761,7 @@
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="16">
         <v>0.033473</v>
@@ -5838,7 +5841,7 @@
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B44" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="16">
         <v>0.005801</v>
@@ -5918,7 +5921,7 @@
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="16">
         <v>0.000145</v>
@@ -5998,7 +6001,7 @@
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="16">
         <v>-6E-06</v>
@@ -6078,7 +6081,7 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="16">
         <v>-0.00157</v>
@@ -6129,13 +6132,13 @@
         <v>3.8E-05</v>
       </c>
       <c r="S47" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T47" s="16">
         <v>0.000618</v>
       </c>
       <c r="U47" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V47" s="16">
         <v>0.000495</v>
@@ -6158,7 +6161,7 @@
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="16">
         <v>-0.013109</v>
@@ -6238,7 +6241,7 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B49" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="16">
         <v>-0.045005</v>
@@ -6318,7 +6321,7 @@
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C50" s="16">
         <v>0.004475</v>
@@ -6398,7 +6401,7 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C51" s="16">
         <v>-0.010339</v>
@@ -6478,10 +6481,10 @@
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D52" s="16">
         <v>0.023665</v>
@@ -6619,37 +6622,37 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" s="16">
         <v>7.2336</v>
@@ -6658,18 +6661,18 @@
         <v>0.0072</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7" s="16">
         <v>0.5046</v>
@@ -6678,18 +6681,18 @@
         <v>0.4775</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="16">
         <v>0.3229</v>
@@ -6698,18 +6701,18 @@
         <v>0.5699</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C9" s="16">
         <v>0.2242</v>
@@ -6718,18 +6721,18 @@
         <v>0.6359</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C10" s="16">
         <v>0.004</v>
@@ -6738,13 +6741,13 @@
         <v>0.9498</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6776,36 +6779,36 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="16">
         <v>0.425</v>
@@ -6813,7 +6816,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C9" s="16">
         <v>0.1599</v>
@@ -6821,7 +6824,7 @@
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" s="16">
         <v>0.3692</v>
@@ -6829,15 +6832,15 @@
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="16">
         <v>0.5031</v>
@@ -6845,27 +6848,27 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -7030,18 +7033,18 @@
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -7049,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D28" s="16">
         <v>0.02178040146827698</v>
@@ -7060,7 +7063,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D29" s="16">
         <v>0.02076428011059761</v>
@@ -7071,7 +7074,7 @@
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D30" s="16">
         <v>0.01783575303852558</v>
@@ -7082,7 +7085,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D31" s="16">
         <v>0.01772940717637539</v>
@@ -7093,7 +7096,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D32" s="16">
         <v>0.01733604446053505</v>
@@ -7104,7 +7107,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D33" s="16">
         <v>0.0167862419039011</v>
@@ -7115,7 +7118,7 @@
         <v>7</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D34" s="16">
         <v>0.01557330787181854</v>
@@ -7126,7 +7129,7 @@
         <v>8</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D35" s="16">
         <v>0.01539521757513285</v>
@@ -7137,7 +7140,7 @@
         <v>9</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D36" s="16">
         <v>0.01488733943551779</v>
@@ -7148,7 +7151,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D37" s="16">
         <v>0.01360253803431988</v>
@@ -7159,7 +7162,7 @@
         <v>11</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D38" s="16">
         <v>0.0134799899533391</v>
@@ -7170,7 +7173,7 @@
         <v>12</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D39" s="16">
         <v>0.01324111688882113</v>
@@ -7181,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D40" s="16">
         <v>0.01247525215148926</v>
@@ -7192,7 +7195,7 @@
         <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D41" s="16">
         <v>0.01242704410105944</v>
@@ -7203,7 +7206,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D42" s="16">
         <v>0.01225554849952459</v>
@@ -7243,12 +7246,12 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -7256,19 +7259,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="2:7">
@@ -7279,16 +7282,16 @@
         <v>0.25</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F6" s="10">
         <v>60</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="2:7">
@@ -7299,16 +7302,16 @@
         <v>0.25</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F7" s="10">
         <v>50</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -7319,16 +7322,16 @@
         <v>0.25</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F8" s="10">
         <v>69</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -7339,16 +7342,16 @@
         <v>0.25</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F9" s="10">
         <v>68</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="2:7">
@@ -7359,16 +7362,16 @@
         <v>0.25</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F10" s="10">
         <v>43</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -7379,16 +7382,16 @@
         <v>0.2</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F11" s="10">
         <v>29</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -7399,16 +7402,16 @@
         <v>0.2</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F12" s="10">
         <v>0</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:7">
@@ -7419,16 +7422,16 @@
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F13" s="10">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="2:7">
@@ -7439,16 +7442,16 @@
         <v>0.2</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="2:7">
@@ -7459,16 +7462,16 @@
         <v>0.2</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F15" s="10">
         <v>48</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -7479,16 +7482,16 @@
         <v>0.2</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F16" s="10">
         <v>56</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -7499,16 +7502,16 @@
         <v>0.2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F17" s="10">
         <v>30</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -7519,16 +7522,16 @@
         <v>0.2</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F18" s="10">
         <v>33</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -7539,16 +7542,16 @@
         <v>0.2</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F19" s="10">
         <v>80</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -7559,16 +7562,16 @@
         <v>0.2</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F20" s="10">
         <v>19</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -7579,16 +7582,16 @@
         <v>0.15</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F21" s="10">
         <v>48</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -7599,16 +7602,16 @@
         <v>0.15</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F22" s="10">
         <v>53</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -7619,16 +7622,16 @@
         <v>0.15</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -7639,16 +7642,16 @@
         <v>0.15</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -7659,16 +7662,16 @@
         <v>0.1</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -7679,16 +7682,16 @@
         <v>0.1</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -7699,16 +7702,16 @@
         <v>0.1</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F27" s="10">
         <v>75</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -7719,16 +7722,16 @@
         <v>0.1</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -7739,16 +7742,16 @@
         <v>0.1</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F29" s="10">
         <v>38</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -7759,16 +7762,16 @@
         <v>0.1</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F30" s="10">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -7779,16 +7782,16 @@
         <v>0.1</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -7799,16 +7802,16 @@
         <v>0.1</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -7850,17 +7853,17 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C5" s="14">
         <v>22</v>
@@ -7868,39 +7871,39 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C6" s="16">
-        <v>0.1550909362864956</v>
+        <v>0.1483538183721982</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C7" s="16">
-        <v>0.1078486730660644</v>
+        <v>0.1067193675889328</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C8" s="16">
-        <v>0.0539510747016974</v>
+        <v>0.05631062061483348</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C9" s="16">
-        <v>-0.04912478825522304</v>
+        <v>0.0378424189052429</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C10" s="11">
         <v>0.5</v>
@@ -7908,7 +7911,7 @@
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C11" s="11">
         <v>0.5454545454545454</v>
@@ -7916,15 +7919,15 @@
     </row>
     <row r="12" spans="2:3">
       <c r="B12" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C12" s="11">
-        <v>0.2335455736127263</v>
+        <v>0.1729797086322691</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C13" s="11">
         <v>0.306871980645762</v>
@@ -7932,7 +7935,7 @@
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C14" s="11">
         <v>0.4945612032498485</v>
@@ -7940,15 +7943,15 @@
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C15" s="10">
-        <v>0.5213441818233974</v>
+        <v>0.4192135232141344</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C16" s="10">
         <v>0.4775014136300051</v>
@@ -7956,24 +7959,24 @@
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -8015,16 +8018,16 @@
         <v>33</v>
       </c>
       <c r="C22" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="11">
-        <v>0.001598189831757129</v>
+        <v>-0.03516352497855219</v>
       </c>
       <c r="E22" s="11">
-        <v>0.03163927438071323</v>
+        <v>-0.01642933677034653</v>
       </c>
       <c r="F22" s="11">
-        <v>0.5555555555555556</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -8032,21 +8035,21 @@
         <v>56</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="11">
-        <v>0.02947379187416812</v>
+        <v>0.05467139182258603</v>
       </c>
       <c r="E23" s="11">
-        <v>0.01347612765786038</v>
+        <v>0.05505192201341436</v>
       </c>
       <c r="F23" s="11">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -8054,34 +8057,34 @@
         <v>36</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -8089,7 +8092,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="10">
-        <v>70.13</v>
+        <v>68.64</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>46</v>
@@ -8098,7 +8101,7 @@
         <v>0.775</v>
       </c>
       <c r="F27" s="10">
-        <v>70.13</v>
+        <v>68.64</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>46</v>
@@ -8110,7 +8113,7 @@
         <v>0.1412242748270999</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K27" s="10">
         <v>114.12242748271</v>
@@ -8124,7 +8127,7 @@
         <v>50</v>
       </c>
       <c r="C28" s="10">
-        <v>61.25</v>
+        <v>60.11</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>47</v>
@@ -8133,7 +8136,7 @@
         <v>0.5</v>
       </c>
       <c r="F28" s="10">
-        <v>61.25</v>
+        <v>60.11</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>47</v>
@@ -8145,7 +8148,7 @@
         <v>-0.02360228603883424</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K28" s="10">
         <v>111.4288773058169</v>
@@ -8159,7 +8162,7 @@
         <v>51</v>
       </c>
       <c r="C29" s="10">
-        <v>60.67</v>
+        <v>60.26</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>47</v>
@@ -8168,7 +8171,7 @@
         <v>0.5</v>
       </c>
       <c r="F29" s="10">
-        <v>60.67</v>
+        <v>60.26</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>47</v>
@@ -8180,7 +8183,7 @@
         <v>0.05820157071963994</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K29" s="10">
         <v>117.9142129885415</v>
@@ -8194,7 +8197,7 @@
         <v>52</v>
       </c>
       <c r="C30" s="10">
-        <v>58.17</v>
+        <v>57.42</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>47</v>
@@ -8203,7 +8206,7 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="10">
-        <v>58.17</v>
+        <v>57.42</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>47</v>
@@ -8215,7 +8218,7 @@
         <v>-0.002045679045305226</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K30" s="10">
         <v>117.6729983538872</v>
@@ -8229,7 +8232,7 @@
         <v>53</v>
       </c>
       <c r="C31" s="10">
-        <v>46.08</v>
+        <v>45.35</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>33</v>
@@ -8238,7 +8241,7 @@
         <v>0.3</v>
       </c>
       <c r="F31" s="10">
-        <v>61.19</v>
+        <v>60.1</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>47</v>
@@ -8250,7 +8253,7 @@
         <v>-0.05921991756860909</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K31" s="10">
         <v>110.7044130913189</v>
@@ -8264,7 +8267,7 @@
         <v>55</v>
       </c>
       <c r="C32" s="10">
-        <v>11.75</v>
+        <v>11.29</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>56</v>
@@ -8273,7 +8276,7 @@
         <v>0.1</v>
       </c>
       <c r="F32" s="10">
-        <v>50.64</v>
+        <v>50.29</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>47</v>
@@ -8285,7 +8288,7 @@
         <v>-0.005468436873747495</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K32" s="10">
         <v>110.0990329966838</v>
@@ -8299,7 +8302,7 @@
         <v>57</v>
       </c>
       <c r="C33" s="10">
-        <v>43.58</v>
+        <v>46.77</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>33</v>
@@ -8308,7 +8311,7 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="10">
-        <v>57.66</v>
+        <v>58.2</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>47</v>
@@ -8320,7 +8323,7 @@
         <v>-0.03312928955666848</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K33" s="10">
         <v>106.4515302526274</v>
@@ -8334,7 +8337,7 @@
         <v>59</v>
       </c>
       <c r="C34" s="10">
-        <v>22.14</v>
+        <v>20.65</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>56</v>
@@ -8343,7 +8346,7 @@
         <v>0.1</v>
       </c>
       <c r="F34" s="10">
-        <v>49.17</v>
+        <v>48.71</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>33</v>
@@ -8355,7 +8358,7 @@
         <v>0.005714484306268553</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K34" s="10">
         <v>107.0598458516343</v>
@@ -8369,7 +8372,7 @@
         <v>60</v>
       </c>
       <c r="C35" s="10">
-        <v>52.25</v>
+        <v>57.76</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>47</v>
@@ -8378,7 +8381,7 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="10">
-        <v>59.6</v>
+        <v>61.2</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>47</v>
@@ -8390,7 +8393,7 @@
         <v>0.02608393447550339</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K35" s="10">
         <v>109.8523878557859</v>
@@ -8401,10 +8404,10 @@
     </row>
     <row r="36" spans="2:12">
       <c r="B36" s="14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10">
-        <v>52.96</v>
+        <v>54.48</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>47</v>
@@ -8413,7 +8416,7 @@
         <v>0.5</v>
       </c>
       <c r="F36" s="10">
-        <v>59.94</v>
+        <v>60.1</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>47</v>
@@ -8425,7 +8428,7 @@
         <v>0.01516274170222642</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K36" s="10">
         <v>111.518051238216</v>
@@ -8436,10 +8439,10 @@
     </row>
     <row r="37" spans="2:12">
       <c r="B37" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10">
-        <v>51.43</v>
+        <v>51.08</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>47</v>
@@ -8448,7 +8451,7 @@
         <v>0.5</v>
       </c>
       <c r="F37" s="10">
-        <v>59.4</v>
+        <v>58.91</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>47</v>
@@ -8460,7 +8463,7 @@
         <v>-0.0104925702898237</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K37" s="10">
         <v>110.3479402470148</v>
@@ -8471,10 +8474,10 @@
     </row>
     <row r="38" spans="2:12">
       <c r="B38" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C38" s="10">
-        <v>32.74</v>
+        <v>31.03</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>56</v>
@@ -8483,7 +8486,7 @@
         <v>0.1</v>
       </c>
       <c r="F38" s="10">
-        <v>52.52</v>
+        <v>51.78</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>47</v>
@@ -8495,7 +8498,7 @@
         <v>0.0136433230377103</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K38" s="10">
         <v>111.8534528423508</v>
@@ -8506,10 +8509,10 @@
     </row>
     <row r="39" spans="2:12">
       <c r="B39" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C39" s="10">
-        <v>30.74</v>
+        <v>29.31</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>56</v>
@@ -8518,7 +8521,7 @@
         <v>0.1</v>
       </c>
       <c r="F39" s="10">
-        <v>51.18</v>
+        <v>50.45</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>47</v>
@@ -8530,7 +8533,7 @@
         <v>-0.003019258774696476</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K39" s="10">
         <v>111.5157383233764</v>
@@ -8541,10 +8544,10 @@
     </row>
     <row r="40" spans="2:12">
       <c r="B40" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C40" s="10">
-        <v>46.17</v>
+        <v>44.81</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>33</v>
@@ -8553,7 +8556,7 @@
         <v>0.3</v>
       </c>
       <c r="F40" s="10">
-        <v>56.35</v>
+        <v>55.45</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>47</v>
@@ -8565,7 +8568,7 @@
         <v>0.01026724054861401</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K40" s="10">
         <v>112.6606972336988</v>
@@ -8576,10 +8579,10 @@
     </row>
     <row r="41" spans="2:12">
       <c r="B41" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C41" s="10">
-        <v>40.55</v>
+        <v>37.27</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>33</v>
@@ -8588,7 +8591,7 @@
         <v>0.3</v>
       </c>
       <c r="F41" s="10">
-        <v>54.24</v>
+        <v>52.65</v>
       </c>
       <c r="G41" s="14" t="s">
         <v>47</v>
@@ -8600,7 +8603,7 @@
         <v>-0.004928801031103957</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K41" s="10">
         <v>112.1054150730085</v>
@@ -8611,10 +8614,10 @@
     </row>
     <row r="42" spans="2:12">
       <c r="B42" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C42" s="10">
-        <v>41.03</v>
+        <v>41.5</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>33</v>
@@ -8623,7 +8626,7 @@
         <v>0.3</v>
       </c>
       <c r="F42" s="10">
-        <v>54.26</v>
+        <v>53.91</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>47</v>
@@ -8635,7 +8638,7 @@
         <v>0.00949178231421397</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K42" s="10">
         <v>113.1694952691261</v>
@@ -8646,19 +8649,19 @@
     </row>
     <row r="43" spans="2:12">
       <c r="B43" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C43" s="10">
-        <v>35.01</v>
+        <v>34.74</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E43" s="9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F43" s="10">
-        <v>52.02</v>
+        <v>51.43</v>
       </c>
       <c r="G43" s="14" t="s">
         <v>47</v>
@@ -8667,13 +8670,13 @@
         <v>0.05295900096414319</v>
       </c>
       <c r="I43" s="11">
-        <v>0.01588770028924296</v>
+        <v>0.005295900096414319</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K43" s="10">
-        <v>114.9674982918469</v>
+        <v>113.768829610033</v>
       </c>
       <c r="L43" s="10">
         <v>115.4963741354999</v>
@@ -8681,19 +8684,19 @@
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C44" s="10">
-        <v>35.27</v>
+        <v>34.88</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="E44" s="9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F44" s="10">
-        <v>51.81</v>
+        <v>51.17</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>47</v>
@@ -8702,13 +8705,13 @@
         <v>0.2075693823715363</v>
       </c>
       <c r="I44" s="11">
-        <v>0.0622708147114609</v>
+        <v>0.02075693823715363</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K44" s="10">
-        <v>122.1266180758187</v>
+        <v>116.1303221795618</v>
       </c>
       <c r="L44" s="10">
         <v>139.4698851809575</v>
@@ -8716,10 +8719,10 @@
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="10">
-        <v>46.39</v>
+        <v>47.09</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>33</v>
@@ -8728,7 +8731,7 @@
         <v>0.3</v>
       </c>
       <c r="F45" s="10">
-        <v>55.42</v>
+        <v>55.14</v>
       </c>
       <c r="G45" s="14" t="s">
         <v>47</v>
@@ -8740,10 +8743,10 @@
         <v>0.0221682614190287</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K45" s="10">
-        <v>124.8339528715453</v>
+        <v>118.7047295203143</v>
       </c>
       <c r="L45" s="10">
         <v>149.7759014302021</v>
@@ -8751,10 +8754,10 @@
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="10">
-        <v>39.19</v>
+        <v>37.08</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>33</v>
@@ -8763,7 +8766,7 @@
         <v>0.3</v>
       </c>
       <c r="F46" s="10">
-        <v>52.94</v>
+        <v>51.72</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>47</v>
@@ -8775,10 +8778,10 @@
         <v>-0.01849267858043475</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K46" s="10">
-        <v>122.5254387051666</v>
+        <v>116.5095611113177</v>
       </c>
       <c r="L46" s="10">
         <v>140.5433760827234</v>
@@ -8786,10 +8789,10 @@
     </row>
     <row r="47" spans="2:12">
       <c r="B47" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" s="10">
-        <v>33.62</v>
+        <v>34.3</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>56</v>
@@ -8798,7 +8801,7 @@
         <v>0.1</v>
       </c>
       <c r="F47" s="10">
-        <v>50.94</v>
+        <v>50.6</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>47</v>
@@ -8810,10 +8813,10 @@
         <v>0.01107919426213355</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K47" s="10">
-        <v>123.8829218426343</v>
+        <v>117.8003931722659</v>
       </c>
       <c r="L47" s="10">
         <v>156.1144497414892</v>
@@ -8821,10 +8824,10 @@
     </row>
     <row r="48" spans="2:12">
       <c r="B48" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C48" s="10">
-        <v>16.99</v>
+        <v>17.43</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>56</v>
@@ -8833,7 +8836,7 @@
         <v>0.1</v>
       </c>
       <c r="F48" s="10">
-        <v>45.07</v>
+        <v>44.66</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>33</v>
@@ -8845,10 +8848,10 @@
         <v>-0.004265030833167561</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K48" s="10">
-        <v>123.3545573612726</v>
+        <v>117.2979708632269</v>
       </c>
       <c r="L48" s="10">
         <v>149.4561203249849</v>
@@ -8856,7 +8859,7 @@
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -8882,7 +8885,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -8943,104 +8946,104 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -9051,10 +9054,10 @@
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -9065,10 +9068,10 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -9079,10 +9082,10 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -9093,10 +9096,10 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -9107,10 +9110,10 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -9121,10 +9124,10 @@
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -9135,10 +9138,10 @@
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -9149,10 +9152,10 @@
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -29,7 +29,7 @@
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 15:48:37  |  Source: output/exports/score_*.json</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 17:03:44  |  Source: output/exports/score_*.json</t>
   </si>
   <si>
     <t>47.2</t>
@@ -938,7 +938,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 15:48:37 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-28 17:03:44 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -24,15 +24,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="306">
   <si>
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-28 17:03:44  |  Source: output/exports/score_*.json</t>
-  </si>
-  <si>
-    <t>47.2</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-29 15:03:12  |  Source: output/exports/score_*.json</t>
+  </si>
+  <si>
+    <t>47.7</t>
   </si>
   <si>
     <t>Raw Regime / Label</t>
@@ -44,7 +44,7 @@
     <t>CALIBRATED ACTION</t>
   </si>
   <si>
-    <t>🔴 SELL — 29.4</t>
+    <t>🔴 SELL — 34.0</t>
   </si>
   <si>
     <t>Recommended Equity</t>
@@ -62,7 +62,7 @@
     <t>Pillar Dispersion</t>
   </si>
   <si>
-    <t>MEDIUM (σ=13.67)</t>
+    <t>LOW (σ=13.67)</t>
   </si>
   <si>
     <t>Data As-Of</t>
@@ -188,15 +188,15 @@
     <t>2022-Q1</t>
   </si>
   <si>
+    <t>SELL</t>
+  </si>
+  <si>
     <t>HIGH</t>
   </si>
   <si>
     <t>2022-Q2</t>
   </si>
   <si>
-    <t>SELL</t>
-  </si>
-  <si>
     <t>2022-Q3</t>
   </si>
   <si>
@@ -695,13 +695,13 @@
     <t>model_quality</t>
   </si>
   <si>
-    <t>Accuracy=42.5% F1=0.369 → quality 40</t>
+    <t>Accuracy=42.5% F1=0.369</t>
   </si>
   <si>
     <t>ml_signal</t>
   </si>
   <si>
-    <t>Forecast: DOWN (conf=50%)</t>
+    <t>Forecast: DOWN (conf=50.0%)</t>
   </si>
   <si>
     <t>ftse_upgrade</t>
@@ -938,7 +938,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-28 17:03:44 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-29 15:03:12 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1295,13 +1295,13 @@
                   <c:v>7.28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.57</c:v>
+                  <c:v>8.08</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.24</c:v>
+                  <c:v>7.63</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.59</c:v>
+                  <c:v>4.16</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>6.04</c:v>
@@ -1479,76 +1479,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>68.64</c:v>
+                  <c:v>66.86</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.11</c:v>
+                  <c:v>62.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60.26</c:v>
+                  <c:v>63.44</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>57.42</c:v>
+                  <c:v>60.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45.35</c:v>
+                  <c:v>30.12</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.29</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.77</c:v>
+                  <c:v>40.99</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.65</c:v>
+                  <c:v>6.74</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>57.76</c:v>
+                  <c:v>50.08</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>54.48</c:v>
+                  <c:v>47.42</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>51.08</c:v>
+                  <c:v>45.78</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>31.03</c:v>
+                  <c:v>29.45</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29.31</c:v>
+                  <c:v>23.54</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>44.81</c:v>
+                  <c:v>42.92</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>37.27</c:v>
+                  <c:v>33.65</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>41.5</c:v>
+                  <c:v>42.96</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>34.74</c:v>
+                  <c:v>34.51</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>34.88</c:v>
+                  <c:v>38.94</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>47.09</c:v>
+                  <c:v>49.86</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>37.08</c:v>
+                  <c:v>41.55</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>34.3</c:v>
+                  <c:v>40.48</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17.43</c:v>
+                  <c:v>21.85</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>30.18</c:v>
+                  <c:v>30.12</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>29.37</c:v>
+                  <c:v>33.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1658,76 +1658,76 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
                 <c:pt idx="0">
-                  <c:v>68.64</c:v>
+                  <c:v>66.86</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60.11</c:v>
+                  <c:v>62.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>60.26</c:v>
+                  <c:v>63.44</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>57.42</c:v>
+                  <c:v>60.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60.1</c:v>
+                  <c:v>59.69</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>50.29</c:v>
+                  <c:v>51.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>58.2</c:v>
+                  <c:v>57.52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>48.71</c:v>
+                  <c:v>45.88</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>61.2</c:v>
+                  <c:v>58.49</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>60.1</c:v>
+                  <c:v>57.35</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>58.91</c:v>
+                  <c:v>56.64</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>51.78</c:v>
+                  <c:v>50.28</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>50.45</c:v>
+                  <c:v>47.02</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>55.45</c:v>
+                  <c:v>53.7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>52.65</c:v>
+                  <c:v>49.74</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>53.91</c:v>
+                  <c:v>53.13</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>51.43</c:v>
+                  <c:v>49.61</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>51.17</c:v>
+                  <c:v>51.03</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>55.14</c:v>
+                  <c:v>55.2</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>51.72</c:v>
+                  <c:v>51.98</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>50.6</c:v>
+                  <c:v>51.47</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>44.66</c:v>
+                  <c:v>44.38</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>47.92</c:v>
+                  <c:v>46.59</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>47.2</c:v>
+                  <c:v>47.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2748,58 +2748,58 @@
                   <c:v>117.6729983538872</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>110.7044130913189</c:v>
+                  <c:v>115.3501365996978</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>110.0990329966838</c:v>
+                  <c:v>114.7193516593242</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>106.4515302526274</c:v>
+                  <c:v>110.9187810404491</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>107.0598458516343</c:v>
+                  <c:v>111.5526246739752</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>109.8523878557859</c:v>
+                  <c:v>114.4623560265416</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>111.518051238216</c:v>
+                  <c:v>115.5036939099769</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>110.3479402470148</c:v>
+                  <c:v>114.7765355337261</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>111.8534528423508</c:v>
+                  <c:v>116.3424688851619</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>111.5157383233764</c:v>
+                  <c:v>115.9912008651105</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>112.6606972336988</c:v>
+                  <c:v>117.1821104259152</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>112.1054150730085</c:v>
+                  <c:v>116.9895879903505</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>113.1694952691261</c:v>
+                  <c:v>118.1000276925845</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>113.768829610033</c:v>
+                  <c:v>118.7254736406282</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>116.1303221795618</c:v>
+                  <c:v>126.1186056112342</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>118.7047295203143</c:v>
+                  <c:v>128.9144358302274</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>116.5095611113177</c:v>
+                  <c:v>126.5304626040409</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>117.8003931722659</c:v>
+                  <c:v>130.7360293298443</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>117.2979708632269</c:v>
+                  <c:v>130.1784361337466</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3636,7 +3636,7 @@
         <v>14.48</v>
       </c>
       <c r="F14" s="11">
-        <v>0.3067796610169491</v>
+        <v>0.3037549821690791</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>25</v>
@@ -3656,7 +3656,7 @@
         <v>7.28</v>
       </c>
       <c r="F15" s="11">
-        <v>0.1542372881355932</v>
+        <v>0.1527165932452276</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -3670,13 +3670,13 @@
         <v>0.2</v>
       </c>
       <c r="D16" s="10">
-        <v>42.87</v>
+        <v>40.39</v>
       </c>
       <c r="E16" s="10">
-        <v>8.57</v>
+        <v>8.08</v>
       </c>
       <c r="F16" s="11">
-        <v>0.1815677966101695</v>
+        <v>0.1694986364589889</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>27</v>
@@ -3690,13 +3690,13 @@
         <v>0.15</v>
       </c>
       <c r="D17" s="10">
-        <v>54.93</v>
+        <v>50.84</v>
       </c>
       <c r="E17" s="10">
-        <v>8.24</v>
+        <v>7.63</v>
       </c>
       <c r="F17" s="11">
-        <v>0.1745762711864407</v>
+        <v>0.1600587371512482</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>25</v>
@@ -3710,13 +3710,13 @@
         <v>0.1</v>
       </c>
       <c r="D18" s="10">
-        <v>25.91</v>
+        <v>41.57</v>
       </c>
       <c r="E18" s="10">
-        <v>2.59</v>
+        <v>4.16</v>
       </c>
       <c r="F18" s="11">
-        <v>0.0548728813559322</v>
+        <v>0.08726662471155863</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>27</v>
@@ -3736,7 +3736,7 @@
         <v>6.04</v>
       </c>
       <c r="F19" s="11">
-        <v>0.1279661016949152</v>
+        <v>0.1267044262638976</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>25</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="10">
-        <v>47.2</v>
+        <v>47.67</v>
       </c>
       <c r="F20" s="11">
         <v>1</v>
@@ -3868,13 +3868,13 @@
         <v>45</v>
       </c>
       <c r="C6" s="10">
-        <v>68.64</v>
+        <v>66.86</v>
       </c>
       <c r="D6" s="14" t="s">
         <v>46</v>
       </c>
       <c r="E6" s="10">
-        <v>68.64</v>
+        <v>66.86</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>46</v>
@@ -3895,10 +3895,10 @@
         <v>12.5</v>
       </c>
       <c r="L6" s="10">
-        <v>8.039999999999999</v>
+        <v>7.65</v>
       </c>
       <c r="M6" s="10">
-        <v>8.52</v>
+        <v>7.13</v>
       </c>
       <c r="N6" s="10">
         <v>7.77</v>
@@ -3918,13 +3918,13 @@
         <v>50</v>
       </c>
       <c r="C7" s="10">
-        <v>60.11</v>
+        <v>62.75</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E7" s="10">
-        <v>60.11</v>
+        <v>62.75</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>47</v>
@@ -3942,13 +3942,13 @@
         <v>9.06</v>
       </c>
       <c r="K7" s="10">
-        <v>12.32</v>
+        <v>12.3</v>
       </c>
       <c r="L7" s="10">
-        <v>8.460000000000001</v>
+        <v>11.28</v>
       </c>
       <c r="M7" s="10">
-        <v>3.89</v>
+        <v>3.73</v>
       </c>
       <c r="N7" s="10">
         <v>8.27</v>
@@ -3968,13 +3968,13 @@
         <v>51</v>
       </c>
       <c r="C8" s="10">
-        <v>60.26</v>
+        <v>63.44</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E8" s="10">
-        <v>60.26</v>
+        <v>63.44</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>47</v>
@@ -3992,13 +3992,13 @@
         <v>11.36</v>
       </c>
       <c r="K8" s="10">
-        <v>12.48</v>
+        <v>12.5</v>
       </c>
       <c r="L8" s="10">
-        <v>9.289999999999999</v>
+        <v>11.75</v>
       </c>
       <c r="M8" s="10">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N8" s="10">
         <v>5.78</v>
@@ -4018,13 +4018,13 @@
         <v>52</v>
       </c>
       <c r="C9" s="10">
-        <v>57.42</v>
+        <v>60.22</v>
       </c>
       <c r="D9" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E9" s="10">
-        <v>57.42</v>
+        <v>60.22</v>
       </c>
       <c r="F9" s="14" t="s">
         <v>47</v>
@@ -4042,13 +4042,13 @@
         <v>11.93</v>
       </c>
       <c r="K9" s="10">
-        <v>11.76</v>
+        <v>11.75</v>
       </c>
       <c r="L9" s="10">
-        <v>7.94</v>
+        <v>9.01</v>
       </c>
       <c r="M9" s="10">
-        <v>3.04</v>
+        <v>4.78</v>
       </c>
       <c r="N9" s="10">
         <v>4.2</v>
@@ -4068,22 +4068,22 @@
         <v>53</v>
       </c>
       <c r="C10" s="10">
-        <v>60.1</v>
+        <v>59.69</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="10">
-        <v>45.35</v>
+        <v>30.12</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I10" s="10">
         <v>18.62</v>
@@ -4092,13 +4092,13 @@
         <v>12.6</v>
       </c>
       <c r="K10" s="10">
-        <v>6.81</v>
+        <v>7.46</v>
       </c>
       <c r="L10" s="10">
-        <v>8.039999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="M10" s="10">
-        <v>7.91</v>
+        <v>6.57</v>
       </c>
       <c r="N10" s="10">
         <v>6.12</v>
@@ -4115,19 +4115,19 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" s="10">
-        <v>50.29</v>
+        <v>51.25</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E11" s="10">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>10</v>
@@ -4142,13 +4142,13 @@
         <v>11</v>
       </c>
       <c r="K11" s="10">
-        <v>7.13</v>
+        <v>7.34</v>
       </c>
       <c r="L11" s="10">
-        <v>7.71</v>
+        <v>7.1</v>
       </c>
       <c r="M11" s="10">
-        <v>2.68</v>
+        <v>4.04</v>
       </c>
       <c r="N11" s="10">
         <v>4.56</v>
@@ -4168,13 +4168,13 @@
         <v>57</v>
       </c>
       <c r="C12" s="10">
-        <v>58.2</v>
+        <v>57.52</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="10">
-        <v>46.77</v>
+        <v>40.99</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>33</v>
@@ -4192,13 +4192,13 @@
         <v>11.33</v>
       </c>
       <c r="K12" s="10">
-        <v>10.48</v>
+        <v>8.15</v>
       </c>
       <c r="L12" s="10">
-        <v>8.779999999999999</v>
+        <v>11.72</v>
       </c>
       <c r="M12" s="10">
-        <v>7.08</v>
+        <v>5.79</v>
       </c>
       <c r="N12" s="10">
         <v>4.43</v>
@@ -4218,16 +4218,16 @@
         <v>59</v>
       </c>
       <c r="C13" s="10">
-        <v>48.71</v>
+        <v>45.88</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E13" s="10">
-        <v>20.65</v>
+        <v>6.74</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>10</v>
@@ -4242,13 +4242,13 @@
         <v>10.14</v>
       </c>
       <c r="K13" s="10">
-        <v>11.94</v>
+        <v>10.06</v>
       </c>
       <c r="L13" s="10">
-        <v>8.220000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="M13" s="10">
-        <v>3.67</v>
+        <v>2.9</v>
       </c>
       <c r="N13" s="10">
         <v>4.17</v>
@@ -4268,13 +4268,13 @@
         <v>60</v>
       </c>
       <c r="C14" s="10">
-        <v>61.2</v>
+        <v>58.49</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E14" s="10">
-        <v>57.76</v>
+        <v>50.08</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>47</v>
@@ -4292,13 +4292,13 @@
         <v>11.48</v>
       </c>
       <c r="K14" s="10">
-        <v>14.81</v>
+        <v>12.87</v>
       </c>
       <c r="L14" s="10">
-        <v>8.31</v>
+        <v>8.85</v>
       </c>
       <c r="M14" s="10">
-        <v>6.7</v>
+        <v>5.39</v>
       </c>
       <c r="N14" s="10">
         <v>6.18</v>
@@ -4318,16 +4318,16 @@
         <v>62</v>
       </c>
       <c r="C15" s="10">
-        <v>60.1</v>
+        <v>57.35</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E15" s="10">
-        <v>54.48</v>
+        <v>47.42</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>47</v>
@@ -4342,13 +4342,13 @@
         <v>11.6</v>
       </c>
       <c r="K15" s="10">
-        <v>14.67</v>
+        <v>12.98</v>
       </c>
       <c r="L15" s="10">
-        <v>8.19</v>
+        <v>8.41</v>
       </c>
       <c r="M15" s="10">
-        <v>6.86</v>
+        <v>5.58</v>
       </c>
       <c r="N15" s="10">
         <v>4.44</v>
@@ -4368,16 +4368,16 @@
         <v>63</v>
       </c>
       <c r="C16" s="10">
-        <v>58.91</v>
+        <v>56.64</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E16" s="10">
-        <v>51.08</v>
+        <v>45.78</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>47</v>
@@ -4392,13 +4392,13 @@
         <v>11.18</v>
       </c>
       <c r="K16" s="10">
-        <v>13.35</v>
+        <v>11.95</v>
       </c>
       <c r="L16" s="10">
-        <v>8.369999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M16" s="10">
-        <v>6.77</v>
+        <v>5.22</v>
       </c>
       <c r="N16" s="10">
         <v>6.14</v>
@@ -4418,16 +4418,16 @@
         <v>64</v>
       </c>
       <c r="C17" s="10">
-        <v>51.78</v>
+        <v>50.28</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E17" s="10">
-        <v>31.03</v>
+        <v>29.45</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>10</v>
@@ -4442,13 +4442,13 @@
         <v>9.470000000000001</v>
       </c>
       <c r="K17" s="10">
-        <v>11.02</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L17" s="10">
-        <v>8.23</v>
+        <v>8.52</v>
       </c>
       <c r="M17" s="10">
-        <v>3.36</v>
+        <v>3.06</v>
       </c>
       <c r="N17" s="10">
         <v>5.42</v>
@@ -4468,22 +4468,22 @@
         <v>65</v>
       </c>
       <c r="C18" s="10">
-        <v>50.45</v>
+        <v>47.02</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E18" s="10">
-        <v>29.31</v>
+        <v>23.54</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I18" s="10">
         <v>16.64</v>
@@ -4492,13 +4492,13 @@
         <v>4</v>
       </c>
       <c r="K18" s="10">
-        <v>11.64</v>
+        <v>10.56</v>
       </c>
       <c r="L18" s="10">
-        <v>8.06</v>
+        <v>7.28</v>
       </c>
       <c r="M18" s="10">
-        <v>6.76</v>
+        <v>5.19</v>
       </c>
       <c r="N18" s="10">
         <v>3.35</v>
@@ -4518,13 +4518,13 @@
         <v>66</v>
       </c>
       <c r="C19" s="10">
-        <v>55.45</v>
+        <v>53.7</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="10">
-        <v>44.81</v>
+        <v>42.92</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>33</v>
@@ -4542,13 +4542,13 @@
         <v>9.880000000000001</v>
       </c>
       <c r="K19" s="10">
-        <v>8.970000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="L19" s="10">
-        <v>8.210000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="M19" s="10">
-        <v>6.96</v>
+        <v>5.7</v>
       </c>
       <c r="N19" s="10">
         <v>5.19</v>
@@ -4568,22 +4568,22 @@
         <v>67</v>
       </c>
       <c r="C20" s="10">
-        <v>52.65</v>
+        <v>49.74</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E20" s="10">
-        <v>37.27</v>
+        <v>33.65</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I20" s="10">
         <v>15.96</v>
@@ -4592,13 +4592,13 @@
         <v>10.15</v>
       </c>
       <c r="K20" s="10">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="L20" s="10">
-        <v>7.91</v>
+        <v>6.38</v>
       </c>
       <c r="M20" s="10">
-        <v>7.53</v>
+        <v>6.19</v>
       </c>
       <c r="N20" s="10">
         <v>3.94</v>
@@ -4618,13 +4618,13 @@
         <v>68</v>
       </c>
       <c r="C21" s="10">
-        <v>53.91</v>
+        <v>53.13</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E21" s="10">
-        <v>41.5</v>
+        <v>42.96</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>33</v>
@@ -4642,10 +4642,10 @@
         <v>10.57</v>
       </c>
       <c r="K21" s="10">
-        <v>8.119999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="L21" s="10">
-        <v>7.95</v>
+        <v>7.13</v>
       </c>
       <c r="M21" s="10">
         <v>4.73</v>
@@ -4668,16 +4668,16 @@
         <v>69</v>
       </c>
       <c r="C22" s="10">
-        <v>51.43</v>
+        <v>49.61</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E22" s="10">
-        <v>34.74</v>
+        <v>34.51</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>47</v>
@@ -4692,13 +4692,13 @@
         <v>8.640000000000001</v>
       </c>
       <c r="K22" s="10">
-        <v>7.06</v>
+        <v>7.41</v>
       </c>
       <c r="L22" s="10">
-        <v>7.92</v>
+        <v>7.09</v>
       </c>
       <c r="M22" s="10">
-        <v>7.01</v>
+        <v>5.67</v>
       </c>
       <c r="N22" s="10">
         <v>4.71</v>
@@ -4718,16 +4718,16 @@
         <v>70</v>
       </c>
       <c r="C23" s="10">
-        <v>51.17</v>
+        <v>51.03</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E23" s="10">
-        <v>34.88</v>
+        <v>38.94</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>47</v>
@@ -4742,13 +4742,13 @@
         <v>10.07</v>
       </c>
       <c r="K23" s="10">
-        <v>6.66</v>
+        <v>7.1</v>
       </c>
       <c r="L23" s="10">
-        <v>7.99</v>
+        <v>7.46</v>
       </c>
       <c r="M23" s="10">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="N23" s="10">
         <v>5.71</v>
@@ -4768,13 +4768,13 @@
         <v>71</v>
       </c>
       <c r="C24" s="10">
-        <v>55.14</v>
+        <v>55.2</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E24" s="10">
-        <v>47.09</v>
+        <v>49.86</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>33</v>
@@ -4792,13 +4792,13 @@
         <v>11.07</v>
       </c>
       <c r="K24" s="10">
-        <v>6.78</v>
+        <v>7.47</v>
       </c>
       <c r="L24" s="10">
-        <v>8.699999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="M24" s="10">
-        <v>6.97</v>
+        <v>5.7</v>
       </c>
       <c r="N24" s="10">
         <v>6.73</v>
@@ -4818,13 +4818,13 @@
         <v>72</v>
       </c>
       <c r="C25" s="10">
-        <v>51.72</v>
+        <v>51.98</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E25" s="10">
-        <v>37.08</v>
+        <v>41.55</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>33</v>
@@ -4833,7 +4833,7 @@
         <v>47</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I25" s="10">
         <v>14.56</v>
@@ -4842,13 +4842,13 @@
         <v>10.2</v>
       </c>
       <c r="K25" s="10">
-        <v>4.79</v>
+        <v>5.55</v>
       </c>
       <c r="L25" s="10">
-        <v>8.43</v>
+        <v>9.74</v>
       </c>
       <c r="M25" s="10">
-        <v>6.92</v>
+        <v>5.11</v>
       </c>
       <c r="N25" s="10">
         <v>6.82</v>
@@ -4868,22 +4868,22 @@
         <v>73</v>
       </c>
       <c r="C26" s="10">
-        <v>50.6</v>
+        <v>51.47</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>47</v>
       </c>
       <c r="E26" s="10">
-        <v>34.3</v>
+        <v>40.48</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I26" s="10">
         <v>16.93</v>
@@ -4892,10 +4892,10 @@
         <v>11.43</v>
       </c>
       <c r="K26" s="10">
-        <v>4.7</v>
+        <v>5.79</v>
       </c>
       <c r="L26" s="10">
-        <v>8.609999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="M26" s="10">
         <v>4.89</v>
@@ -4918,22 +4918,22 @@
         <v>74</v>
       </c>
       <c r="C27" s="10">
-        <v>44.66</v>
+        <v>44.38</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E27" s="10">
-        <v>17.43</v>
+        <v>21.85</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I27" s="10">
         <v>12.61</v>
@@ -4942,13 +4942,13 @@
         <v>8.08</v>
       </c>
       <c r="K27" s="10">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="L27" s="10">
-        <v>8.82</v>
+        <v>9.77</v>
       </c>
       <c r="M27" s="10">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="N27" s="10">
         <v>5.67</v>
@@ -4968,22 +4968,22 @@
         <v>75</v>
       </c>
       <c r="C28" s="10">
-        <v>47.92</v>
+        <v>46.59</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E28" s="10">
-        <v>30.18</v>
+        <v>30.12</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I28" s="10">
         <v>15.32</v>
@@ -4992,13 +4992,13 @@
         <v>8.35</v>
       </c>
       <c r="K28" s="10">
-        <v>4.36</v>
+        <v>4.92</v>
       </c>
       <c r="L28" s="10">
-        <v>8.609999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="M28" s="10">
-        <v>6.86</v>
+        <v>5.39</v>
       </c>
       <c r="N28" s="10">
         <v>4.42</v>
@@ -5018,16 +5018,16 @@
         <v>76</v>
       </c>
       <c r="C29" s="10">
-        <v>47.2</v>
+        <v>47.67</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="10">
-        <v>29.37</v>
+        <v>33.97</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
@@ -5042,13 +5042,13 @@
         <v>7.28</v>
       </c>
       <c r="K29" s="10">
-        <v>8.57</v>
+        <v>8.08</v>
       </c>
       <c r="L29" s="10">
-        <v>8.24</v>
+        <v>7.63</v>
       </c>
       <c r="M29" s="10">
-        <v>2.59</v>
+        <v>4.16</v>
       </c>
       <c r="N29" s="10">
         <v>6.04</v>
@@ -5539,7 +5539,7 @@
         <v>53</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>57</v>
@@ -7667,8 +7667,8 @@
       <c r="E25" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F25" s="14" t="s">
-        <v>94</v>
+      <c r="F25" s="10">
+        <v>39.7</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>187</v>
@@ -7687,8 +7687,8 @@
       <c r="E26" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="14" t="s">
-        <v>94</v>
+      <c r="F26" s="10">
+        <v>42.5</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>187</v>
@@ -7874,7 +7874,7 @@
         <v>241</v>
       </c>
       <c r="C6" s="16">
-        <v>0.1483538183721982</v>
+        <v>0.2837804645096819</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -7882,7 +7882,7 @@
         <v>242</v>
       </c>
       <c r="C7" s="16">
-        <v>0.1067193675889328</v>
+        <v>0.251270468661773</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -7890,7 +7890,7 @@
         <v>243</v>
       </c>
       <c r="C8" s="16">
-        <v>0.05631062061483348</v>
+        <v>0.03964834070416489</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -7898,7 +7898,7 @@
         <v>244</v>
       </c>
       <c r="C9" s="16">
-        <v>0.0378424189052429</v>
+        <v>-0.0254093732354602</v>
       </c>
     </row>
     <row r="10" spans="2:3">
@@ -7914,7 +7914,7 @@
         <v>246</v>
       </c>
       <c r="C11" s="11">
-        <v>0.5454545454545454</v>
+        <v>0.5909090909090909</v>
       </c>
     </row>
     <row r="12" spans="2:3">
@@ -7922,7 +7922,7 @@
         <v>247</v>
       </c>
       <c r="C12" s="11">
-        <v>0.1729797086322691</v>
+        <v>0.3017843613374662</v>
       </c>
     </row>
     <row r="13" spans="2:3">
@@ -7930,7 +7930,7 @@
         <v>248</v>
       </c>
       <c r="C13" s="11">
-        <v>0.306871980645762</v>
+        <v>0.3056281529812772</v>
       </c>
     </row>
     <row r="14" spans="2:3">
@@ -7946,7 +7946,7 @@
         <v>250</v>
       </c>
       <c r="C15" s="10">
-        <v>0.4192135232141344</v>
+        <v>0.6829570846962959</v>
       </c>
     </row>
     <row r="16" spans="2:3">
@@ -8001,13 +8001,13 @@
         <v>47</v>
       </c>
       <c r="C21" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" s="11">
-        <v>0.02110257050780219</v>
+        <v>0.02931877005550193</v>
       </c>
       <c r="E21" s="11">
-        <v>0.0131170626569212</v>
+        <v>0.02403825543019816</v>
       </c>
       <c r="F21" s="11">
         <v>0.5</v>
@@ -8018,33 +8018,33 @@
         <v>33</v>
       </c>
       <c r="C22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D22" s="11">
-        <v>-0.03516352497855219</v>
+        <v>0.03282067277409505</v>
       </c>
       <c r="E22" s="11">
-        <v>-0.01642933677034653</v>
+        <v>0.03163927438071323</v>
       </c>
       <c r="F22" s="11">
-        <v>0.4285714285714285</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" s="14">
         <v>8</v>
       </c>
       <c r="D23" s="11">
-        <v>0.05467139182258603</v>
+        <v>-0.01185240655140339</v>
       </c>
       <c r="E23" s="11">
-        <v>0.05505192201341436</v>
+        <v>-0.02331096225865564</v>
       </c>
       <c r="F23" s="11">
-        <v>0.625</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -8092,7 +8092,7 @@
         <v>45</v>
       </c>
       <c r="C27" s="10">
-        <v>68.64</v>
+        <v>66.86</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>46</v>
@@ -8101,7 +8101,7 @@
         <v>0.775</v>
       </c>
       <c r="F27" s="10">
-        <v>68.64</v>
+        <v>66.86</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>46</v>
@@ -8127,7 +8127,7 @@
         <v>50</v>
       </c>
       <c r="C28" s="10">
-        <v>60.11</v>
+        <v>62.75</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>47</v>
@@ -8136,7 +8136,7 @@
         <v>0.5</v>
       </c>
       <c r="F28" s="10">
-        <v>60.11</v>
+        <v>62.75</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>47</v>
@@ -8162,7 +8162,7 @@
         <v>51</v>
       </c>
       <c r="C29" s="10">
-        <v>60.26</v>
+        <v>63.44</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>47</v>
@@ -8171,7 +8171,7 @@
         <v>0.5</v>
       </c>
       <c r="F29" s="10">
-        <v>60.26</v>
+        <v>63.44</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>47</v>
@@ -8197,7 +8197,7 @@
         <v>52</v>
       </c>
       <c r="C30" s="10">
-        <v>57.42</v>
+        <v>60.22</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>47</v>
@@ -8206,7 +8206,7 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="10">
-        <v>57.42</v>
+        <v>60.22</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>47</v>
@@ -8232,16 +8232,16 @@
         <v>53</v>
       </c>
       <c r="C31" s="10">
-        <v>45.35</v>
+        <v>30.12</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E31" s="9">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F31" s="10">
-        <v>60.1</v>
+        <v>59.69</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>47</v>
@@ -8250,13 +8250,13 @@
         <v>-0.197399725228697</v>
       </c>
       <c r="I31" s="11">
-        <v>-0.05921991756860909</v>
+        <v>-0.0197399725228697</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>267</v>
       </c>
       <c r="K31" s="10">
-        <v>110.7044130913189</v>
+        <v>115.3501365996978</v>
       </c>
       <c r="L31" s="10">
         <v>100.5170214194588</v>
@@ -8264,19 +8264,19 @@
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" s="10">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E32" s="9">
         <v>0.1</v>
       </c>
       <c r="F32" s="10">
-        <v>50.29</v>
+        <v>51.25</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>47</v>
@@ -8291,7 +8291,7 @@
         <v>267</v>
       </c>
       <c r="K32" s="10">
-        <v>110.0990329966838</v>
+        <v>114.7193516593242</v>
       </c>
       <c r="L32" s="10">
         <v>95.02031155576445</v>
@@ -8302,7 +8302,7 @@
         <v>57</v>
       </c>
       <c r="C33" s="10">
-        <v>46.77</v>
+        <v>40.99</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>33</v>
@@ -8311,7 +8311,7 @@
         <v>0.3</v>
       </c>
       <c r="F33" s="10">
-        <v>58.2</v>
+        <v>57.52</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>47</v>
@@ -8326,7 +8326,7 @@
         <v>267</v>
       </c>
       <c r="K33" s="10">
-        <v>106.4515302526274</v>
+        <v>110.9187810404491</v>
       </c>
       <c r="L33" s="10">
         <v>84.52712683811188</v>
@@ -8337,16 +8337,16 @@
         <v>59</v>
       </c>
       <c r="C34" s="10">
-        <v>20.65</v>
+        <v>6.74</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E34" s="9">
         <v>0.1</v>
       </c>
       <c r="F34" s="10">
-        <v>48.71</v>
+        <v>45.88</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>33</v>
@@ -8361,7 +8361,7 @@
         <v>268</v>
       </c>
       <c r="K34" s="10">
-        <v>107.0598458516343</v>
+        <v>111.5526246739752</v>
       </c>
       <c r="L34" s="10">
         <v>89.35741623581549</v>
@@ -8372,7 +8372,7 @@
         <v>60</v>
       </c>
       <c r="C35" s="10">
-        <v>57.76</v>
+        <v>50.08</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>47</v>
@@ -8381,7 +8381,7 @@
         <v>0.5</v>
       </c>
       <c r="F35" s="10">
-        <v>61.2</v>
+        <v>58.49</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>47</v>
@@ -8396,7 +8396,7 @@
         <v>267</v>
       </c>
       <c r="K35" s="10">
-        <v>109.8523878557859</v>
+        <v>114.4623560265416</v>
       </c>
       <c r="L35" s="10">
         <v>94.01900221580608</v>
@@ -8407,16 +8407,16 @@
         <v>62</v>
       </c>
       <c r="C36" s="10">
-        <v>54.48</v>
+        <v>47.42</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E36" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F36" s="10">
-        <v>60.1</v>
+        <v>57.35</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>47</v>
@@ -8425,13 +8425,13 @@
         <v>0.03032548340445285</v>
       </c>
       <c r="I36" s="11">
-        <v>0.01516274170222642</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>267</v>
+        <v>0.009097645021335853</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>268</v>
       </c>
       <c r="K36" s="10">
-        <v>111.518051238216</v>
+        <v>115.5036939099769</v>
       </c>
       <c r="L36" s="10">
         <v>96.87017390720473</v>
@@ -8442,16 +8442,16 @@
         <v>63</v>
       </c>
       <c r="C37" s="10">
-        <v>51.08</v>
+        <v>45.78</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E37" s="9">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F37" s="10">
-        <v>58.91</v>
+        <v>56.64</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>47</v>
@@ -8460,13 +8460,13 @@
         <v>-0.0209851405796474</v>
       </c>
       <c r="I37" s="11">
-        <v>-0.0104925702898237</v>
-      </c>
-      <c r="J37" s="13" t="s">
-        <v>268</v>
+        <v>-0.00629554217389422</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>267</v>
       </c>
       <c r="K37" s="10">
-        <v>110.3479402470148</v>
+        <v>114.7765355337261</v>
       </c>
       <c r="L37" s="10">
         <v>94.83733968978714</v>
@@ -8477,16 +8477,16 @@
         <v>64</v>
       </c>
       <c r="C38" s="10">
-        <v>31.03</v>
+        <v>29.45</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E38" s="9">
         <v>0.1</v>
       </c>
       <c r="F38" s="10">
-        <v>51.78</v>
+        <v>50.28</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>47</v>
@@ -8501,7 +8501,7 @@
         <v>268</v>
       </c>
       <c r="K38" s="10">
-        <v>111.8534528423508</v>
+        <v>116.3424688851619</v>
       </c>
       <c r="L38" s="10">
         <v>107.7763043040354</v>
@@ -8512,19 +8512,19 @@
         <v>65</v>
       </c>
       <c r="C39" s="10">
-        <v>29.31</v>
+        <v>23.54</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E39" s="9">
         <v>0.1</v>
       </c>
       <c r="F39" s="10">
-        <v>50.45</v>
+        <v>47.02</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H39" s="11">
         <v>-0.03019258774696476</v>
@@ -8536,7 +8536,7 @@
         <v>267</v>
       </c>
       <c r="K39" s="10">
-        <v>111.5157383233764</v>
+        <v>115.9912008651105</v>
       </c>
       <c r="L39" s="10">
         <v>104.5222587792923</v>
@@ -8547,7 +8547,7 @@
         <v>66</v>
       </c>
       <c r="C40" s="10">
-        <v>44.81</v>
+        <v>42.92</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>33</v>
@@ -8556,7 +8556,7 @@
         <v>0.3</v>
       </c>
       <c r="F40" s="10">
-        <v>55.45</v>
+        <v>53.7</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>47</v>
@@ -8571,7 +8571,7 @@
         <v>268</v>
       </c>
       <c r="K40" s="10">
-        <v>112.6606972336988</v>
+        <v>117.1821104259152</v>
       </c>
       <c r="L40" s="10">
         <v>108.0994426911972</v>
@@ -8582,31 +8582,31 @@
         <v>67</v>
       </c>
       <c r="C41" s="10">
-        <v>37.27</v>
+        <v>33.65</v>
       </c>
       <c r="D41" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F41" s="10">
+        <v>49.74</v>
+      </c>
+      <c r="G41" s="14" t="s">
         <v>33</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="F41" s="10">
-        <v>52.65</v>
-      </c>
-      <c r="G41" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="H41" s="11">
         <v>-0.01642933677034653</v>
       </c>
       <c r="I41" s="11">
-        <v>-0.004928801031103957</v>
+        <v>-0.001642933677034653</v>
       </c>
       <c r="J41" s="17" t="s">
         <v>267</v>
       </c>
       <c r="K41" s="10">
-        <v>112.1054150730085</v>
+        <v>116.9895879903505</v>
       </c>
       <c r="L41" s="10">
         <v>106.3234405425367</v>
@@ -8617,7 +8617,7 @@
         <v>68</v>
       </c>
       <c r="C42" s="10">
-        <v>41.5</v>
+        <v>42.96</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>33</v>
@@ -8626,7 +8626,7 @@
         <v>0.3</v>
       </c>
       <c r="F42" s="10">
-        <v>53.91</v>
+        <v>53.13</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>47</v>
@@ -8641,7 +8641,7 @@
         <v>268</v>
       </c>
       <c r="K42" s="10">
-        <v>113.1694952691261</v>
+        <v>118.1000276925845</v>
       </c>
       <c r="L42" s="10">
         <v>109.6874370509635</v>
@@ -8652,19 +8652,19 @@
         <v>69</v>
       </c>
       <c r="C43" s="10">
-        <v>34.74</v>
+        <v>34.51</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E43" s="9">
         <v>0.1</v>
       </c>
       <c r="F43" s="10">
-        <v>51.43</v>
+        <v>49.61</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H43" s="11">
         <v>0.05295900096414319</v>
@@ -8676,7 +8676,7 @@
         <v>268</v>
       </c>
       <c r="K43" s="10">
-        <v>113.768829610033</v>
+        <v>118.7254736406282</v>
       </c>
       <c r="L43" s="10">
         <v>115.4963741354999</v>
@@ -8687,16 +8687,16 @@
         <v>70</v>
       </c>
       <c r="C44" s="10">
-        <v>34.88</v>
+        <v>38.94</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E44" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F44" s="10">
-        <v>51.17</v>
+        <v>51.03</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>47</v>
@@ -8705,13 +8705,13 @@
         <v>0.2075693823715363</v>
       </c>
       <c r="I44" s="11">
-        <v>0.02075693823715363</v>
+        <v>0.0622708147114609</v>
       </c>
       <c r="J44" s="13" t="s">
         <v>268</v>
       </c>
       <c r="K44" s="10">
-        <v>116.1303221795618</v>
+        <v>126.1186056112342</v>
       </c>
       <c r="L44" s="10">
         <v>139.4698851809575</v>
@@ -8722,7 +8722,7 @@
         <v>71</v>
       </c>
       <c r="C45" s="10">
-        <v>47.09</v>
+        <v>49.86</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>33</v>
@@ -8731,7 +8731,7 @@
         <v>0.3</v>
       </c>
       <c r="F45" s="10">
-        <v>55.14</v>
+        <v>55.2</v>
       </c>
       <c r="G45" s="14" t="s">
         <v>47</v>
@@ -8746,7 +8746,7 @@
         <v>268</v>
       </c>
       <c r="K45" s="10">
-        <v>118.7047295203143</v>
+        <v>128.9144358302274</v>
       </c>
       <c r="L45" s="10">
         <v>149.7759014302021</v>
@@ -8757,7 +8757,7 @@
         <v>72</v>
       </c>
       <c r="C46" s="10">
-        <v>37.08</v>
+        <v>41.55</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>33</v>
@@ -8766,7 +8766,7 @@
         <v>0.3</v>
       </c>
       <c r="F46" s="10">
-        <v>51.72</v>
+        <v>51.98</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>47</v>
@@ -8781,7 +8781,7 @@
         <v>267</v>
       </c>
       <c r="K46" s="10">
-        <v>116.5095611113177</v>
+        <v>126.5304626040409</v>
       </c>
       <c r="L46" s="10">
         <v>140.5433760827234</v>
@@ -8792,16 +8792,16 @@
         <v>73</v>
       </c>
       <c r="C47" s="10">
-        <v>34.3</v>
+        <v>40.48</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="E47" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F47" s="10">
-        <v>50.6</v>
+        <v>51.47</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>47</v>
@@ -8810,13 +8810,13 @@
         <v>0.1107919426213355</v>
       </c>
       <c r="I47" s="11">
-        <v>0.01107919426213355</v>
+        <v>0.03323758278640065</v>
       </c>
       <c r="J47" s="13" t="s">
         <v>268</v>
       </c>
       <c r="K47" s="10">
-        <v>117.8003931722659</v>
+        <v>130.7360293298443</v>
       </c>
       <c r="L47" s="10">
         <v>156.1144497414892</v>
@@ -8827,16 +8827,16 @@
         <v>74</v>
       </c>
       <c r="C48" s="10">
-        <v>17.43</v>
+        <v>21.85</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E48" s="9">
         <v>0.1</v>
       </c>
       <c r="F48" s="10">
-        <v>44.66</v>
+        <v>44.38</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>33</v>
@@ -8851,7 +8851,7 @@
         <v>267</v>
       </c>
       <c r="K48" s="10">
-        <v>117.2979708632269</v>
+        <v>130.1784361337466</v>
       </c>
       <c r="L48" s="10">
         <v>149.4561203249849</v>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -29,7 +29,7 @@
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-29 15:03:12  |  Source: output/exports/score_*.json</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-29 16:27:01  |  Source: output/exports/score_*.json</t>
   </si>
   <si>
     <t>47.7</t>
@@ -131,7 +131,7 @@
     <t>COMPOSITE SCORE HISTORY vs VN-INDEX</t>
   </si>
   <si>
-    <t>Two-tier scores: Total Score = raw composite (reference) | Calibrated Score = action signal (z-score vs prior quarters, point-in-time). Pillar columns are weighted contributions (raw × weight). Fwd Return = VN-Index return of the NEXT quarter (signal evaluation).</t>
+    <t>Two-tier scores: Total Score = raw composite (reference) | Calibrated Score = relative regime/allocation signal vs PRIOR quarters only (point-in-time, v2: σ-floor 5.0, z winsorised ±3, bounded ±25 vs raw — saturation near 5/95 by design, NOT a return forecast). Pillar columns are weighted contributions (raw × weight). Fwd Return = VN-Index return of the NEXT quarter (signal evaluation).</t>
   </si>
   <si>
     <t>Quarter</t>
@@ -188,15 +188,15 @@
     <t>2022-Q1</t>
   </si>
   <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>2022-Q2</t>
+  </si>
+  <si>
     <t>SELL</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>2022-Q2</t>
-  </si>
-  <si>
     <t>2022-Q3</t>
   </si>
   <si>
@@ -740,10 +740,10 @@
     <t>3/3 components with data → average over 3</t>
   </si>
   <si>
-    <t>SIGNAL EFFICACY — DOES THE CALIBRATED ACTION SIGNAL PREDICT NEXT-QUARTER RETURNS?</t>
-  </si>
-  <si>
-    <t>Primary test = CALIBRATED action signal (z-score vs prior quarters, point-in-time). Signal at quarter t is evaluated against the VN-Index return over quarter t+1. Raw composite shown as comparison. No look-ahead.</t>
+    <t>SIGNAL EFFICACY — DOES THE CALIBRATED ACTION SIGNAL PREDICT STRICT FORWARD (t+1) RETURNS?</t>
+  </si>
+  <si>
+    <t>Primary test = CALIBRATED action signal (relative regime vs prior quarters only, point-in-time, winsorised v2). Signal at quarter t is evaluated against the VN-Index return over quarter t+1 (strict forward return — outcome data is never an input to scoring). Raw composite shown as comparison. No look-ahead.</t>
   </si>
   <si>
     <t>Quarters evaluated (N)</t>
@@ -938,7 +938,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-29 15:03:12 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-09-29 16:27:01 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1491,16 +1491,16 @@
                   <c:v>60.22</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.12</c:v>
+                  <c:v>39.12</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>26.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>40.99</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.74</c:v>
+                  <c:v>20.88</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>50.08</c:v>
@@ -2748,58 +2748,58 @@
                   <c:v>117.6729983538872</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>115.3501365996978</c:v>
+                  <c:v>110.7044130913189</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>114.7193516593242</c:v>
+                  <c:v>110.0990329966838</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110.9187810404491</c:v>
+                  <c:v>106.4515302526274</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>111.5526246739752</c:v>
+                  <c:v>107.0598458516343</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>114.4623560265416</c:v>
+                  <c:v>109.8523878557859</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>115.5036939099769</c:v>
+                  <c:v>110.8517858852439</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>114.7765355337261</c:v>
+                  <c:v>110.1539137921519</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>116.3424688851619</c:v>
+                  <c:v>111.6567792218863</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>115.9912008651105</c:v>
+                  <c:v>111.3196585114663</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>117.1821104259152</c:v>
+                  <c:v>112.462604223193</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>116.9895879903505</c:v>
+                  <c:v>112.2778356233077</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>118.1000276925845</c:v>
+                  <c:v>113.3435523977553</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>118.7254736406282</c:v>
+                  <c:v>113.9438085278265</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>126.1186056112342</c:v>
+                  <c:v>121.0391823161809</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>128.9144358302274</c:v>
+                  <c:v>123.7224105517115</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>126.5304626040409</c:v>
+                  <c:v>121.4344517801821</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>130.7360293298443</c:v>
+                  <c:v>125.4706394243471</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>130.1784361337466</c:v>
+                  <c:v>124.935503278545</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4074,16 +4074,16 @@
         <v>47</v>
       </c>
       <c r="E10" s="10">
-        <v>30.12</v>
+        <v>39.12</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10" s="10">
         <v>18.62</v>
@@ -4115,7 +4115,7 @@
     </row>
     <row r="11" spans="2:17">
       <c r="B11" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="10">
         <v>51.25</v>
@@ -4124,10 +4124,10 @@
         <v>47</v>
       </c>
       <c r="E11" s="10">
-        <v>0</v>
+        <v>26.25</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>10</v>
@@ -4224,10 +4224,10 @@
         <v>33</v>
       </c>
       <c r="E13" s="10">
-        <v>6.74</v>
+        <v>20.88</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>10</v>
@@ -4427,7 +4427,7 @@
         <v>29.45</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>10</v>
@@ -4477,13 +4477,13 @@
         <v>23.54</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I18" s="10">
         <v>16.64</v>
@@ -4577,13 +4577,13 @@
         <v>33.65</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>47</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I20" s="10">
         <v>15.96</v>
@@ -4677,7 +4677,7 @@
         <v>34.51</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>47</v>
@@ -4833,7 +4833,7 @@
         <v>47</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I25" s="10">
         <v>14.56</v>
@@ -4883,7 +4883,7 @@
         <v>10</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I26" s="10">
         <v>16.93</v>
@@ -4927,13 +4927,13 @@
         <v>21.85</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I27" s="10">
         <v>12.61</v>
@@ -4977,13 +4977,13 @@
         <v>30.12</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I28" s="10">
         <v>15.32</v>
@@ -5027,7 +5027,7 @@
         <v>33.97</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
@@ -5539,7 +5539,7 @@
         <v>53</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>57</v>
@@ -7874,7 +7874,7 @@
         <v>241</v>
       </c>
       <c r="C6" s="16">
-        <v>0.2837804645096819</v>
+        <v>0.2294181544909315</v>
       </c>
     </row>
     <row r="7" spans="2:3">
@@ -7882,7 +7882,7 @@
         <v>242</v>
       </c>
       <c r="C7" s="16">
-        <v>0.251270468661773</v>
+        <v>0.1835121400338792</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -7922,7 +7922,7 @@
         <v>247</v>
       </c>
       <c r="C12" s="11">
-        <v>0.3017843613374662</v>
+        <v>0.2493550327854499</v>
       </c>
     </row>
     <row r="13" spans="2:3">
@@ -7946,7 +7946,7 @@
         <v>250</v>
       </c>
       <c r="C15" s="10">
-        <v>0.6829570846962959</v>
+        <v>0.5491911124734257</v>
       </c>
     </row>
     <row r="16" spans="2:3">
@@ -8018,33 +8018,33 @@
         <v>33</v>
       </c>
       <c r="C22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D22" s="11">
-        <v>0.03282067277409505</v>
+        <v>0.009798632973815845</v>
       </c>
       <c r="E22" s="11">
-        <v>0.03163927438071323</v>
+        <v>0.03098237889258304</v>
       </c>
       <c r="F22" s="11">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="11">
-        <v>-0.01185240655140339</v>
+        <v>0.01465435325963855</v>
       </c>
       <c r="E23" s="11">
-        <v>-0.02331096225865564</v>
+        <v>-0.01642933677034653</v>
       </c>
       <c r="F23" s="11">
-        <v>0.375</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -8232,13 +8232,13 @@
         <v>53</v>
       </c>
       <c r="C31" s="10">
-        <v>30.12</v>
+        <v>39.12</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="E31" s="9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F31" s="10">
         <v>59.69</v>
@@ -8250,13 +8250,13 @@
         <v>-0.197399725228697</v>
       </c>
       <c r="I31" s="11">
-        <v>-0.0197399725228697</v>
+        <v>-0.05921991756860909</v>
       </c>
       <c r="J31" s="17" t="s">
         <v>267</v>
       </c>
       <c r="K31" s="10">
-        <v>115.3501365996978</v>
+        <v>110.7044130913189</v>
       </c>
       <c r="L31" s="10">
         <v>100.5170214194588</v>
@@ -8264,13 +8264,13 @@
     </row>
     <row r="32" spans="2:12">
       <c r="B32" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="10">
+        <v>26.25</v>
+      </c>
+      <c r="D32" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="C32" s="10">
-        <v>0</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="E32" s="9">
         <v>0.1</v>
@@ -8291,7 +8291,7 @@
         <v>267</v>
       </c>
       <c r="K32" s="10">
-        <v>114.7193516593242</v>
+        <v>110.0990329966838</v>
       </c>
       <c r="L32" s="10">
         <v>95.02031155576445</v>
@@ -8326,7 +8326,7 @@
         <v>267</v>
       </c>
       <c r="K33" s="10">
-        <v>110.9187810404491</v>
+        <v>106.4515302526274</v>
       </c>
       <c r="L33" s="10">
         <v>84.52712683811188</v>
@@ -8337,10 +8337,10 @@
         <v>59</v>
       </c>
       <c r="C34" s="10">
-        <v>6.74</v>
+        <v>20.88</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E34" s="9">
         <v>0.1</v>
@@ -8361,7 +8361,7 @@
         <v>268</v>
       </c>
       <c r="K34" s="10">
-        <v>111.5526246739752</v>
+        <v>107.0598458516343</v>
       </c>
       <c r="L34" s="10">
         <v>89.35741623581549</v>
@@ -8396,7 +8396,7 @@
         <v>267</v>
       </c>
       <c r="K35" s="10">
-        <v>114.4623560265416</v>
+        <v>109.8523878557859</v>
       </c>
       <c r="L35" s="10">
         <v>94.01900221580608</v>
@@ -8431,7 +8431,7 @@
         <v>268</v>
       </c>
       <c r="K36" s="10">
-        <v>115.5036939099769</v>
+        <v>110.8517858852439</v>
       </c>
       <c r="L36" s="10">
         <v>96.87017390720473</v>
@@ -8466,7 +8466,7 @@
         <v>267</v>
       </c>
       <c r="K37" s="10">
-        <v>114.7765355337261</v>
+        <v>110.1539137921519</v>
       </c>
       <c r="L37" s="10">
         <v>94.83733968978714</v>
@@ -8480,7 +8480,7 @@
         <v>29.45</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E38" s="9">
         <v>0.1</v>
@@ -8501,7 +8501,7 @@
         <v>268</v>
       </c>
       <c r="K38" s="10">
-        <v>116.3424688851619</v>
+        <v>111.6567792218863</v>
       </c>
       <c r="L38" s="10">
         <v>107.7763043040354</v>
@@ -8515,7 +8515,7 @@
         <v>23.54</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E39" s="9">
         <v>0.1</v>
@@ -8536,7 +8536,7 @@
         <v>267</v>
       </c>
       <c r="K39" s="10">
-        <v>115.9912008651105</v>
+        <v>111.3196585114663</v>
       </c>
       <c r="L39" s="10">
         <v>104.5222587792923</v>
@@ -8571,7 +8571,7 @@
         <v>268</v>
       </c>
       <c r="K40" s="10">
-        <v>117.1821104259152</v>
+        <v>112.462604223193</v>
       </c>
       <c r="L40" s="10">
         <v>108.0994426911972</v>
@@ -8585,7 +8585,7 @@
         <v>33.65</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E41" s="9">
         <v>0.1</v>
@@ -8606,7 +8606,7 @@
         <v>267</v>
       </c>
       <c r="K41" s="10">
-        <v>116.9895879903505</v>
+        <v>112.2778356233077</v>
       </c>
       <c r="L41" s="10">
         <v>106.3234405425367</v>
@@ -8641,7 +8641,7 @@
         <v>268</v>
       </c>
       <c r="K42" s="10">
-        <v>118.1000276925845</v>
+        <v>113.3435523977553</v>
       </c>
       <c r="L42" s="10">
         <v>109.6874370509635</v>
@@ -8655,7 +8655,7 @@
         <v>34.51</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E43" s="9">
         <v>0.1</v>
@@ -8676,7 +8676,7 @@
         <v>268</v>
       </c>
       <c r="K43" s="10">
-        <v>118.7254736406282</v>
+        <v>113.9438085278265</v>
       </c>
       <c r="L43" s="10">
         <v>115.4963741354999</v>
@@ -8711,7 +8711,7 @@
         <v>268</v>
       </c>
       <c r="K44" s="10">
-        <v>126.1186056112342</v>
+        <v>121.0391823161809</v>
       </c>
       <c r="L44" s="10">
         <v>139.4698851809575</v>
@@ -8746,7 +8746,7 @@
         <v>268</v>
       </c>
       <c r="K45" s="10">
-        <v>128.9144358302274</v>
+        <v>123.7224105517115</v>
       </c>
       <c r="L45" s="10">
         <v>149.7759014302021</v>
@@ -8781,7 +8781,7 @@
         <v>267</v>
       </c>
       <c r="K46" s="10">
-        <v>126.5304626040409</v>
+        <v>121.4344517801821</v>
       </c>
       <c r="L46" s="10">
         <v>140.5433760827234</v>
@@ -8816,7 +8816,7 @@
         <v>268</v>
       </c>
       <c r="K47" s="10">
-        <v>130.7360293298443</v>
+        <v>125.4706394243471</v>
       </c>
       <c r="L47" s="10">
         <v>156.1144497414892</v>
@@ -8830,7 +8830,7 @@
         <v>21.85</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E48" s="9">
         <v>0.1</v>
@@ -8851,7 +8851,7 @@
         <v>267</v>
       </c>
       <c r="K48" s="10">
-        <v>130.1784361337466</v>
+        <v>124.935503278545</v>
       </c>
       <c r="L48" s="10">
         <v>149.4561203249849</v>

--- a/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
+++ b/output/exports/VN_Index_Quant_Factor_Analysis.xlsx
@@ -17,22 +17,22 @@
     <sheet name="07_Methodology" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Factor_Scores'!$B$5:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Factor_Scores'!$B$5:$G$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="309">
   <si>
     <t>VN-INDEX QUARTERLY QUANT FACTOR WORKBOOK</t>
   </si>
   <si>
-    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-09-29 16:27:01  |  Source: output/exports/score_*.json</t>
-  </si>
-  <si>
-    <t>47.7</t>
+    <t>Latest full-model quarter: 2026-Q4  |  Generated at: 2026-10-01 14:40:52  |  Source: output/exports/score_*.json</t>
+  </si>
+  <si>
+    <t>46.7</t>
   </si>
   <si>
     <t>Raw Regime / Label</t>
@@ -44,7 +44,7 @@
     <t>CALIBRATED ACTION</t>
   </si>
   <si>
-    <t>🔴 SELL — 34.0</t>
+    <t>🔴 SELL — 31.5</t>
   </si>
   <si>
     <t>Recommended Equity</t>
@@ -62,13 +62,13 @@
     <t>Pillar Dispersion</t>
   </si>
   <si>
-    <t>LOW (σ=13.67)</t>
+    <t>MEDIUM (σ=10.16)</t>
   </si>
   <si>
     <t>Data As-Of</t>
   </si>
   <si>
-    <t>2026-09-25</t>
+    <t>2026-09-30</t>
   </si>
   <si>
     <t>Point-in-Time</t>
@@ -290,25 +290,46 @@
     <t>Economic Reading</t>
   </si>
   <si>
+    <t>delta_vn1y_yield</t>
+  </si>
+  <si>
+    <t>**</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>A rise in delta_vn1y_yield is a headwind for next-quarter VN-Index returns (statistically significant, p=0.042).</t>
+  </si>
+  <si>
     <t>delta_dxy</t>
   </si>
   <si>
-    <t>**</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>A rise in delta_dxy is a headwind for next-quarter VN-Index returns (statistically significant, p=0.028).</t>
+    <t>***</t>
+  </si>
+  <si>
+    <t>A rise in delta_dxy is a headwind for next-quarter VN-Index returns (statistically significant, p=0.008).</t>
+  </si>
+  <si>
+    <t>pe_zscore</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>A rise in pe_zscore is a headwind for next-quarter VN-Index returns (not significant, p=0.708).</t>
   </si>
   <si>
     <t>delta_us10y</t>
   </si>
   <si>
-    <t>—</t>
+    <t>A rise in delta_us10y is a headwind for next-quarter VN-Index returns (statistically significant, p=0.019).</t>
+  </si>
+  <si>
+    <t>delta_usdjpy</t>
   </si>
   <si>
     <t>+</t>
@@ -317,121 +338,106 @@
     <t>FAIL</t>
   </si>
   <si>
-    <t>A rise in delta_us10y is supportive of next-quarter VN-Index returns (not significant, p=0.944).</t>
-  </si>
-  <si>
-    <t>delta_usdjpy</t>
+    <t>A rise in delta_usdjpy is a headwind for next-quarter VN-Index returns (statistically significant, p=0.000).</t>
+  </si>
+  <si>
+    <t>usd_vnd_pct_change</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>A rise in usd_vnd_pct_change is a headwind for next-quarter VN-Index returns (not significant, p=0.124).</t>
+  </si>
+  <si>
+    <t>rsi_14</t>
+  </si>
+  <si>
+    <t>A rise in rsi_14 is supportive of next-quarter VN-Index returns (not significant, p=0.473).</t>
+  </si>
+  <si>
+    <t>macd_hist</t>
+  </si>
+  <si>
+    <t>A rise in macd_hist is a headwind for next-quarter VN-Index returns (not significant, p=0.805).</t>
+  </si>
+  <si>
+    <t>rvol_20d</t>
+  </si>
+  <si>
+    <t>A rise in rvol_20d is a headwind for next-quarter VN-Index returns (not significant, p=0.986).</t>
+  </si>
+  <si>
+    <t>drawdown_from_peak</t>
+  </si>
+  <si>
+    <t>A rise in drawdown_from_peak is a headwind for next-quarter VN-Index returns (not significant, p=0.507).</t>
+  </si>
+  <si>
+    <t>price_vs_ma200</t>
+  </si>
+  <si>
+    <t>A rise in price_vs_ma200 is supportive of next-quarter VN-Index returns (not significant, p=0.811).</t>
+  </si>
+  <si>
+    <t>log_return_lag1</t>
+  </si>
+  <si>
+    <t>A rise in log_return_lag1 is a headwind for next-quarter VN-Index returns (not significant, p=0.232).</t>
+  </si>
+  <si>
+    <t>log_return_lag5</t>
+  </si>
+  <si>
+    <t>A rise in log_return_lag5 is supportive of next-quarter VN-Index returns (not significant, p=0.677).</t>
+  </si>
+  <si>
+    <t>Sign-check pass rate:</t>
+  </si>
+  <si>
+    <t>4/13 (31%)</t>
+  </si>
+  <si>
+    <t>BETA STABILITY ACROSS QUARTERS (sign consistency = % quarters with same sign as latest)</t>
+  </si>
+  <si>
+    <t>Sign Consistency</t>
+  </si>
+  <si>
+    <t>bb_pct</t>
+  </si>
+  <si>
+    <t>VAR GRANGER CAUSALITY — WHICH FACTORS LEAD THE VN-INDEX?</t>
+  </si>
+  <si>
+    <t>H0: factor does NOT Granger-cause VNI returns. p &lt; 0.05 → reject H0 → factor has leading power.</t>
+  </si>
+  <si>
+    <t>F-Statistic</t>
+  </si>
+  <si>
+    <t>Granger-causes VNI?</t>
+  </si>
+  <si>
+    <t>Verdict</t>
+  </si>
+  <si>
+    <t>YES — LEADING</t>
+  </si>
+  <si>
+    <t>delta_dxy contains predictive information for future VN-Index returns.</t>
   </si>
   <si>
     <t>*</t>
   </si>
   <si>
-    <t>A rise in delta_usdjpy is a headwind for next-quarter VN-Index returns (weakly significant, p=0.059).</t>
-  </si>
-  <si>
-    <t>usd_vnd_pct_change</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>A rise in usd_vnd_pct_change is a headwind for next-quarter VN-Index returns (not significant, p=0.749).</t>
-  </si>
-  <si>
-    <t>rsi_14</t>
-  </si>
-  <si>
-    <t>A rise in rsi_14 is supportive of next-quarter VN-Index returns (statistically significant, p=0.022).</t>
-  </si>
-  <si>
-    <t>macd_hist</t>
-  </si>
-  <si>
-    <t>A rise in macd_hist is a headwind for next-quarter VN-Index returns (not significant, p=0.236).</t>
-  </si>
-  <si>
-    <t>bb_pct</t>
-  </si>
-  <si>
-    <t>A rise in bb_pct is a headwind for next-quarter VN-Index returns (not significant, p=0.880).</t>
-  </si>
-  <si>
-    <t>rvol_20d</t>
-  </si>
-  <si>
-    <t>A rise in rvol_20d is a headwind for next-quarter VN-Index returns (not significant, p=0.378).</t>
-  </si>
-  <si>
-    <t>drawdown_from_peak</t>
-  </si>
-  <si>
-    <t>***</t>
-  </si>
-  <si>
-    <t>A rise in drawdown_from_peak is a headwind for next-quarter VN-Index returns (statistically significant, p=0.001).</t>
-  </si>
-  <si>
-    <t>price_vs_ma200</t>
-  </si>
-  <si>
-    <t>A rise in price_vs_ma200 is supportive of next-quarter VN-Index returns (weakly significant, p=0.089).</t>
-  </si>
-  <si>
-    <t>log_return_lag1</t>
-  </si>
-  <si>
-    <t>A rise in log_return_lag1 is a headwind for next-quarter VN-Index returns (not significant, p=0.228).</t>
-  </si>
-  <si>
-    <t>log_return_lag5</t>
-  </si>
-  <si>
-    <t>A rise in log_return_lag5 is a headwind for next-quarter VN-Index returns (not significant, p=0.863).</t>
-  </si>
-  <si>
-    <t>Sign-check pass rate:</t>
-  </si>
-  <si>
-    <t>1/12 (8%)</t>
-  </si>
-  <si>
-    <t>BETA STABILITY ACROSS QUARTERS (sign consistency = % quarters with same sign as latest)</t>
-  </si>
-  <si>
-    <t>Sign Consistency</t>
-  </si>
-  <si>
-    <t>VAR GRANGER CAUSALITY — WHICH FACTORS LEAD THE VN-INDEX?</t>
-  </si>
-  <si>
-    <t>H0: factor does NOT Granger-cause VNI returns. p &lt; 0.05 → reject H0 → factor has leading power.</t>
-  </si>
-  <si>
-    <t>F-Statistic</t>
-  </si>
-  <si>
-    <t>Granger-causes VNI?</t>
-  </si>
-  <si>
-    <t>Verdict</t>
-  </si>
-  <si>
-    <t>YES — LEADING</t>
-  </si>
-  <si>
-    <t>delta_dxy contains predictive information for future VN-Index returns.</t>
-  </si>
-  <si>
-    <t>delta_vn1y_yield</t>
-  </si>
-  <si>
     <t>NO</t>
   </si>
   <si>
     <t>No statistical evidence that delta_vn1y_yield leads VN-Index returns.</t>
   </si>
   <si>
-    <t>pe_zscore</t>
+    <t>No statistical evidence that delta_usdjpy leads VN-Index returns.</t>
   </si>
   <si>
     <t>No statistical evidence that pe_zscore leads VN-Index returns.</t>
@@ -440,9 +446,6 @@
     <t>No statistical evidence that delta_us10y leads VN-Index returns.</t>
   </si>
   <si>
-    <t>No statistical evidence that delta_usdjpy leads VN-Index returns.</t>
-  </si>
-  <si>
     <t>MACHINE LEARNING — WALK-FORWARD VALIDATION (no look-ahead bias)</t>
   </si>
   <si>
@@ -461,7 +464,7 @@
     <t>Features</t>
   </si>
   <si>
-    <t>104</t>
+    <t>136</t>
   </si>
   <si>
     <t>Mean Accuracy</t>
@@ -515,130 +518,130 @@
     <t>Importance</t>
   </si>
   <si>
+    <t>m2_yoy_pct</t>
+  </si>
+  <si>
+    <t>bb_lower</t>
+  </si>
+  <si>
     <t>ema_20</t>
   </si>
   <si>
+    <t>bb_mid</t>
+  </si>
+  <si>
+    <t>us10y_30d_change</t>
+  </si>
+  <si>
+    <t>us10y_zscore_1y</t>
+  </si>
+  <si>
+    <t>oil_n_shock_days_ytd</t>
+  </si>
+  <si>
     <t>macd_line</t>
   </si>
   <si>
-    <t>etf_flow_q_zscore</t>
-  </si>
-  <si>
-    <t>bb_mid</t>
-  </si>
-  <si>
-    <t>us10y_30d_change</t>
-  </si>
-  <si>
-    <t>usd_vnd_zscore_lag1</t>
-  </si>
-  <si>
-    <t>us10y_zscore_1y</t>
-  </si>
-  <si>
-    <t>oil_n_shock_days_ytd</t>
-  </si>
-  <si>
-    <t>etf_flow_q_zscore_live</t>
+    <t>oil_max_weekly_change_ytd</t>
+  </si>
+  <si>
+    <t>valuation_composite_score</t>
+  </si>
+  <si>
+    <t>headline_pe</t>
   </si>
   <si>
     <t>dxy_zscore_60d</t>
   </si>
   <si>
-    <t>bb_lower</t>
-  </si>
-  <si>
-    <t>ex_vingroup_pe</t>
+    <t>nff_ex_etf_rolling60d</t>
+  </si>
+  <si>
+    <t>macd_signal</t>
+  </si>
+  <si>
+    <t>FACTOR-LEVEL SCORE DECOMPOSITION — 2026-Q4</t>
+  </si>
+  <si>
+    <t>Every indicator inside each pillar with its parsed 0-100 score. &lt;MISSING&gt; indicators fall back to neutral 50.</t>
+  </si>
+  <si>
+    <t>Pillar Weight</t>
+  </si>
+  <si>
+    <t>Indicator</t>
+  </si>
+  <si>
+    <t>Observed Value / Analysis</t>
+  </si>
+  <si>
+    <t>Score (0-100)</t>
+  </si>
+  <si>
+    <t>Data Status</t>
+  </si>
+  <si>
+    <t>vn1y_yield</t>
+  </si>
+  <si>
+    <t>3.82%</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>ir_trend</t>
+  </si>
+  <si>
+    <t>Δ VN1Y = -0.0067 (→ Hold)</t>
+  </si>
+  <si>
+    <t>usd_vnd</t>
+  </si>
+  <si>
+    <t>Z-score = -1.29</t>
+  </si>
+  <si>
+    <t>m2_yoy_growth</t>
+  </si>
+  <si>
+    <t>15.0% YoY</t>
+  </si>
+  <si>
+    <t>vn_bonds</t>
+  </si>
+  <si>
+    <t>VN10Y 4.49% | Spread 0.56%</t>
+  </si>
+  <si>
+    <t>dxy</t>
+  </si>
+  <si>
+    <t>Z = 1.56</t>
+  </si>
+  <si>
+    <t>us10y</t>
+  </si>
+  <si>
+    <t>5.29%</t>
+  </si>
+  <si>
+    <t>nff_ex_etf</t>
+  </si>
+  <si>
+    <t>Z = -0.12 (Neutral)</t>
   </si>
   <si>
     <t>nff_ex_etf_q_ytd</t>
   </si>
   <si>
-    <t>nff_ex_etf_rolling60d</t>
-  </si>
-  <si>
-    <t>rvol_10d</t>
-  </si>
-  <si>
-    <t>FACTOR-LEVEL SCORE DECOMPOSITION — 2026-Q4</t>
-  </si>
-  <si>
-    <t>Every indicator inside each pillar with its parsed 0-100 score. &lt;MISSING&gt; indicators fall back to neutral 50.</t>
-  </si>
-  <si>
-    <t>Pillar Weight</t>
-  </si>
-  <si>
-    <t>Indicator</t>
-  </si>
-  <si>
-    <t>Observed Value / Analysis</t>
-  </si>
-  <si>
-    <t>Score (0-100)</t>
-  </si>
-  <si>
-    <t>Data Status</t>
-  </si>
-  <si>
-    <t>vn1y_yield</t>
-  </si>
-  <si>
-    <t>3.86%</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>ir_trend</t>
-  </si>
-  <si>
-    <t>Δ VN1Y = 0.0044 (→ Hold)</t>
-  </si>
-  <si>
-    <t>usd_vnd</t>
-  </si>
-  <si>
-    <t>Z-score = -1.27</t>
-  </si>
-  <si>
-    <t>m2_yoy_growth</t>
-  </si>
-  <si>
-    <t>15.0% YoY</t>
-  </si>
-  <si>
-    <t>vn_bonds</t>
-  </si>
-  <si>
-    <t>VN10Y 4.48% | Spread 0.53%</t>
-  </si>
-  <si>
-    <t>dxy</t>
-  </si>
-  <si>
-    <t>Z = 1.05</t>
-  </si>
-  <si>
-    <t>us10y</t>
-  </si>
-  <si>
-    <t>5.18%</t>
-  </si>
-  <si>
-    <t>nff_ex_etf</t>
-  </si>
-  <si>
-    <t>Z = -0.05 (Neutral)</t>
-  </si>
-  <si>
-    <t>-0.16% of Market Cap (YTD in Q)</t>
+    <t>-0.18% of Market Cap (YTD in Q)</t>
   </si>
   <si>
     <t>jpy_carry</t>
   </si>
   <si>
-    <t>Z = -0.16 (Neutral)</t>
+    <t>Z = -0.58 (Neutral)</t>
   </si>
   <si>
     <t>oil_shock</t>
@@ -647,13 +650,13 @@
     <t>Oil Shock Score = 43.8 (Max Δ5d = 19.5%)</t>
   </si>
   <si>
-    <t>P/E Headline: 12.46 | Median: 10.25 | Ex-VG: 10.03 | Z = 0.81 (FAIR VALUE)</t>
+    <t>P/E Headline: 12.36 | Median: 9.92 | Ex-VG: 9.92 | Z = 0.75 (FAIR VALUE)</t>
   </si>
   <si>
     <t>pb_zscore</t>
   </si>
   <si>
-    <t>Z = 0.68 (FAIR VALUE)</t>
+    <t>Z = 0.64 (FAIR VALUE)</t>
   </si>
   <si>
     <t>margin_risk</t>
@@ -665,25 +668,25 @@
     <t>eyg_zscore</t>
   </si>
   <si>
-    <t>EYG Z-score = -1.25</t>
+    <t>EYG Z-score = -1.22</t>
   </si>
   <si>
     <t>mlr_forecast</t>
   </si>
   <si>
-    <t>Forward log-return/day (next ~1M) = -0.0006</t>
+    <t>Forward log-return/day (next ~1M) = -0.0002</t>
   </si>
   <si>
     <t>var_forecast</t>
   </si>
   <si>
-    <t>VAR T+5 return = 0.0011</t>
+    <t>VAR T+5 return = 0.0001</t>
   </si>
   <si>
     <t>mlr_adj_r2</t>
   </si>
   <si>
-    <t>Adj-R² = 0.1092 → confidence bonus 1.1</t>
+    <t>Adj-R² = 0.0602 → confidence bonus 0.6</t>
   </si>
   <si>
     <t>granger_leaders</t>
@@ -692,16 +695,22 @@
     <t>1 vars Granger-cause VNI (p&lt;5%)</t>
   </si>
   <si>
+    <t>signal_coverage</t>
+  </si>
+  <si>
+    <t>Both MLR &amp; VAR live — simple average (50/50)</t>
+  </si>
+  <si>
     <t>model_quality</t>
   </si>
   <si>
-    <t>Accuracy=42.5% F1=0.369</t>
+    <t>Accuracy=48.5% F1=0.433</t>
   </si>
   <si>
     <t>ml_signal</t>
   </si>
   <si>
-    <t>Forecast: DOWN (conf=50.0%)</t>
+    <t>Forecast: DOWN (conf=62.6%)</t>
   </si>
   <si>
     <t>ftse_upgrade</t>
@@ -713,19 +722,19 @@
     <t>rebalancing</t>
   </si>
   <si>
-    <t>0 months to rebalancing → bonus +20</t>
+    <t>3 months to rebalancing → bonus +6</t>
   </si>
   <si>
     <t>adtv</t>
   </si>
   <si>
-    <t>ADTV change -11.9% QoQ</t>
+    <t>ADTV change -12.3% QoQ</t>
   </si>
   <si>
     <t>etf_flow</t>
   </si>
   <si>
-    <t>Z = -0.12 (Neutral)</t>
+    <t>Z = -0.11 (Neutral)</t>
   </si>
   <si>
     <t>etf_flow_q_ytd</t>
@@ -938,7 +947,7 @@
     <t>Data: vnstock (HOSE OHLCV, foreign flows, valuation), yfinance/FRED (DXY, US10Y, USD/JPY), SBV (rates, USD/VND), KBNN (VN yield curve).</t>
   </si>
   <si>
-    <t>Workbook generated at 2026-09-29 16:27:01 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
+    <t>Workbook generated at 2026-10-01 14:40:52 from output/exports/score_*.json, data/scores/quarterly_scores_history.parquet and data/scores/vnindex_quarterly_close.json.</t>
   </si>
   <si>
     <t>Disclaimer: for research purposes only. Not financial advice.</t>
@@ -1289,22 +1298,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>14.48</c:v>
+                  <c:v>14.62</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.28</c:v>
+                  <c:v>6.58</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.08</c:v>
+                  <c:v>8.220000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.63</c:v>
+                  <c:v>7.74</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.16</c:v>
+                  <c:v>3.95</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.04</c:v>
+                  <c:v>5.57</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1548,7 +1557,7 @@
                   <c:v>30.12</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>33.97</c:v>
+                  <c:v>31.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1727,7 +1736,7 @@
                   <c:v>46.59</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>47.67</c:v>
+                  <c:v>46.68000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1909,10 +1918,10 @@
                   <c:v>1860.01</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1780.68</c:v>
+                  <c:v>1768.62</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>1749.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,43 +2080,46 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'02_Factor_Impact'!$B$6:$B$17</c:f>
+              <c:f>'02_Factor_Impact'!$B$6:$B$18</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
+                  <c:v>delta_vn1y_yield</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>delta_dxy</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>pe_zscore</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>delta_us10y</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>delta_usdjpy</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>usd_vnd_pct_change</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>rsi_14</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>macd_hist</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>bb_pct</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>rvol_20d</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>drawdown_from_peak</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>price_vs_ma200</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>log_return_lag1</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>log_return_lag5</c:v>
                 </c:pt>
               </c:strCache>
@@ -2115,45 +2127,48 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'02_Factor_Impact'!$C$6:$C$17</c:f>
+              <c:f>'02_Factor_Impact'!$C$6:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>-0.036358</c:v>
+                  <c:v>-0.007046</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.000137</c:v>
+                  <c:v>-0.04764</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.032628</c:v>
+                  <c:v>-0.000235</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.002719</c:v>
+                  <c:v>-0.003042</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.899999999999999e-05</c:v>
+                  <c:v>-0.054515</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-8.000000000000001e-05</c:v>
+                  <c:v>-0.09286899999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.000221</c:v>
+                  <c:v>2.9e-05</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.002852</c:v>
+                  <c:v>-2e-05</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.029501</c:v>
+                  <c:v>-0.000111</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.006628</c:v>
+                  <c:v>-0.007878</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.005037</c:v>
+                  <c:v>0.002128</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.000575</c:v>
+                  <c:v>-0.008406</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.001914</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2277,28 +2292,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.5077</c:v>
+                  <c:v>0.4923</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2308</c:v>
+                  <c:v>0.2769</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.3077</c:v>
+                  <c:v>0.4308</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1846</c:v>
+                  <c:v>0.3385</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5385</c:v>
+                  <c:v>0.4615</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4769</c:v>
+                  <c:v>0.6768999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.6</c:v>
+                  <c:v>0.5538</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.5538</c:v>
+                  <c:v>0.6462</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2355,28 +2370,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.4311</c:v>
+                  <c:v>0.42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.1253</c:v>
+                  <c:v>0.1966</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.2744</c:v>
+                  <c:v>0.4119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.1733</c:v>
+                  <c:v>0.3863</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.4494</c:v>
+                  <c:v>0.2915</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.4372</c:v>
+                  <c:v>0.634</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5671</c:v>
+                  <c:v>0.529</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.496</c:v>
+                  <c:v>0.5918</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2471,13 +2486,13 @@
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>m2_yoy_pct</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>bb_lower</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>ema_20</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>macd_line</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>etf_flow_q_zscore</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>bb_mid</c:v>
@@ -2486,34 +2501,34 @@
                   <c:v>us10y_30d_change</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>usd_vnd_zscore_lag1</c:v>
+                  <c:v>us10y_zscore_1y</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>us10y_zscore_1y</c:v>
+                  <c:v>oil_n_shock_days_ytd</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>oil_n_shock_days_ytd</c:v>
+                  <c:v>macd_line</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>etf_flow_q_zscore_live</c:v>
+                  <c:v>oil_max_weekly_change_ytd</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>valuation_composite_score</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>headline_pe</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>dxy_zscore_60d</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>bb_lower</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>ex_vingroup_pe</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>nff_ex_etf_q_ytd</c:v>
+                  <c:v>nff_ex_etf_rolling60d</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>nff_ex_etf_rolling60d</c:v>
+                  <c:v>price_vs_ma200</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>rvol_10d</c:v>
+                  <c:v>macd_signal</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2525,49 +2540,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.02178040146827698</c:v>
+                  <c:v>0.01707467995584011</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.02076428011059761</c:v>
+                  <c:v>0.01457174587994814</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.01783575303852558</c:v>
+                  <c:v>0.01421605050563812</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.01772940717637539</c:v>
+                  <c:v>0.0133400084450841</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.01733604446053505</c:v>
+                  <c:v>0.01314797159284353</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0167862419039011</c:v>
+                  <c:v>0.01264037005603313</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.01557330787181854</c:v>
+                  <c:v>0.01242248620837927</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.01539521757513285</c:v>
+                  <c:v>0.01232288777828217</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.01488733943551779</c:v>
+                  <c:v>0.01212919689714909</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.01360253803431988</c:v>
+                  <c:v>0.01088140346109867</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.0134799899533391</c:v>
+                  <c:v>0.01080580707639456</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.01324111688882113</c:v>
+                  <c:v>0.01069003902375698</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.01247525215148926</c:v>
+                  <c:v>0.01060809195041656</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.01242704410105944</c:v>
+                  <c:v>0.01058133877813816</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.01225554849952459</c:v>
+                  <c:v>0.01048300601541996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2657,9 +2672,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'06_Signal_Efficacy'!$B$27:$B$48</c:f>
+              <c:f>'06_Signal_Efficacy'!$B$27:$B$49</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>2021-Q1</c:v>
                 </c:pt>
@@ -2725,16 +2740,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>2026-Q2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2026-Q3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'06_Signal_Efficacy'!$K$27:$K$48</c:f>
+              <c:f>'06_Signal_Efficacy'!$K$27:$K$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>114.12242748271</c:v>
                 </c:pt>
@@ -2799,7 +2817,10 @@
                   <c:v>125.4706394243471</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>124.935503278545</c:v>
+                  <c:v>124.8541501723005</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>124.7177623568665</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2824,9 +2845,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'06_Signal_Efficacy'!$B$27:$B$48</c:f>
+              <c:f>'06_Signal_Efficacy'!$B$27:$B$49</c:f>
               <c:strCache>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>2021-Q1</c:v>
                 </c:pt>
@@ -2892,16 +2913,19 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>2026-Q2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2026-Q3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'06_Signal_Efficacy'!$L$27:$L$48</c:f>
+              <c:f>'06_Signal_Efficacy'!$L$27:$L$49</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
+                <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>118.2224870744645</c:v>
                 </c:pt>
@@ -2966,7 +2990,10 @@
                   <c:v>156.1144497414892</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>149.4561203249849</c:v>
+                  <c:v>148.4438998187067</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>146.822332639495</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3093,13 +3120,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3193,13 +3220,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3630,13 +3657,13 @@
         <v>0.25</v>
       </c>
       <c r="D14" s="10">
-        <v>57.92</v>
+        <v>58.47</v>
       </c>
       <c r="E14" s="10">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="F14" s="11">
-        <v>0.3037549821690791</v>
+        <v>0.3131962296486718</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>25</v>
@@ -3650,13 +3677,13 @@
         <v>0.2</v>
       </c>
       <c r="D15" s="10">
-        <v>36.4</v>
+        <v>32.9</v>
       </c>
       <c r="E15" s="10">
-        <v>7.28</v>
+        <v>6.58</v>
       </c>
       <c r="F15" s="11">
-        <v>0.1527165932452276</v>
+        <v>0.1409597257926307</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>27</v>
@@ -3670,13 +3697,13 @@
         <v>0.2</v>
       </c>
       <c r="D16" s="10">
-        <v>40.39</v>
+        <v>41.08</v>
       </c>
       <c r="E16" s="10">
-        <v>8.08</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="F16" s="11">
-        <v>0.1694986364589889</v>
+        <v>0.1760925449871465</v>
       </c>
       <c r="G16" s="13" t="s">
         <v>27</v>
@@ -3690,13 +3717,13 @@
         <v>0.15</v>
       </c>
       <c r="D17" s="10">
-        <v>50.84</v>
+        <v>51.6</v>
       </c>
       <c r="E17" s="10">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="F17" s="11">
-        <v>0.1600587371512482</v>
+        <v>0.1658097686375321</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>25</v>
@@ -3710,13 +3737,13 @@
         <v>0.1</v>
       </c>
       <c r="D18" s="10">
-        <v>41.57</v>
+        <v>39.52</v>
       </c>
       <c r="E18" s="10">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="F18" s="11">
-        <v>0.08726662471155863</v>
+        <v>0.08461868037703514</v>
       </c>
       <c r="G18" s="13" t="s">
         <v>27</v>
@@ -3730,13 +3757,13 @@
         <v>0.1</v>
       </c>
       <c r="D19" s="10">
-        <v>60.43</v>
+        <v>55.67</v>
       </c>
       <c r="E19" s="10">
-        <v>6.04</v>
+        <v>5.57</v>
       </c>
       <c r="F19" s="11">
-        <v>0.1267044262638976</v>
+        <v>0.1193230505569837</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>25</v>
@@ -3751,7 +3778,7 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="10">
-        <v>47.67</v>
+        <v>46.68</v>
       </c>
       <c r="F20" s="11">
         <v>1</v>
@@ -4960,7 +4987,7 @@
         <v>0.1107919426213355</v>
       </c>
       <c r="Q27" s="11">
-        <v>-0.0426503083316756</v>
+        <v>-0.04913414444008368</v>
       </c>
     </row>
     <row r="28" spans="2:17">
@@ -5004,13 +5031,13 @@
         <v>4.42</v>
       </c>
       <c r="O28" s="10">
-        <v>1780.68</v>
+        <v>1768.62</v>
       </c>
       <c r="P28" s="11">
-        <v>-0.0426503083316756</v>
-      </c>
-      <c r="Q28" s="14" t="s">
-        <v>49</v>
+        <v>-0.04913414444008368</v>
+      </c>
+      <c r="Q28" s="11">
+        <v>-0.01092377107575393</v>
       </c>
     </row>
     <row r="29" spans="2:17">
@@ -5018,13 +5045,13 @@
         <v>76</v>
       </c>
       <c r="C29" s="10">
-        <v>47.67</v>
+        <v>46.68000000000001</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="10">
-        <v>33.97</v>
+        <v>31.5</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>56</v>
@@ -5036,28 +5063,28 @@
         <v>48</v>
       </c>
       <c r="I29" s="10">
-        <v>14.48</v>
+        <v>14.62</v>
       </c>
       <c r="J29" s="10">
-        <v>7.28</v>
+        <v>6.58</v>
       </c>
       <c r="K29" s="10">
-        <v>8.08</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L29" s="10">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="M29" s="10">
-        <v>4.16</v>
+        <v>3.95</v>
       </c>
       <c r="N29" s="10">
-        <v>6.04</v>
-      </c>
-      <c r="O29" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="P29" s="14" t="s">
-        <v>49</v>
+        <v>5.57</v>
+      </c>
+      <c r="O29" s="10">
+        <v>1749.3</v>
+      </c>
+      <c r="P29" s="11">
+        <v>-0.01092377107575393</v>
       </c>
       <c r="Q29" s="14" t="s">
         <v>49</v>
@@ -5110,7 +5137,7 @@
   <sheetPr>
     <tabColor rgb="FF8B5CF6"/>
   </sheetPr>
-  <dimension ref="B2:AA52"/>
+  <dimension ref="B2:AA55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -5163,10 +5190,10 @@
         <v>88</v>
       </c>
       <c r="C6" s="15">
-        <v>-0.036358</v>
+        <v>-0.007046</v>
       </c>
       <c r="D6" s="16">
-        <v>0.0278</v>
+        <v>0.0422</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>89</v>
@@ -5181,7 +5208,7 @@
         <v>91</v>
       </c>
       <c r="I6" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="18" t="s">
         <v>92</v>
@@ -5192,10 +5219,10 @@
         <v>93</v>
       </c>
       <c r="C7" s="15">
-        <v>0.000137</v>
+        <v>-0.04764</v>
       </c>
       <c r="D7" s="16">
-        <v>0.9441000000000001</v>
+        <v>0.0076</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>94</v>
@@ -5204,129 +5231,129 @@
         <v>90</v>
       </c>
       <c r="G7" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" s="14">
+        <v>3</v>
+      </c>
+      <c r="J7" s="18" t="s">
         <v>95</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I7" s="14">
-        <v>10</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8" s="15">
-        <v>-0.032628</v>
+        <v>-0.000235</v>
       </c>
       <c r="D8" s="16">
-        <v>0.0592</v>
+        <v>0.7077</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>96</v>
+      <c r="H8" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="I8" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C9" s="15">
-        <v>-0.002719</v>
+        <v>-0.003042</v>
       </c>
       <c r="D9" s="16">
-        <v>0.7492</v>
+        <v>0.0195</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="13" t="s">
-        <v>96</v>
+      <c r="H9" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="I9" s="14">
         <v>7</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C10" s="15">
-        <v>9.899999999999999E-05</v>
+        <v>-0.054515</v>
       </c>
       <c r="D10" s="16">
-        <v>0.0223</v>
+        <v>0</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>102</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I10" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J10" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="15">
+        <v>-0.09286899999999999</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0.1237</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>106</v>
-      </c>
-      <c r="C11" s="15">
-        <v>-8.000000000000001E-05</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.2363</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>102</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>90</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I11" s="14">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J11" s="18" t="s">
         <v>107</v>
@@ -5337,25 +5364,25 @@
         <v>108</v>
       </c>
       <c r="C12" s="15">
-        <v>-0.000221</v>
+        <v>2.9E-05</v>
       </c>
       <c r="D12" s="16">
-        <v>0.8799</v>
+        <v>0.4734</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F12" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>90</v>
-      </c>
       <c r="H12" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I12" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J12" s="18" t="s">
         <v>109</v>
@@ -5366,25 +5393,25 @@
         <v>110</v>
       </c>
       <c r="C13" s="15">
-        <v>-0.002852</v>
+        <v>-2E-05</v>
       </c>
       <c r="D13" s="16">
-        <v>0.3781</v>
+        <v>0.8053</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>90</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I13" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J13" s="18" t="s">
         <v>111</v>
@@ -5395,288 +5422,237 @@
         <v>112</v>
       </c>
       <c r="C14" s="15">
-        <v>-0.029501</v>
+        <v>-0.000111</v>
       </c>
       <c r="D14" s="16">
-        <v>0.0005999999999999999</v>
+        <v>0.986</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>90</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" s="15">
+        <v>-0.007878</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0.5072</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="14">
+        <v>5</v>
+      </c>
+      <c r="J15" s="18" t="s">
         <v>115</v>
-      </c>
-      <c r="C15" s="15">
-        <v>0.006628</v>
-      </c>
-      <c r="D15" s="16">
-        <v>0.08939999999999999</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" s="14">
-        <v>4</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="15">
+        <v>0.002128</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0.8106</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="14">
+        <v>8</v>
+      </c>
+      <c r="J16" s="18" t="s">
         <v>117</v>
-      </c>
-      <c r="C16" s="15">
-        <v>-0.005037</v>
-      </c>
-      <c r="D16" s="16">
-        <v>0.2276</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="14">
-        <v>5</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" s="15">
-        <v>-0.000575</v>
+        <v>-0.008406</v>
       </c>
       <c r="D17" s="16">
-        <v>0.8627</v>
+        <v>0.232</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>90</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J17" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+      <c r="C18" s="15">
+        <v>0.001914</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.6772</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" s="14">
+        <v>9</v>
+      </c>
+      <c r="J18" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="5" t="s">
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B39" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C41" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D41" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E41" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G41" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H41" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I41" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J40" s="7" t="s">
+      <c r="J41" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K40" s="7" t="s">
+      <c r="K41" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="L41" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M41" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="N40" s="7" t="s">
+      <c r="N41" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="O40" s="7" t="s">
+      <c r="O41" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="P40" s="7" t="s">
+      <c r="P41" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="Q40" s="7" t="s">
+      <c r="Q41" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="R40" s="7" t="s">
+      <c r="R41" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="S40" s="7" t="s">
+      <c r="S41" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="T40" s="7" t="s">
+      <c r="T41" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="U40" s="7" t="s">
+      <c r="U41" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="V40" s="7" t="s">
+      <c r="V41" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="W40" s="7" t="s">
+      <c r="W41" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="X40" s="7" t="s">
+      <c r="X41" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="Y40" s="7" t="s">
+      <c r="Y41" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="Z40" s="7" t="s">
+      <c r="Z41" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="AA40" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="B41" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="16">
-        <v>0.050404</v>
-      </c>
-      <c r="D41" s="16">
-        <v>0.006624</v>
-      </c>
-      <c r="E41" s="16">
-        <v>0.013965</v>
-      </c>
-      <c r="F41" s="16">
-        <v>0.006474</v>
-      </c>
-      <c r="G41" s="16">
-        <v>0.002148</v>
-      </c>
-      <c r="H41" s="16">
-        <v>-0.004712</v>
-      </c>
-      <c r="I41" s="16">
-        <v>-0.016656</v>
-      </c>
-      <c r="J41" s="16">
-        <v>-0.016362</v>
-      </c>
-      <c r="K41" s="16">
-        <v>-0.020037</v>
-      </c>
-      <c r="L41" s="16">
-        <v>-0.012647</v>
-      </c>
-      <c r="M41" s="16">
-        <v>-0.023677</v>
-      </c>
-      <c r="N41" s="16">
-        <v>-0.018202</v>
-      </c>
-      <c r="O41" s="16">
-        <v>-0.03138</v>
-      </c>
-      <c r="P41" s="16">
-        <v>-0.034724</v>
-      </c>
-      <c r="Q41" s="16">
-        <v>-0.03524</v>
-      </c>
-      <c r="R41" s="16">
-        <v>-0.034191</v>
-      </c>
-      <c r="S41" s="16">
-        <v>-0.029253</v>
-      </c>
-      <c r="T41" s="16">
-        <v>-0.036504</v>
-      </c>
-      <c r="U41" s="16">
-        <v>-0.037081</v>
-      </c>
-      <c r="V41" s="16">
-        <v>-0.036758</v>
-      </c>
-      <c r="W41" s="16">
-        <v>-0.035163</v>
-      </c>
-      <c r="X41" s="16">
-        <v>-0.036565</v>
-      </c>
-      <c r="Y41" s="16">
-        <v>-0.035193</v>
-      </c>
-      <c r="Z41" s="16">
-        <v>-0.036358</v>
-      </c>
-      <c r="AA41" s="9">
-        <v>0.7916666666666666</v>
+      <c r="AA41" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="2:27" x14ac:dyDescent="0.25">
@@ -5684,159 +5660,159 @@
         <v>93</v>
       </c>
       <c r="C42" s="16">
-        <v>0.006803</v>
+        <v>0.050404</v>
       </c>
       <c r="D42" s="16">
-        <v>0.007754</v>
+        <v>0.006624</v>
       </c>
       <c r="E42" s="16">
-        <v>0.007541</v>
+        <v>0.013965</v>
       </c>
       <c r="F42" s="16">
-        <v>0.00665</v>
+        <v>0.006474</v>
       </c>
       <c r="G42" s="16">
-        <v>0.006591</v>
+        <v>0.002148</v>
       </c>
       <c r="H42" s="16">
-        <v>0.006584</v>
+        <v>-0.004712</v>
       </c>
       <c r="I42" s="16">
-        <v>0.007067</v>
+        <v>-0.016656</v>
       </c>
       <c r="J42" s="16">
-        <v>0.007084</v>
+        <v>-0.016362</v>
       </c>
       <c r="K42" s="16">
-        <v>0.00689</v>
+        <v>-0.020037</v>
       </c>
       <c r="L42" s="16">
-        <v>0.006287</v>
+        <v>-0.012647</v>
       </c>
       <c r="M42" s="16">
-        <v>0.003754</v>
+        <v>-0.023677</v>
       </c>
       <c r="N42" s="16">
-        <v>0.002628</v>
+        <v>-0.018202</v>
       </c>
       <c r="O42" s="16">
-        <v>0.000961</v>
+        <v>-0.03138</v>
       </c>
       <c r="P42" s="16">
-        <v>2E-06</v>
+        <v>-0.034724</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.000215</v>
+        <v>-0.03524</v>
       </c>
       <c r="R42" s="16">
-        <v>0.000127</v>
+        <v>-0.034191</v>
       </c>
       <c r="S42" s="16">
-        <v>0.000223</v>
+        <v>-0.029253</v>
       </c>
       <c r="T42" s="16">
-        <v>0.000407</v>
+        <v>-0.036504</v>
       </c>
       <c r="U42" s="16">
-        <v>9.7E-05</v>
+        <v>-0.037081</v>
       </c>
       <c r="V42" s="16">
-        <v>1.2E-05</v>
+        <v>-0.036758</v>
       </c>
       <c r="W42" s="16">
-        <v>6.8E-05</v>
+        <v>-0.035163</v>
       </c>
       <c r="X42" s="16">
-        <v>1E-05</v>
+        <v>-0.036565</v>
       </c>
       <c r="Y42" s="16">
-        <v>0.000131</v>
+        <v>-0.035193</v>
       </c>
       <c r="Z42" s="16">
-        <v>0.000137</v>
+        <v>-0.04764</v>
       </c>
       <c r="AA42" s="9">
-        <v>1</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="43" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B43" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="16">
-        <v>0.033473</v>
+        <v>0.006803</v>
       </c>
       <c r="D43" s="16">
-        <v>0.022516</v>
+        <v>0.007754</v>
       </c>
       <c r="E43" s="16">
-        <v>0.01748</v>
+        <v>0.007541</v>
       </c>
       <c r="F43" s="16">
-        <v>0.011213</v>
+        <v>0.00665</v>
       </c>
       <c r="G43" s="16">
-        <v>0.010198</v>
+        <v>0.006591</v>
       </c>
       <c r="H43" s="16">
-        <v>0.011903</v>
+        <v>0.006584</v>
       </c>
       <c r="I43" s="16">
-        <v>0.013569</v>
+        <v>0.007067</v>
       </c>
       <c r="J43" s="16">
-        <v>0.016083</v>
+        <v>0.007084</v>
       </c>
       <c r="K43" s="16">
-        <v>0.019138</v>
+        <v>0.00689</v>
       </c>
       <c r="L43" s="16">
-        <v>0.018489</v>
+        <v>0.006287</v>
       </c>
       <c r="M43" s="16">
-        <v>-0.013591</v>
+        <v>0.003754</v>
       </c>
       <c r="N43" s="16">
-        <v>-0.022457</v>
+        <v>0.002628</v>
       </c>
       <c r="O43" s="16">
-        <v>-0.034347</v>
+        <v>0.000961</v>
       </c>
       <c r="P43" s="16">
-        <v>-0.035499</v>
+        <v>2E-06</v>
       </c>
       <c r="Q43" s="16">
-        <v>-0.036478</v>
+        <v>0.000215</v>
       </c>
       <c r="R43" s="16">
-        <v>-0.034911</v>
+        <v>0.000127</v>
       </c>
       <c r="S43" s="16">
-        <v>-0.02986</v>
+        <v>0.000223</v>
       </c>
       <c r="T43" s="16">
-        <v>-0.033047</v>
+        <v>0.000407</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.033622</v>
+        <v>9.7E-05</v>
       </c>
       <c r="V43" s="16">
-        <v>-0.031625</v>
+        <v>1.2E-05</v>
       </c>
       <c r="W43" s="16">
-        <v>-0.032236</v>
+        <v>6.8E-05</v>
       </c>
       <c r="X43" s="16">
-        <v>-0.030806</v>
+        <v>1E-05</v>
       </c>
       <c r="Y43" s="16">
-        <v>-0.030603</v>
+        <v>0.000131</v>
       </c>
       <c r="Z43" s="16">
-        <v>-0.032628</v>
+        <v>-0.003042</v>
       </c>
       <c r="AA43" s="9">
-        <v>0.5833333333333334</v>
+        <v>0.04166666666666666</v>
       </c>
     </row>
     <row r="44" spans="2:27" x14ac:dyDescent="0.25">
@@ -5844,236 +5820,236 @@
         <v>101</v>
       </c>
       <c r="C44" s="16">
-        <v>0.005801</v>
+        <v>0.033473</v>
       </c>
       <c r="D44" s="16">
-        <v>0.004894</v>
+        <v>0.022516</v>
       </c>
       <c r="E44" s="16">
-        <v>0.005028</v>
+        <v>0.01748</v>
       </c>
       <c r="F44" s="16">
-        <v>0.006399</v>
+        <v>0.011213</v>
       </c>
       <c r="G44" s="16">
-        <v>0.004831</v>
+        <v>0.010198</v>
       </c>
       <c r="H44" s="16">
-        <v>0.006396</v>
+        <v>0.011903</v>
       </c>
       <c r="I44" s="16">
-        <v>0.006124</v>
+        <v>0.013569</v>
       </c>
       <c r="J44" s="16">
-        <v>0.005942</v>
+        <v>0.016083</v>
       </c>
       <c r="K44" s="16">
-        <v>0.007115</v>
+        <v>0.019138</v>
       </c>
       <c r="L44" s="16">
-        <v>0.007019</v>
+        <v>0.018489</v>
       </c>
       <c r="M44" s="16">
-        <v>0.008952999999999999</v>
+        <v>-0.013591</v>
       </c>
       <c r="N44" s="16">
-        <v>0.009018</v>
+        <v>-0.022457</v>
       </c>
       <c r="O44" s="16">
-        <v>0.008296</v>
+        <v>-0.034347</v>
       </c>
       <c r="P44" s="16">
-        <v>0.001818</v>
+        <v>-0.035499</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.001972</v>
+        <v>-0.036478</v>
       </c>
       <c r="R44" s="16">
-        <v>0.0005419999999999999</v>
+        <v>-0.034911</v>
       </c>
       <c r="S44" s="16">
-        <v>0.000313</v>
+        <v>-0.02986</v>
       </c>
       <c r="T44" s="16">
-        <v>-0.000442</v>
+        <v>-0.033047</v>
       </c>
       <c r="U44" s="16">
-        <v>-0.001517</v>
+        <v>-0.033622</v>
       </c>
       <c r="V44" s="16">
-        <v>-0.001892</v>
+        <v>-0.031625</v>
       </c>
       <c r="W44" s="16">
-        <v>-0.00276</v>
+        <v>-0.032236</v>
       </c>
       <c r="X44" s="16">
-        <v>-0.001614</v>
+        <v>-0.030806</v>
       </c>
       <c r="Y44" s="16">
-        <v>-0.001627</v>
+        <v>-0.030603</v>
       </c>
       <c r="Z44" s="16">
-        <v>-0.002719</v>
+        <v>-0.054515</v>
       </c>
       <c r="AA44" s="9">
-        <v>0.2916666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="45" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B45" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C45" s="16">
-        <v>0.000145</v>
+        <v>0.005801</v>
       </c>
       <c r="D45" s="16">
-        <v>9.7E-05</v>
+        <v>0.004894</v>
       </c>
       <c r="E45" s="16">
-        <v>0.000109</v>
+        <v>0.005028</v>
       </c>
       <c r="F45" s="16">
-        <v>0.000108</v>
+        <v>0.006399</v>
       </c>
       <c r="G45" s="16">
-        <v>9.8E-05</v>
+        <v>0.004831</v>
       </c>
       <c r="H45" s="16">
-        <v>8.4E-05</v>
+        <v>0.006396</v>
       </c>
       <c r="I45" s="16">
-        <v>9.2E-05</v>
+        <v>0.006124</v>
       </c>
       <c r="J45" s="16">
-        <v>9.000000000000001E-05</v>
+        <v>0.005942</v>
       </c>
       <c r="K45" s="16">
-        <v>9.000000000000001E-05</v>
+        <v>0.007115</v>
       </c>
       <c r="L45" s="16">
-        <v>9.500000000000001E-05</v>
+        <v>0.007019</v>
       </c>
       <c r="M45" s="16">
-        <v>0.000116</v>
+        <v>0.008952999999999999</v>
       </c>
       <c r="N45" s="16">
-        <v>0.000108</v>
+        <v>0.009018</v>
       </c>
       <c r="O45" s="16">
-        <v>7.2E-05</v>
+        <v>0.008296</v>
       </c>
       <c r="P45" s="16">
-        <v>8.7E-05</v>
+        <v>0.001818</v>
       </c>
       <c r="Q45" s="16">
-        <v>9.899999999999999E-05</v>
+        <v>0.001972</v>
       </c>
       <c r="R45" s="16">
-        <v>0.000103</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="S45" s="16">
-        <v>0.000104</v>
+        <v>0.000313</v>
       </c>
       <c r="T45" s="16">
-        <v>8.7E-05</v>
+        <v>-0.000442</v>
       </c>
       <c r="U45" s="16">
-        <v>0.000105</v>
+        <v>-0.001517</v>
       </c>
       <c r="V45" s="16">
-        <v>9.399999999999999E-05</v>
+        <v>-0.001892</v>
       </c>
       <c r="W45" s="16">
-        <v>0.0001</v>
+        <v>-0.00276</v>
       </c>
       <c r="X45" s="16">
-        <v>0.0001</v>
+        <v>-0.001614</v>
       </c>
       <c r="Y45" s="16">
-        <v>0.000101</v>
+        <v>-0.001627</v>
       </c>
       <c r="Z45" s="16">
-        <v>9.899999999999999E-05</v>
+        <v>-0.09286899999999999</v>
       </c>
       <c r="AA45" s="9">
-        <v>1</v>
+        <v>0.2916666666666667</v>
       </c>
     </row>
     <row r="46" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B46" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C46" s="16">
-        <v>-6E-06</v>
+        <v>0.000145</v>
       </c>
       <c r="D46" s="16">
-        <v>-4.2E-05</v>
+        <v>9.7E-05</v>
       </c>
       <c r="E46" s="16">
-        <v>-6.3E-05</v>
+        <v>0.000109</v>
       </c>
       <c r="F46" s="16">
-        <v>-5.6E-05</v>
+        <v>0.000108</v>
       </c>
       <c r="G46" s="16">
-        <v>-9.000000000000001E-05</v>
+        <v>9.8E-05</v>
       </c>
       <c r="H46" s="16">
-        <v>-9.899999999999999E-05</v>
+        <v>8.4E-05</v>
       </c>
       <c r="I46" s="16">
-        <v>-9.1E-05</v>
+        <v>9.2E-05</v>
       </c>
       <c r="J46" s="16">
-        <v>-0.000101</v>
+        <v>9.000000000000001E-05</v>
       </c>
       <c r="K46" s="16">
-        <v>-9.500000000000001E-05</v>
+        <v>9.000000000000001E-05</v>
       </c>
       <c r="L46" s="16">
-        <v>-9.899999999999999E-05</v>
+        <v>9.500000000000001E-05</v>
       </c>
       <c r="M46" s="16">
-        <v>-9.399999999999999E-05</v>
+        <v>0.000116</v>
       </c>
       <c r="N46" s="16">
-        <v>-0.000148</v>
+        <v>0.000108</v>
       </c>
       <c r="O46" s="16">
-        <v>-0.000107</v>
+        <v>7.2E-05</v>
       </c>
       <c r="P46" s="16">
-        <v>-7.2E-05</v>
+        <v>8.7E-05</v>
       </c>
       <c r="Q46" s="16">
-        <v>-9.7E-05</v>
+        <v>9.899999999999999E-05</v>
       </c>
       <c r="R46" s="16">
-        <v>-9.7E-05</v>
+        <v>0.000103</v>
       </c>
       <c r="S46" s="16">
-        <v>-9.399999999999999E-05</v>
+        <v>0.000104</v>
       </c>
       <c r="T46" s="16">
-        <v>-0.0001</v>
+        <v>8.7E-05</v>
       </c>
       <c r="U46" s="16">
-        <v>-8.6E-05</v>
+        <v>0.000105</v>
       </c>
       <c r="V46" s="16">
-        <v>-9.399999999999999E-05</v>
+        <v>9.399999999999999E-05</v>
       </c>
       <c r="W46" s="16">
-        <v>-9.500000000000001E-05</v>
+        <v>0.0001</v>
       </c>
       <c r="X46" s="16">
-        <v>-9.000000000000001E-05</v>
+        <v>0.0001</v>
       </c>
       <c r="Y46" s="16">
-        <v>-8.7E-05</v>
+        <v>0.000101</v>
       </c>
       <c r="Z46" s="16">
-        <v>-8.000000000000001E-05</v>
+        <v>2.9E-05</v>
       </c>
       <c r="AA46" s="9">
         <v>1</v>
@@ -6081,162 +6057,162 @@
     </row>
     <row r="47" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B47" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C47" s="16">
-        <v>-0.00157</v>
+        <v>-6E-06</v>
       </c>
       <c r="D47" s="16">
-        <v>-0.000242</v>
+        <v>-4.2E-05</v>
       </c>
       <c r="E47" s="16">
-        <v>-0.0003</v>
+        <v>-6.3E-05</v>
       </c>
       <c r="F47" s="16">
-        <v>-0.000305</v>
+        <v>-5.6E-05</v>
       </c>
       <c r="G47" s="16">
-        <v>0.000279</v>
+        <v>-9.000000000000001E-05</v>
       </c>
       <c r="H47" s="16">
-        <v>0.000702</v>
+        <v>-9.899999999999999E-05</v>
       </c>
       <c r="I47" s="16">
-        <v>0.000173</v>
+        <v>-9.1E-05</v>
       </c>
       <c r="J47" s="16">
-        <v>0.000299</v>
+        <v>-0.000101</v>
       </c>
       <c r="K47" s="16">
-        <v>0.00012</v>
+        <v>-9.500000000000001E-05</v>
       </c>
       <c r="L47" s="16">
-        <v>-0.00014</v>
+        <v>-9.899999999999999E-05</v>
       </c>
       <c r="M47" s="16">
-        <v>-0.000413</v>
+        <v>-9.399999999999999E-05</v>
       </c>
       <c r="N47" s="16">
-        <v>0.000169</v>
+        <v>-0.000148</v>
       </c>
       <c r="O47" s="16">
-        <v>0.001389</v>
+        <v>-0.000107</v>
       </c>
       <c r="P47" s="16">
-        <v>0.000673</v>
+        <v>-7.2E-05</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.000316</v>
+        <v>-9.7E-05</v>
       </c>
       <c r="R47" s="16">
-        <v>3.8E-05</v>
-      </c>
-      <c r="S47" s="14" t="s">
-        <v>94</v>
+        <v>-9.7E-05</v>
+      </c>
+      <c r="S47" s="16">
+        <v>-9.399999999999999E-05</v>
       </c>
       <c r="T47" s="16">
-        <v>0.000618</v>
-      </c>
-      <c r="U47" s="14" t="s">
-        <v>94</v>
+        <v>-0.0001</v>
+      </c>
+      <c r="U47" s="16">
+        <v>-8.6E-05</v>
       </c>
       <c r="V47" s="16">
-        <v>0.000495</v>
+        <v>-9.399999999999999E-05</v>
       </c>
       <c r="W47" s="16">
-        <v>0.000367</v>
+        <v>-9.500000000000001E-05</v>
       </c>
       <c r="X47" s="16">
-        <v>0.000112</v>
+        <v>-9.000000000000001E-05</v>
       </c>
       <c r="Y47" s="16">
-        <v>-7.4E-05</v>
+        <v>-8.7E-05</v>
       </c>
       <c r="Z47" s="16">
-        <v>-0.000221</v>
+        <v>-2E-05</v>
       </c>
       <c r="AA47" s="9">
-        <v>0.3636363636363636</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B48" s="8" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C48" s="16">
-        <v>-0.013109</v>
+        <v>-0.00157</v>
       </c>
       <c r="D48" s="16">
-        <v>0.003849</v>
+        <v>-0.000242</v>
       </c>
       <c r="E48" s="16">
-        <v>0.003886</v>
+        <v>-0.0003</v>
       </c>
       <c r="F48" s="16">
-        <v>0.001542</v>
+        <v>-0.000305</v>
       </c>
       <c r="G48" s="16">
-        <v>0.000296</v>
+        <v>0.000279</v>
       </c>
       <c r="H48" s="16">
-        <v>0.000697</v>
+        <v>0.000702</v>
       </c>
       <c r="I48" s="16">
-        <v>0.000845</v>
+        <v>0.000173</v>
       </c>
       <c r="J48" s="16">
-        <v>0.000343</v>
+        <v>0.000299</v>
       </c>
       <c r="K48" s="16">
-        <v>0.000402</v>
+        <v>0.00012</v>
       </c>
       <c r="L48" s="16">
-        <v>0.000299</v>
+        <v>-0.00014</v>
       </c>
       <c r="M48" s="16">
-        <v>0.000109</v>
+        <v>-0.000413</v>
       </c>
       <c r="N48" s="16">
-        <v>-0.000374</v>
+        <v>0.000169</v>
       </c>
       <c r="O48" s="16">
-        <v>-0.001812</v>
+        <v>0.001389</v>
       </c>
       <c r="P48" s="16">
-        <v>-0.0029</v>
+        <v>0.000673</v>
       </c>
       <c r="Q48" s="16">
-        <v>-0.0009</v>
+        <v>0.000316</v>
       </c>
       <c r="R48" s="16">
-        <v>-0.000527</v>
-      </c>
-      <c r="S48" s="16">
-        <v>-0.001713</v>
+        <v>3.8E-05</v>
+      </c>
+      <c r="S48" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="T48" s="16">
-        <v>-0.001567</v>
-      </c>
-      <c r="U48" s="16">
-        <v>-0.002374</v>
+        <v>0.000618</v>
+      </c>
+      <c r="U48" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="V48" s="16">
-        <v>-0.002744</v>
+        <v>0.000495</v>
       </c>
       <c r="W48" s="16">
-        <v>-0.003249</v>
+        <v>0.000367</v>
       </c>
       <c r="X48" s="16">
-        <v>-0.002727</v>
+        <v>0.000112</v>
       </c>
       <c r="Y48" s="16">
-        <v>-0.002898</v>
-      </c>
-      <c r="Z48" s="16">
-        <v>-0.002852</v>
+        <v>-7.4E-05</v>
+      </c>
+      <c r="Z48" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="AA48" s="9">
-        <v>0.5833333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.25">
@@ -6244,323 +6220,563 @@
         <v>112</v>
       </c>
       <c r="C49" s="16">
-        <v>-0.045005</v>
+        <v>-0.013109</v>
       </c>
       <c r="D49" s="16">
-        <v>-0.048312</v>
+        <v>0.003849</v>
       </c>
       <c r="E49" s="16">
-        <v>-0.052531</v>
+        <v>0.003886</v>
       </c>
       <c r="F49" s="16">
-        <v>-0.038803</v>
+        <v>0.001542</v>
       </c>
       <c r="G49" s="16">
-        <v>-0.034688</v>
+        <v>0.000296</v>
       </c>
       <c r="H49" s="16">
-        <v>-0.034572</v>
+        <v>0.000697</v>
       </c>
       <c r="I49" s="16">
-        <v>-0.031276</v>
+        <v>0.000845</v>
       </c>
       <c r="J49" s="16">
-        <v>-0.031238</v>
+        <v>0.000343</v>
       </c>
       <c r="K49" s="16">
-        <v>-0.030675</v>
+        <v>0.000402</v>
       </c>
       <c r="L49" s="16">
-        <v>-0.031084</v>
+        <v>0.000299</v>
       </c>
       <c r="M49" s="16">
-        <v>-0.034407</v>
+        <v>0.000109</v>
       </c>
       <c r="N49" s="16">
-        <v>-0.028486</v>
+        <v>-0.000374</v>
       </c>
       <c r="O49" s="16">
-        <v>-0.034882</v>
+        <v>-0.001812</v>
       </c>
       <c r="P49" s="16">
-        <v>-0.037589</v>
+        <v>-0.0029</v>
       </c>
       <c r="Q49" s="16">
-        <v>-0.03325</v>
+        <v>-0.0009</v>
       </c>
       <c r="R49" s="16">
-        <v>-0.032021</v>
+        <v>-0.000527</v>
       </c>
       <c r="S49" s="16">
-        <v>-0.030831</v>
+        <v>-0.001713</v>
       </c>
       <c r="T49" s="16">
-        <v>-0.029485</v>
+        <v>-0.001567</v>
       </c>
       <c r="U49" s="16">
-        <v>-0.031027</v>
+        <v>-0.002374</v>
       </c>
       <c r="V49" s="16">
-        <v>-0.030793</v>
+        <v>-0.002744</v>
       </c>
       <c r="W49" s="16">
-        <v>-0.030979</v>
+        <v>-0.003249</v>
       </c>
       <c r="X49" s="16">
-        <v>-0.030008</v>
+        <v>-0.002727</v>
       </c>
       <c r="Y49" s="16">
-        <v>-0.030197</v>
+        <v>-0.002898</v>
       </c>
       <c r="Z49" s="16">
-        <v>-0.029501</v>
+        <v>-0.000111</v>
       </c>
       <c r="AA49" s="9">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="50" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B50" s="8" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C50" s="16">
-        <v>0.004475</v>
+        <v>-0.045005</v>
       </c>
       <c r="D50" s="16">
-        <v>-0.001573</v>
+        <v>-0.048312</v>
       </c>
       <c r="E50" s="16">
-        <v>-0.003987</v>
+        <v>-0.052531</v>
       </c>
       <c r="F50" s="16">
-        <v>-0.00619</v>
+        <v>-0.038803</v>
       </c>
       <c r="G50" s="16">
-        <v>-0.005235</v>
+        <v>-0.034688</v>
       </c>
       <c r="H50" s="16">
-        <v>-0.004077</v>
+        <v>-0.034572</v>
       </c>
       <c r="I50" s="16">
-        <v>-0.003762</v>
+        <v>-0.031276</v>
       </c>
       <c r="J50" s="16">
-        <v>-0.003101</v>
+        <v>-0.031238</v>
       </c>
       <c r="K50" s="16">
-        <v>-0.004253</v>
+        <v>-0.030675</v>
       </c>
       <c r="L50" s="16">
-        <v>-0.003181</v>
+        <v>-0.031084</v>
       </c>
       <c r="M50" s="16">
-        <v>-0.002957</v>
+        <v>-0.034407</v>
       </c>
       <c r="N50" s="16">
-        <v>-0.0023</v>
+        <v>-0.028486</v>
       </c>
       <c r="O50" s="16">
-        <v>-0.003768</v>
+        <v>-0.034882</v>
       </c>
       <c r="P50" s="16">
-        <v>-0.004357</v>
+        <v>-0.037589</v>
       </c>
       <c r="Q50" s="16">
-        <v>-0.004951</v>
+        <v>-0.03325</v>
       </c>
       <c r="R50" s="16">
-        <v>-0.005013</v>
+        <v>-0.032021</v>
       </c>
       <c r="S50" s="16">
-        <v>-0.004654</v>
+        <v>-0.030831</v>
       </c>
       <c r="T50" s="16">
-        <v>-0.005315</v>
+        <v>-0.029485</v>
       </c>
       <c r="U50" s="16">
-        <v>-0.006199</v>
+        <v>-0.031027</v>
       </c>
       <c r="V50" s="16">
-        <v>-0.006078</v>
+        <v>-0.030793</v>
       </c>
       <c r="W50" s="16">
-        <v>-0.006727</v>
+        <v>-0.030979</v>
       </c>
       <c r="X50" s="16">
-        <v>-0.0059</v>
+        <v>-0.030008</v>
       </c>
       <c r="Y50" s="16">
-        <v>-0.005488</v>
+        <v>-0.030197</v>
       </c>
       <c r="Z50" s="16">
-        <v>-0.005037</v>
+        <v>-0.007878</v>
       </c>
       <c r="AA50" s="9">
-        <v>0.9583333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B51" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="16">
-        <v>-0.010339</v>
+        <v>0.004475</v>
       </c>
       <c r="D51" s="16">
-        <v>-0.011984</v>
+        <v>-0.001573</v>
       </c>
       <c r="E51" s="16">
-        <v>-0.010539</v>
+        <v>-0.003987</v>
       </c>
       <c r="F51" s="16">
-        <v>-0.011065</v>
+        <v>-0.00619</v>
       </c>
       <c r="G51" s="16">
-        <v>-0.007483</v>
+        <v>-0.005235</v>
       </c>
       <c r="H51" s="16">
-        <v>-0.007032</v>
+        <v>-0.004077</v>
       </c>
       <c r="I51" s="16">
-        <v>-0.007436</v>
+        <v>-0.003762</v>
       </c>
       <c r="J51" s="16">
-        <v>-0.006856</v>
+        <v>-0.003101</v>
       </c>
       <c r="K51" s="16">
-        <v>-0.007194</v>
+        <v>-0.004253</v>
       </c>
       <c r="L51" s="16">
+        <v>-0.003181</v>
+      </c>
+      <c r="M51" s="16">
+        <v>-0.002957</v>
+      </c>
+      <c r="N51" s="16">
+        <v>-0.0023</v>
+      </c>
+      <c r="O51" s="16">
+        <v>-0.003768</v>
+      </c>
+      <c r="P51" s="16">
+        <v>-0.004357</v>
+      </c>
+      <c r="Q51" s="16">
+        <v>-0.004951</v>
+      </c>
+      <c r="R51" s="16">
+        <v>-0.005013</v>
+      </c>
+      <c r="S51" s="16">
+        <v>-0.004654</v>
+      </c>
+      <c r="T51" s="16">
+        <v>-0.005315</v>
+      </c>
+      <c r="U51" s="16">
+        <v>-0.006199</v>
+      </c>
+      <c r="V51" s="16">
         <v>-0.006078</v>
       </c>
-      <c r="M51" s="16">
-        <v>-0.005673</v>
-      </c>
-      <c r="N51" s="16">
-        <v>-0.001512</v>
-      </c>
-      <c r="O51" s="16">
-        <v>-0.002039</v>
-      </c>
-      <c r="P51" s="16">
-        <v>-0.001862</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>-0.000885</v>
-      </c>
-      <c r="R51" s="16">
-        <v>-6.9E-05</v>
-      </c>
-      <c r="S51" s="16">
-        <v>-0.000309</v>
-      </c>
-      <c r="T51" s="16">
-        <v>0.000279</v>
-      </c>
-      <c r="U51" s="16">
-        <v>-0.000315</v>
-      </c>
-      <c r="V51" s="16">
-        <v>0.000144</v>
-      </c>
       <c r="W51" s="16">
-        <v>3.1E-05</v>
+        <v>-0.006727</v>
       </c>
       <c r="X51" s="16">
-        <v>-0.000149</v>
+        <v>-0.0059</v>
       </c>
       <c r="Y51" s="16">
-        <v>-0.000367</v>
+        <v>-0.005488</v>
       </c>
       <c r="Z51" s="16">
-        <v>-0.000575</v>
+        <v>-0.008406</v>
       </c>
       <c r="AA51" s="9">
-        <v>0.875</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="52" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B52" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>94</v>
+        <v>120</v>
+      </c>
+      <c r="C52" s="16">
+        <v>-0.010339</v>
       </c>
       <c r="D52" s="16">
+        <v>-0.011984</v>
+      </c>
+      <c r="E52" s="16">
+        <v>-0.010539</v>
+      </c>
+      <c r="F52" s="16">
+        <v>-0.011065</v>
+      </c>
+      <c r="G52" s="16">
+        <v>-0.007483</v>
+      </c>
+      <c r="H52" s="16">
+        <v>-0.007032</v>
+      </c>
+      <c r="I52" s="16">
+        <v>-0.007436</v>
+      </c>
+      <c r="J52" s="16">
+        <v>-0.006856</v>
+      </c>
+      <c r="K52" s="16">
+        <v>-0.007194</v>
+      </c>
+      <c r="L52" s="16">
+        <v>-0.006078</v>
+      </c>
+      <c r="M52" s="16">
+        <v>-0.005673</v>
+      </c>
+      <c r="N52" s="16">
+        <v>-0.001512</v>
+      </c>
+      <c r="O52" s="16">
+        <v>-0.002039</v>
+      </c>
+      <c r="P52" s="16">
+        <v>-0.001862</v>
+      </c>
+      <c r="Q52" s="16">
+        <v>-0.000885</v>
+      </c>
+      <c r="R52" s="16">
+        <v>-6.9E-05</v>
+      </c>
+      <c r="S52" s="16">
+        <v>-0.000309</v>
+      </c>
+      <c r="T52" s="16">
+        <v>0.000279</v>
+      </c>
+      <c r="U52" s="16">
+        <v>-0.000315</v>
+      </c>
+      <c r="V52" s="16">
+        <v>0.000144</v>
+      </c>
+      <c r="W52" s="16">
+        <v>3.1E-05</v>
+      </c>
+      <c r="X52" s="16">
+        <v>-0.000149</v>
+      </c>
+      <c r="Y52" s="16">
+        <v>-0.000367</v>
+      </c>
+      <c r="Z52" s="16">
+        <v>0.001914</v>
+      </c>
+      <c r="AA52" s="9">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B53" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="16">
         <v>0.023665</v>
       </c>
-      <c r="E52" s="16">
+      <c r="E53" s="16">
         <v>0.027307</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F53" s="16">
         <v>0.012942</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G53" s="16">
         <v>0.008152</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H53" s="16">
         <v>0.009540999999999999</v>
       </c>
-      <c r="I52" s="16">
+      <c r="I53" s="16">
         <v>0.00611</v>
       </c>
-      <c r="J52" s="16">
+      <c r="J53" s="16">
         <v>0.006012</v>
       </c>
-      <c r="K52" s="16">
+      <c r="K53" s="16">
         <v>0.00596</v>
       </c>
-      <c r="L52" s="16">
+      <c r="L53" s="16">
         <v>0.005966</v>
       </c>
-      <c r="M52" s="16">
+      <c r="M53" s="16">
         <v>0.006577</v>
       </c>
-      <c r="N52" s="16">
+      <c r="N53" s="16">
         <v>0.006169</v>
       </c>
-      <c r="O52" s="16">
+      <c r="O53" s="16">
         <v>0.009952000000000001</v>
       </c>
-      <c r="P52" s="16">
+      <c r="P53" s="16">
         <v>0.011546</v>
       </c>
-      <c r="Q52" s="16">
+      <c r="Q53" s="16">
         <v>0.009398999999999999</v>
       </c>
-      <c r="R52" s="16">
+      <c r="R53" s="16">
         <v>0.008768</v>
       </c>
-      <c r="S52" s="16">
+      <c r="S53" s="16">
         <v>0.00774</v>
       </c>
-      <c r="T52" s="16">
+      <c r="T53" s="16">
         <v>0.007517</v>
       </c>
-      <c r="U52" s="16">
+      <c r="U53" s="16">
         <v>0.007005</v>
       </c>
-      <c r="V52" s="16">
+      <c r="V53" s="16">
         <v>0.006881</v>
       </c>
-      <c r="W52" s="16">
+      <c r="W53" s="16">
         <v>0.006513</v>
       </c>
-      <c r="X52" s="16">
+      <c r="X53" s="16">
         <v>0.006515</v>
       </c>
-      <c r="Y52" s="16">
+      <c r="Y53" s="16">
         <v>0.006596</v>
       </c>
-      <c r="Z52" s="16">
-        <v>0.006628</v>
-      </c>
-      <c r="AA52" s="9">
+      <c r="Z53" s="16">
+        <v>0.002128</v>
+      </c>
+      <c r="AA53" s="9">
         <v>1</v>
       </c>
     </row>
+    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B54" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="L54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="M54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="N54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="O54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="R54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="S54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="T54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="U54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="V54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="W54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="X54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y54" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z54" s="16">
+        <v>-0.007046</v>
+      </c>
+      <c r="AA54" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B55" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="I55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="L55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="M55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="N55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="O55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="P55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="R55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="S55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="T55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="U55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="V55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="W55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="X55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y55" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z55" s="16">
+        <v>-0.000235</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C17">
+  <conditionalFormatting sqref="C6:C18">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -6574,7 +6790,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D17">
+  <conditionalFormatting sqref="D6:D18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -6595,7 +6811,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>C6:C17</xm:sqref>
+          <xm:sqref>C6:C18</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6622,12 +6838,12 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="2:7">
@@ -6635,7 +6851,7 @@
         <v>79</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>81</v>
@@ -6644,110 +6860,110 @@
         <v>82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C6" s="16">
-        <v>7.2336</v>
+        <v>10.0148</v>
       </c>
       <c r="D6" s="16">
-        <v>0.0072</v>
+        <v>0</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="8" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="C7" s="16">
-        <v>0.5046</v>
+        <v>2.3998</v>
       </c>
       <c r="D7" s="16">
-        <v>0.4775</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0.994</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.3701</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="16">
-        <v>0.3229</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0.5699</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>133</v>
-      </c>
       <c r="G8" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C9" s="16">
-        <v>0.2242</v>
+        <v>0.3216</v>
       </c>
       <c r="D9" s="16">
-        <v>0.6359</v>
+        <v>0.725</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C10" s="16">
-        <v>0.004</v>
+        <v>0.2281</v>
       </c>
       <c r="D10" s="16">
-        <v>0.9498</v>
+        <v>0.7961</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -6779,96 +6995,96 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C8" s="16">
-        <v>0.425</v>
+        <v>0.4846</v>
       </c>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C9" s="16">
-        <v>0.1599</v>
+        <v>0.1393</v>
       </c>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C10" s="16">
-        <v>0.3692</v>
+        <v>0.4326</v>
       </c>
     </row>
     <row r="11" spans="2:7">
       <c r="B11" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="16">
-        <v>0.5031</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -6876,19 +7092,19 @@
         <v>1</v>
       </c>
       <c r="C16" s="14">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D16" s="14">
         <v>65</v>
       </c>
       <c r="E16" s="16">
-        <v>0.5077</v>
+        <v>0.4923</v>
       </c>
       <c r="F16" s="16">
-        <v>0.4311</v>
+        <v>0.42</v>
       </c>
       <c r="G16" s="16">
-        <v>0.3769</v>
+        <v>0.368</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -6896,19 +7112,19 @@
         <v>2</v>
       </c>
       <c r="C17" s="14">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D17" s="14">
         <v>65</v>
       </c>
       <c r="E17" s="16">
-        <v>0.2308</v>
+        <v>0.2769</v>
       </c>
       <c r="F17" s="16">
-        <v>0.1253</v>
+        <v>0.1966</v>
       </c>
       <c r="G17" s="16">
-        <v>0.7093</v>
+        <v>0.4988</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -6916,19 +7132,19 @@
         <v>3</v>
       </c>
       <c r="C18" s="14">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="D18" s="14">
         <v>65</v>
       </c>
       <c r="E18" s="16">
-        <v>0.3077</v>
+        <v>0.4308</v>
       </c>
       <c r="F18" s="16">
-        <v>0.2744</v>
+        <v>0.4119</v>
       </c>
       <c r="G18" s="16">
-        <v>0.2511</v>
+        <v>0.4502</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -6936,19 +7152,19 @@
         <v>4</v>
       </c>
       <c r="C19" s="14">
-        <v>845</v>
+        <v>851</v>
       </c>
       <c r="D19" s="14">
         <v>65</v>
       </c>
       <c r="E19" s="16">
-        <v>0.1846</v>
+        <v>0.3385</v>
       </c>
       <c r="F19" s="16">
-        <v>0.1733</v>
+        <v>0.3863</v>
       </c>
       <c r="G19" s="16">
-        <v>0.4133</v>
+        <v>0.5746</v>
       </c>
     </row>
     <row r="20" spans="2:7">
@@ -6956,19 +7172,19 @@
         <v>5</v>
       </c>
       <c r="C20" s="14">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D20" s="14">
         <v>65</v>
       </c>
       <c r="E20" s="16">
-        <v>0.5385</v>
+        <v>0.4615</v>
       </c>
       <c r="F20" s="16">
-        <v>0.4494</v>
+        <v>0.2915</v>
       </c>
       <c r="G20" s="16">
-        <v>0.5404</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -6976,19 +7192,19 @@
         <v>6</v>
       </c>
       <c r="C21" s="14">
-        <v>975</v>
+        <v>981</v>
       </c>
       <c r="D21" s="14">
         <v>65</v>
       </c>
       <c r="E21" s="16">
-        <v>0.4769</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="F21" s="16">
-        <v>0.4372</v>
+        <v>0.634</v>
       </c>
       <c r="G21" s="16">
-        <v>0.4128</v>
+        <v>0.6059</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -6996,19 +7212,19 @@
         <v>7</v>
       </c>
       <c r="C22" s="14">
-        <v>1040</v>
+        <v>1046</v>
       </c>
       <c r="D22" s="14">
         <v>65</v>
       </c>
       <c r="E22" s="16">
-        <v>0.6</v>
+        <v>0.5538</v>
       </c>
       <c r="F22" s="16">
-        <v>0.5671</v>
+        <v>0.529</v>
       </c>
       <c r="G22" s="16">
-        <v>0.5387999999999999</v>
+        <v>0.5172</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -7016,35 +7232,35 @@
         <v>8</v>
       </c>
       <c r="C23" s="14">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="D23" s="14">
         <v>65</v>
       </c>
       <c r="E23" s="16">
-        <v>0.5538</v>
+        <v>0.6462</v>
       </c>
       <c r="F23" s="16">
-        <v>0.496</v>
+        <v>0.5918</v>
       </c>
       <c r="G23" s="16">
-        <v>0.4801</v>
+        <v>0.5462</v>
       </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="2:7">
@@ -7052,10 +7268,10 @@
         <v>1</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D28" s="16">
-        <v>0.02178040146827698</v>
+        <v>0.01707467995584011</v>
       </c>
     </row>
     <row r="29" spans="2:7">
@@ -7063,10 +7279,10 @@
         <v>2</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D29" s="16">
-        <v>0.02076428011059761</v>
+        <v>0.01457174587994814</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -7074,10 +7290,10 @@
         <v>3</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D30" s="16">
-        <v>0.01783575303852558</v>
+        <v>0.01421605050563812</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -7085,10 +7301,10 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D31" s="16">
-        <v>0.01772940717637539</v>
+        <v>0.0133400084450841</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -7096,10 +7312,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D32" s="16">
-        <v>0.01733604446053505</v>
+        <v>0.01314797159284353</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -7107,10 +7323,10 @@
         <v>6</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D33" s="16">
-        <v>0.0167862419039011</v>
+        <v>0.01264037005603313</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -7118,10 +7334,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D34" s="16">
-        <v>0.01557330787181854</v>
+        <v>0.01242248620837927</v>
       </c>
     </row>
     <row r="35" spans="2:4">
@@ -7129,10 +7345,10 @@
         <v>8</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" s="16">
-        <v>0.01539521757513285</v>
+        <v>0.01232288777828217</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -7140,10 +7356,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D36" s="16">
-        <v>0.01488733943551779</v>
+        <v>0.01212919689714909</v>
       </c>
     </row>
     <row r="37" spans="2:4">
@@ -7151,10 +7367,10 @@
         <v>10</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D37" s="16">
-        <v>0.01360253803431988</v>
+        <v>0.01088140346109867</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -7162,10 +7378,10 @@
         <v>11</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D38" s="16">
-        <v>0.0134799899533391</v>
+        <v>0.01080580707639456</v>
       </c>
     </row>
     <row r="39" spans="2:4">
@@ -7173,10 +7389,10 @@
         <v>12</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D39" s="16">
-        <v>0.01324111688882113</v>
+        <v>0.01069003902375698</v>
       </c>
     </row>
     <row r="40" spans="2:4">
@@ -7184,10 +7400,10 @@
         <v>13</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D40" s="16">
-        <v>0.01247525215148926</v>
+        <v>0.01060809195041656</v>
       </c>
     </row>
     <row r="41" spans="2:4">
@@ -7195,10 +7411,10 @@
         <v>14</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="D41" s="16">
-        <v>0.01242704410105944</v>
+        <v>0.01058133877813816</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -7209,7 +7425,7 @@
         <v>177</v>
       </c>
       <c r="D42" s="16">
-        <v>0.01225554849952459</v>
+        <v>0.01048300601541996</v>
       </c>
     </row>
   </sheetData>
@@ -7232,7 +7448,7 @@
   <sheetPr>
     <tabColor rgb="FFF97316"/>
   </sheetPr>
-  <dimension ref="B2:G32"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -7308,7 +7524,7 @@
         <v>189</v>
       </c>
       <c r="F7" s="10">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>187</v>
@@ -7368,7 +7584,7 @@
         <v>195</v>
       </c>
       <c r="F10" s="10">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G10" s="17" t="s">
         <v>187</v>
@@ -7388,7 +7604,7 @@
         <v>197</v>
       </c>
       <c r="F11" s="10">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>187</v>
@@ -7428,7 +7644,7 @@
         <v>201</v>
       </c>
       <c r="F13" s="10">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>187</v>
@@ -7442,13 +7658,13 @@
         <v>0.2</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>187</v>
@@ -7462,13 +7678,13 @@
         <v>0.2</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F15" s="10">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G15" s="17" t="s">
         <v>187</v>
@@ -7482,10 +7698,10 @@
         <v>0.2</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F16" s="10">
         <v>56</v>
@@ -7502,13 +7718,13 @@
         <v>0.2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F17" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G17" s="17" t="s">
         <v>187</v>
@@ -7522,13 +7738,13 @@
         <v>0.2</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F18" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>187</v>
@@ -7542,10 +7758,10 @@
         <v>0.2</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F19" s="10">
         <v>80</v>
@@ -7562,10 +7778,10 @@
         <v>0.2</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F20" s="10">
         <v>19</v>
@@ -7582,13 +7798,13 @@
         <v>0.15</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F21" s="10">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>187</v>
@@ -7602,13 +7818,13 @@
         <v>0.15</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F22" s="10">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G22" s="17" t="s">
         <v>187</v>
@@ -7622,13 +7838,13 @@
         <v>0.15</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G23" s="17" t="s">
         <v>187</v>
@@ -7642,13 +7858,13 @@
         <v>0.15</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G24" s="17" t="s">
         <v>187</v>
@@ -7656,19 +7872,19 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" s="9">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="F25" s="10">
-        <v>39.7</v>
+        <v>224</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>187</v>
@@ -7682,13 +7898,13 @@
         <v>0.1</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F26" s="10">
-        <v>42.5</v>
+        <v>45.86</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>187</v>
@@ -7696,19 +7912,19 @@
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9">
         <v>0.1</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F27" s="10">
-        <v>75</v>
+        <v>36.81</v>
       </c>
       <c r="G27" s="17" t="s">
         <v>187</v>
@@ -7722,13 +7938,13 @@
         <v>0.1</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>94</v>
+        <v>230</v>
+      </c>
+      <c r="F28" s="10">
+        <v>75</v>
       </c>
       <c r="G28" s="17" t="s">
         <v>187</v>
@@ -7742,13 +7958,13 @@
         <v>0.1</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="F29" s="10">
-        <v>38</v>
+        <v>232</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="G29" s="17" t="s">
         <v>187</v>
@@ -7762,13 +7978,13 @@
         <v>0.1</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F30" s="10">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G30" s="17" t="s">
         <v>187</v>
@@ -7782,13 +7998,13 @@
         <v>0.1</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>94</v>
+        <v>236</v>
+      </c>
+      <c r="F31" s="10">
+        <v>48</v>
       </c>
       <c r="G31" s="17" t="s">
         <v>187</v>
@@ -7802,21 +8018,41 @@
         <v>0.1</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>187</v>
       </c>
     </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B5:G32"/>
-  <conditionalFormatting sqref="F6:F32">
+  <autoFilter ref="B5:G33"/>
+  <conditionalFormatting sqref="F6:F33">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -7837,7 +8073,7 @@
   <sheetPr>
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
-  <dimension ref="B2:L69"/>
+  <dimension ref="B2:L70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -7853,130 +8089,130 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C5" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C6" s="16">
-        <v>0.2294181544909315</v>
+        <v>0.2428719512999113</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C7" s="16">
-        <v>0.1835121400338792</v>
+        <v>0.2183794466403162</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C8" s="16">
-        <v>0.03964834070416489</v>
+        <v>0.06348173297257896</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C9" s="16">
-        <v>-0.0254093732354602</v>
+        <v>0.02569169960474308</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C10" s="11">
-        <v>0.5</v>
+        <v>0.5217391304347826</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C11" s="11">
-        <v>0.5909090909090909</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="B12" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C12" s="11">
-        <v>0.2493550327854499</v>
+        <v>0.2471776235686654</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C13" s="11">
-        <v>0.3056281529812772</v>
+        <v>0.2987853088519887</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C14" s="11">
-        <v>0.4945612032498485</v>
+        <v>0.4682233263949502</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="4" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C15" s="10">
-        <v>0.5491911124734257</v>
+        <v>0.5325055719182512</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C16" s="10">
-        <v>0.4775014136300051</v>
+        <v>0.4489187602243451</v>
       </c>
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -8035,21 +8271,21 @@
         <v>56</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="11">
-        <v>0.01465435325963855</v>
+        <v>0.01064660820416348</v>
       </c>
       <c r="E23" s="11">
-        <v>-0.01642933677034653</v>
+        <v>-0.01367655392305023</v>
       </c>
       <c r="F23" s="11">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -8057,34 +8293,34 @@
         <v>36</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>44</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -8113,7 +8349,7 @@
         <v>0.1412242748270999</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K27" s="10">
         <v>114.12242748271</v>
@@ -8148,7 +8384,7 @@
         <v>-0.02360228603883424</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K28" s="10">
         <v>111.4288773058169</v>
@@ -8183,7 +8419,7 @@
         <v>0.05820157071963994</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K29" s="10">
         <v>117.9142129885415</v>
@@ -8218,7 +8454,7 @@
         <v>-0.002045679045305226</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K30" s="10">
         <v>117.6729983538872</v>
@@ -8253,7 +8489,7 @@
         <v>-0.05921991756860909</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K31" s="10">
         <v>110.7044130913189</v>
@@ -8288,7 +8524,7 @@
         <v>-0.005468436873747495</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K32" s="10">
         <v>110.0990329966838</v>
@@ -8323,7 +8559,7 @@
         <v>-0.03312928955666848</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K33" s="10">
         <v>106.4515302526274</v>
@@ -8358,7 +8594,7 @@
         <v>0.005714484306268553</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K34" s="10">
         <v>107.0598458516343</v>
@@ -8393,7 +8629,7 @@
         <v>0.02608393447550339</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K35" s="10">
         <v>109.8523878557859</v>
@@ -8428,7 +8664,7 @@
         <v>0.009097645021335853</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K36" s="10">
         <v>110.8517858852439</v>
@@ -8463,7 +8699,7 @@
         <v>-0.00629554217389422</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K37" s="10">
         <v>110.1539137921519</v>
@@ -8498,7 +8734,7 @@
         <v>0.0136433230377103</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K38" s="10">
         <v>111.6567792218863</v>
@@ -8533,7 +8769,7 @@
         <v>-0.003019258774696476</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K39" s="10">
         <v>111.3196585114663</v>
@@ -8568,7 +8804,7 @@
         <v>0.01026724054861401</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K40" s="10">
         <v>112.462604223193</v>
@@ -8603,7 +8839,7 @@
         <v>-0.001642933677034653</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K41" s="10">
         <v>112.2778356233077</v>
@@ -8638,7 +8874,7 @@
         <v>0.00949178231421397</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K42" s="10">
         <v>113.3435523977553</v>
@@ -8673,7 +8909,7 @@
         <v>0.005295900096414319</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K43" s="10">
         <v>113.9438085278265</v>
@@ -8708,7 +8944,7 @@
         <v>0.0622708147114609</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K44" s="10">
         <v>121.0391823161809</v>
@@ -8743,7 +8979,7 @@
         <v>0.0221682614190287</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K45" s="10">
         <v>123.7224105517115</v>
@@ -8778,7 +9014,7 @@
         <v>-0.01849267858043475</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K46" s="10">
         <v>121.4344517801821</v>
@@ -8813,7 +9049,7 @@
         <v>0.03323758278640065</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K47" s="10">
         <v>125.4706394243471</v>
@@ -8842,24 +9078,59 @@
         <v>33</v>
       </c>
       <c r="H48" s="11">
-        <v>-0.0426503083316756</v>
+        <v>-0.04913414444008368</v>
       </c>
       <c r="I48" s="11">
-        <v>-0.004265030833167561</v>
+        <v>-0.004913414444008369</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K48" s="10">
-        <v>124.935503278545</v>
+        <v>124.8541501723005</v>
       </c>
       <c r="L48" s="10">
-        <v>149.4561203249849</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="19" t="s">
-        <v>269</v>
+        <v>148.4438998187067</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12">
+      <c r="B49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="10">
+        <v>30.12</v>
+      </c>
+      <c r="D49" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F49" s="10">
+        <v>46.59</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="11">
+        <v>-0.01092377107575393</v>
+      </c>
+      <c r="I49" s="11">
+        <v>-0.001092377107575393</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="K49" s="10">
+        <v>124.7177623568665</v>
+      </c>
+      <c r="L49" s="10">
+        <v>146.822332639495</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="19" t="s">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -8885,7 +9156,7 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="2:5">
@@ -8946,104 +9217,104 @@
     </row>
     <row r="13" spans="2:5">
       <c r="B13" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="B14" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="14" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="14" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" s="14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="14" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="2:9">
       <c r="B19" s="14" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="2:9">
       <c r="B21" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="2:9">
       <c r="B22" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -9054,10 +9325,10 @@
     </row>
     <row r="23" spans="2:9">
       <c r="B23" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -9068,10 +9339,10 @@
     </row>
     <row r="24" spans="2:9">
       <c r="B24" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -9082,10 +9353,10 @@
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -9096,10 +9367,10 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -9110,10 +9381,10 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -9124,10 +9395,10 @@
     </row>
     <row r="28" spans="2:9">
       <c r="B28" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -9138,10 +9409,10 @@
     </row>
     <row r="29" spans="2:9">
       <c r="B29" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -9152,10 +9423,10 @@
     </row>
     <row r="30" spans="2:9">
       <c r="B30" s="14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
